--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -1,17 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="20490" windowHeight="7620"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -31,9 +47,15 @@
     <t>Link 3</t>
   </si>
   <si>
+    <t xml:space="preserve">Status </t>
+  </si>
+  <si>
     <t>1. Pattern: Two Pointers</t>
   </si>
   <si>
+    <t xml:space="preserve">Done </t>
+  </si>
+  <si>
     <t>Pair with Target Sum (easy)</t>
   </si>
   <si>
@@ -51,10 +73,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/remove-duplicates-from-sorted-list/</t>
     </r>
@@ -65,10 +88,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/remove-duplicates-from-sorted-array-ii/</t>
     </r>
@@ -85,10 +109,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/3sum/</t>
     </r>
@@ -99,10 +124,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/3sum-closest/</t>
     </r>
@@ -119,10 +145,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/subarray-product-less-than-k/</t>
     </r>
@@ -139,10 +166,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/4sum/</t>
     </r>
@@ -153,10 +181,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/backspace-string-compare/</t>
     </r>
@@ -167,10 +196,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/shortest-unsorted-continuous-subarray/</t>
     </r>
@@ -178,10 +208,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://www.ideserve.co.in/learn/minimum-length-subarray-sorting-which-results-in-sorted-array</t>
     </r>
@@ -195,10 +226,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/linked-list-cycle/</t>
     </r>
@@ -209,10 +241,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/linked-list-cycle-ii/</t>
     </r>
@@ -223,10 +256,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/happy-number/</t>
     </r>
@@ -243,10 +277,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/middle-of-the-linked-list/</t>
     </r>
@@ -257,10 +292,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/palindrome-linked-list/</t>
     </r>
@@ -271,10 +307,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/reorder-list/</t>
     </r>
@@ -285,10 +322,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/circular-array-loop/</t>
     </r>
@@ -320,10 +358,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/fruit-into-baskets/</t>
     </r>
@@ -334,10 +373,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/longest-substring-without-repeating-characters/</t>
     </r>
@@ -348,10 +388,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/longest-repeating-character-replacement/</t>
     </r>
@@ -362,10 +403,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/max-consecutive-ones-iii/</t>
     </r>
@@ -385,10 +427,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/permutation-in-string/</t>
     </r>
@@ -399,10 +442,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/find-all-anagrams-in-a-string/</t>
     </r>
@@ -518,10 +562,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://www.geeksforgeeks.org/check-if-any-two-intervals-overlap-among-a-given-set-of-intervals/</t>
     </r>
@@ -538,10 +583,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://www.geeksforgeeks.org/maximum-cpu-load-from-the-given-list-of-jobs/</t>
     </r>
@@ -552,10 +598,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://www.codertrain.co/employee-free-time</t>
     </r>
@@ -569,10 +616,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://www.geeksforgeeks.org/sort-an-array-which-contain-1-to-n-values-in-on-using-cycle-sort/</t>
     </r>
@@ -583,10 +631,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/missing-number/</t>
     </r>
@@ -597,10 +646,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/find-all-numbers-disappeared-in-an-array/</t>
     </r>
@@ -611,10 +661,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/find-the-duplicate-number/</t>
     </r>
@@ -625,10 +676,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/find-all-duplicates-in-an-array/</t>
     </r>
@@ -639,10 +691,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://thecodingsimplified.com/find-currupt-pair/</t>
     </r>
@@ -653,10 +706,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/first-missing-positive/</t>
     </r>
@@ -667,10 +721,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://thecodingsimplified.com/find-the-first-k-missing-positive-number/</t>
     </r>
@@ -684,10 +739,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/reverse-linked-list/</t>
     </r>
@@ -698,10 +754,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/reverse-linked-list-ii/</t>
     </r>
@@ -718,10 +775,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/reverse-nodes-in-k-group/</t>
     </r>
@@ -738,10 +796,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/rotate-list/</t>
     </r>
@@ -761,10 +820,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/valid-parentheses/description/</t>
     </r>
@@ -784,10 +844,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/daily-temperatures/</t>
     </r>
@@ -798,10 +859,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/remove-nodes-from-linked-list/</t>
     </r>
@@ -812,10 +874,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/remove-all-adjacent-duplicates-in-string-ii/</t>
     </r>
@@ -832,10 +895,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/remove-k-digits/</t>
     </r>
@@ -849,10 +913,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/first-unique-character-in-a-string/</t>
     </r>
@@ -863,10 +928,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/maximum-number-of-balloons/</t>
     </r>
@@ -877,10 +943,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/longest-palindrome/</t>
     </r>
@@ -891,10 +958,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/ransom-note/</t>
     </r>
@@ -1043,10 +1111,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/find-if-path-exists-in-graph/</t>
     </r>
@@ -1057,10 +1126,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/number-of-provinces/</t>
     </r>
@@ -1071,10 +1141,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/minimum-number-of-vertices-to-reach-all-nodes/</t>
     </r>
@@ -1088,10 +1159,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/number-of-islands/</t>
     </r>
@@ -1105,10 +1177,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/flood-fill/</t>
     </r>
@@ -1119,10 +1192,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/number-of-closed-islands/</t>
     </r>
@@ -1145,10 +1219,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/find-median-from-data-stream/</t>
     </r>
@@ -1159,10 +1234,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/sliding-window-median/</t>
     </r>
@@ -1173,10 +1249,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/ipo/</t>
     </r>
@@ -1187,10 +1264,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://www.interviewbit.com/problems/maximum-sum-combinations/</t>
     </r>
@@ -1204,10 +1282,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://www.educative.io/courses/grokking-the-coding-interview/gx2OqlvEnWG</t>
     </r>
@@ -1218,10 +1297,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://www.educative.io/courses/grokking-the-coding-interview/7npk3V3JQNr</t>
     </r>
@@ -1232,10 +1312,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://www.educative.io/courses/grokking-the-coding-interview/B8R83jyN3KY</t>
     </r>
@@ -1252,10 +1333,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/generalized-abbreviation/</t>
     </r>
@@ -1284,10 +1366,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://github.com/dipjul/Grokking-the-Coding-Interview-Patterns-for-Coding-Questions/blob/master/13.-pattern-top-k-elements/02.top-k-numbers.md</t>
     </r>
@@ -1301,10 +1384,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/k-closest-points-to-origin/</t>
     </r>
@@ -1324,10 +1408,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/kth-largest-element-in-a-stream/</t>
     </r>
@@ -1359,10 +1444,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://github.com/dipjul/Grokking-the-Coding-Interview-Patterns-for-Coding-Questions/blob/master/13.-pattern-top-k-elements/13.HeapImplementation.md</t>
     </r>
@@ -1376,10 +1462,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/merge-k-sorted-lists/</t>
     </r>
@@ -1390,10 +1477,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://www.geeksforgeeks.org/find-m-th-smallest-value-in-k-sorted-arrays/</t>
     </r>
@@ -1404,10 +1492,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://www.educative.io/courses/grokking-the-coding-interview/x1NJVYKNvqz</t>
     </r>
@@ -1418,10 +1507,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/smallest-range-covering-elements-from-k-lists/</t>
     </r>
@@ -1438,10 +1528,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/valid-palindrome-ii/</t>
     </r>
@@ -1452,10 +1543,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/maximum-length-of-pair-chain/</t>
     </r>
@@ -1466,10 +1558,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/minimum-add-to-make-parentheses-valid/</t>
     </r>
@@ -1480,10 +1573,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/remove-duplicate-letters/</t>
     </r>
@@ -1494,10 +1588,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/largest-palindromic-number/</t>
     </r>
@@ -1508,10 +1603,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/removing-minimum-and-maximum-from-array/</t>
     </r>
@@ -1525,10 +1621,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://www.geeksforgeeks.org/0-1-knapsack-problem-dp-10/</t>
     </r>
@@ -1539,10 +1636,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/partition-equal-subset-sum/</t>
     </r>
@@ -1553,10 +1651,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://www.geeksforgeeks.org/subset-sum-problem-dp-25/</t>
     </r>
@@ -1567,10 +1666,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://www.geeksforgeeks.org/partition-a-set-into-two-subsets-such-that-the-difference-of-subset-sums-is-minimum/</t>
     </r>
@@ -1590,10 +1690,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/combination-sum/</t>
     </r>
@@ -1601,10 +1702,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/combination-sum-ii/</t>
     </r>
@@ -1612,10 +1714,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/combination-sum-iii/</t>
     </r>
@@ -1626,10 +1729,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/word-search/</t>
     </r>
@@ -1637,10 +1741,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/word-search-ii/</t>
     </r>
@@ -1651,10 +1756,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/sudoku-solver/</t>
     </r>
@@ -1665,10 +1771,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/factor-combinations/</t>
     </r>
@@ -1679,10 +1786,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/split-a-string-into-the-max-number-of-unique-substrings/</t>
     </r>
@@ -1696,10 +1804,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/implement-trie-prefix-tree/</t>
     </r>
@@ -1710,10 +1819,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/index-pairs-of-a-string/</t>
     </r>
@@ -1724,10 +1834,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/design-add-and-search-words-data-structure/</t>
     </r>
@@ -1738,10 +1849,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/extra-characters-in-a-string/</t>
     </r>
@@ -1752,10 +1864,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/search-suggestions-system/</t>
     </r>
@@ -1769,10 +1882,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://www.youtube.com/watch?v=cIBFEhD77b4</t>
     </r>
@@ -1783,10 +1897,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/course-schedule/</t>
     </r>
@@ -1795,26 +1910,16 @@
     <t>Tasks Scheduling Order (medium)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
-      </rPr>
-      <t>https://leetcode.com/problems/course-schedule/</t>
-    </r>
-  </si>
-  <si>
     <t>All Tasks Scheduling Orders (hard)</t>
   </si>
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/course-schedule-ii/</t>
     </r>
@@ -1825,10 +1930,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/alien-dictionary/</t>
     </r>
@@ -1839,10 +1945,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/sequence-reconstruction/</t>
     </r>
@@ -1853,10 +1960,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/minimum-height-trees/</t>
     </r>
@@ -1870,10 +1978,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/redundant-connection/</t>
     </r>
@@ -1881,35 +1990,26 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/redundant-connection-ii/</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
-      </rPr>
-      <t>https://leetcode.com/problems/number-of-provinces/</t>
-    </r>
-  </si>
-  <si>
     <t>Is Graph Bipartite? (medium)</t>
   </si>
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/is-graph-bipartite/</t>
     </r>
@@ -1920,10 +2020,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/path-with-minimum-effort/</t>
     </r>
@@ -1937,10 +2038,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/merge-similar-items/</t>
     </r>
@@ -1951,10 +2053,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/132-pattern/</t>
     </r>
@@ -1965,10 +2068,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/my-calendar-i/</t>
     </r>
@@ -1976,10 +2080,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/my-calendar-ii/</t>
     </r>
@@ -1987,10 +2092,11 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+        <charset val="134"/>
       </rPr>
       <t>https://leetcode.com/problems/my-calendar-iii/</t>
     </r>
@@ -1999,85 +2105,248 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="12">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="31">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
-      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF1155CC"/>
+      <name val="Calibri, sans-serif"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2089,6 +2358,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -2109,9 +2384,201 @@
         <bgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
-    <border/>
+  <borders count="10">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -2125,102 +2592,567 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="24">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf quotePrefix="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -2410,24 +3342,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F207"/>
+  <sheetFormatPr defaultColWidth="12.6285714285714" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="5"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.63"/>
-    <col customWidth="1" min="2" max="2" width="65.5"/>
-    <col customWidth="1" min="3" max="3" width="77.25"/>
-    <col customWidth="1" min="4" max="4" width="53.13"/>
-    <col customWidth="1" min="5" max="5" width="30.5"/>
+    <col min="1" max="1" width="17.6285714285714" customWidth="1"/>
+    <col min="2" max="2" width="65.5047619047619" customWidth="1"/>
+    <col min="3" max="3" width="15.8571428571429" customWidth="1"/>
+    <col min="4" max="4" width="25.7142857142857" customWidth="1"/>
+    <col min="5" max="5" width="30.5047619047619" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2436,7 +3370,7 @@
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
     </row>
-    <row r="2">
+    <row r="2" customHeight="1" spans="1:6">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -2452,2171 +3386,2177 @@
       <c r="E2" s="5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3">
+      <c r="F2" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:6">
       <c r="A3" s="6"/>
       <c r="B3" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
-    </row>
-    <row r="4">
+      <c r="F3" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:5">
       <c r="A4" s="6"/>
-      <c r="B4" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>8</v>
+      <c r="B4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>10</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
     </row>
-    <row r="5">
+    <row r="5" customHeight="1" spans="1:5">
       <c r="A5" s="6"/>
-      <c r="B5" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="13"/>
-    </row>
-    <row r="6">
+      <c r="B5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="13"/>
+      <c r="E5" s="14"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:5">
       <c r="A6" s="6"/>
-      <c r="B6" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="10" t="s">
+      <c r="B6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7">
+      <c r="D6" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:5">
       <c r="A7" s="6"/>
-      <c r="B7" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>16</v>
+      <c r="B7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>18</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
     </row>
-    <row r="8">
+    <row r="8" customHeight="1" spans="1:5">
       <c r="A8" s="6"/>
-      <c r="B8" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>18</v>
+      <c r="B8" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
     </row>
-    <row r="9">
+    <row r="9" customHeight="1" spans="1:5">
       <c r="A9" s="6"/>
-      <c r="B9" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>20</v>
+      <c r="B9" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>22</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
     </row>
-    <row r="10">
+    <row r="10" customHeight="1" spans="1:5">
       <c r="A10" s="6"/>
-      <c r="B10" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>22</v>
+      <c r="B10" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>24</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
     </row>
-    <row r="11">
+    <row r="11" customHeight="1" spans="1:5">
       <c r="A11" s="6"/>
-      <c r="B11" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>24</v>
+      <c r="B11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12">
+    <row r="12" customHeight="1" spans="1:5">
       <c r="A12" s="6"/>
-      <c r="B12" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>26</v>
+      <c r="B12" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>28</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
     </row>
-    <row r="13">
+    <row r="13" customHeight="1" spans="1:5">
       <c r="A13" s="6"/>
-      <c r="B13" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>28</v>
+      <c r="B13" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>30</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
     </row>
-    <row r="14">
+    <row r="14" customHeight="1" spans="1:5">
       <c r="A14" s="6"/>
-      <c r="B14" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>30</v>
+      <c r="B14" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>32</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
     </row>
-    <row r="15">
+    <row r="15" customHeight="1" spans="1:4">
       <c r="A15" s="6"/>
-      <c r="B15" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="11" t="s">
+      <c r="B15" s="6" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="16">
+      <c r="C15" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:5">
       <c r="A16" s="6"/>
       <c r="B16" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
     </row>
-    <row r="17">
+    <row r="17" customHeight="1" spans="1:5">
       <c r="A17" s="6"/>
-      <c r="B17" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>36</v>
+      <c r="B17" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
     </row>
-    <row r="18">
+    <row r="18" customHeight="1" spans="1:5">
       <c r="A18" s="6"/>
-      <c r="B18" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>38</v>
+      <c r="B18" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
     </row>
-    <row r="19">
+    <row r="19" customHeight="1" spans="1:5">
       <c r="A19" s="6"/>
-      <c r="B19" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>40</v>
+      <c r="B19" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
     </row>
-    <row r="20">
+    <row r="20" customHeight="1" spans="1:5">
       <c r="A20" s="6"/>
-      <c r="B20" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>42</v>
+      <c r="B20" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
     </row>
-    <row r="21">
+    <row r="21" customHeight="1" spans="1:5">
       <c r="A21" s="6"/>
-      <c r="B21" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>44</v>
+      <c r="B21" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>46</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
     </row>
-    <row r="22">
+    <row r="22" customHeight="1" spans="1:5">
       <c r="A22" s="6"/>
-      <c r="B22" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>46</v>
+      <c r="B22" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
     </row>
-    <row r="23">
+    <row r="23" customHeight="1" spans="1:5">
       <c r="A23" s="6"/>
-      <c r="B23" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>48</v>
+      <c r="B23" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>50</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
     </row>
-    <row r="24">
+    <row r="24" customHeight="1" spans="1:5">
       <c r="A24" s="6"/>
-      <c r="B24" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>50</v>
+      <c r="B24" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
     </row>
-    <row r="25">
+    <row r="25" customHeight="1" spans="1:5">
       <c r="A25" s="6"/>
       <c r="B25" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
     </row>
-    <row r="26">
+    <row r="26" customHeight="1" spans="1:5">
       <c r="A26" s="6"/>
-      <c r="B26" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>53</v>
+      <c r="B26" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>55</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
     </row>
-    <row r="27">
+    <row r="27" customHeight="1" spans="1:5">
       <c r="A27" s="6"/>
-      <c r="B27" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>55</v>
+      <c r="B27" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
     </row>
-    <row r="28">
+    <row r="28" customHeight="1" spans="1:5">
       <c r="A28" s="6"/>
-      <c r="B28" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>57</v>
+      <c r="B28" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
     </row>
-    <row r="29">
+    <row r="29" customHeight="1" spans="1:5">
       <c r="A29" s="6"/>
-      <c r="B29" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>59</v>
+      <c r="B29" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
     </row>
-    <row r="30">
+    <row r="30" customHeight="1" spans="1:5">
       <c r="A30" s="6"/>
-      <c r="B30" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>61</v>
+      <c r="B30" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>63</v>
       </c>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
     </row>
-    <row r="31">
+    <row r="31" customHeight="1" spans="1:5">
       <c r="A31" s="6"/>
-      <c r="B31" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>63</v>
+      <c r="B31" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
     </row>
-    <row r="32">
+    <row r="32" customHeight="1" spans="1:5">
       <c r="A32" s="6"/>
-      <c r="B32" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>65</v>
+      <c r="B32" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>67</v>
       </c>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
     </row>
-    <row r="33">
+    <row r="33" customHeight="1" spans="1:5">
       <c r="A33" s="6"/>
-      <c r="B33" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>55</v>
+      <c r="B33" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
     </row>
-    <row r="34">
+    <row r="34" customHeight="1" spans="1:5">
       <c r="A34" s="6"/>
-      <c r="B34" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>68</v>
+      <c r="B34" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>70</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
     </row>
-    <row r="35">
+    <row r="35" customHeight="1" spans="1:5">
       <c r="A35" s="6"/>
-      <c r="B35" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>70</v>
+      <c r="B35" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
     </row>
-    <row r="36">
+    <row r="36" customHeight="1" spans="1:5">
       <c r="A36" s="6"/>
-      <c r="B36" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>72</v>
+      <c r="B36" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
     </row>
-    <row r="37">
+    <row r="37" customHeight="1" spans="1:5">
       <c r="A37" s="6"/>
-      <c r="B37" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>74</v>
+      <c r="B37" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>76</v>
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
     </row>
-    <row r="38">
+    <row r="38" customHeight="1" spans="1:5">
       <c r="A38" s="6"/>
       <c r="B38" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
     </row>
-    <row r="39">
+    <row r="39" customHeight="1" spans="1:5">
       <c r="A39" s="6"/>
-      <c r="B39" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C39" s="17" t="s">
-        <v>77</v>
+      <c r="B39" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>79</v>
       </c>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
     </row>
-    <row r="40">
+    <row r="40" customHeight="1" spans="1:5">
       <c r="A40" s="6"/>
-      <c r="B40" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C40" s="17" t="s">
-        <v>79</v>
+      <c r="B40" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>81</v>
       </c>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
     </row>
-    <row r="41">
+    <row r="41" customHeight="1" spans="1:5">
       <c r="A41" s="6"/>
-      <c r="B41" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="C41" s="17" t="s">
-        <v>81</v>
+      <c r="B41" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>83</v>
       </c>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
     </row>
-    <row r="42">
+    <row r="42" customHeight="1" spans="1:5">
       <c r="A42" s="6"/>
-      <c r="B42" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="C42" s="17" t="s">
-        <v>83</v>
+      <c r="B42" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" s="18" t="s">
+        <v>85</v>
       </c>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
     </row>
-    <row r="43">
+    <row r="43" customHeight="1" spans="1:5">
       <c r="A43" s="6"/>
-      <c r="B43" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" s="17" t="s">
-        <v>85</v>
+      <c r="B43" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43" s="18" t="s">
+        <v>87</v>
       </c>
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
     </row>
-    <row r="44">
+    <row r="44" customHeight="1" spans="1:5">
       <c r="A44" s="6"/>
-      <c r="B44" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="C44" s="17" t="s">
-        <v>87</v>
+      <c r="B44" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>89</v>
       </c>
       <c r="D44" s="8"/>
       <c r="E44" s="8"/>
     </row>
-    <row r="45">
+    <row r="45" customHeight="1" spans="1:5">
       <c r="A45" s="6"/>
       <c r="B45" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
     </row>
-    <row r="46">
+    <row r="46" customHeight="1" spans="1:5">
       <c r="A46" s="6"/>
-      <c r="B46" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="C46" s="17" t="s">
-        <v>90</v>
+      <c r="B46" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C46" s="18" t="s">
+        <v>92</v>
       </c>
       <c r="D46" s="8"/>
       <c r="E46" s="8"/>
     </row>
-    <row r="47">
+    <row r="47" customHeight="1" spans="1:5">
       <c r="A47" s="6"/>
-      <c r="B47" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="C47" s="17" t="s">
-        <v>92</v>
+      <c r="B47" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C47" s="18" t="s">
+        <v>94</v>
       </c>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
     </row>
-    <row r="48">
+    <row r="48" customHeight="1" spans="1:5">
       <c r="A48" s="6"/>
-      <c r="B48" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="C48" s="17" t="s">
-        <v>94</v>
+      <c r="B48" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C48" s="18" t="s">
+        <v>96</v>
       </c>
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
     </row>
-    <row r="49">
+    <row r="49" customHeight="1" spans="1:5">
       <c r="A49" s="6"/>
-      <c r="B49" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="C49" s="17" t="s">
-        <v>96</v>
+      <c r="B49" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C49" s="18" t="s">
+        <v>98</v>
       </c>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
     </row>
-    <row r="50">
+    <row r="50" customHeight="1" spans="1:5">
       <c r="A50" s="6"/>
-      <c r="B50" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C50" s="17" t="s">
-        <v>98</v>
+      <c r="B50" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50" s="18" t="s">
+        <v>100</v>
       </c>
       <c r="D50" s="8"/>
       <c r="E50" s="8"/>
     </row>
-    <row r="51">
+    <row r="51" customHeight="1" spans="1:5">
       <c r="A51" s="6"/>
-      <c r="B51" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C51" s="17" t="s">
-        <v>100</v>
+      <c r="B51" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="C51" s="18" t="s">
+        <v>102</v>
       </c>
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
     </row>
-    <row r="52">
+    <row r="52" customHeight="1" spans="1:5">
       <c r="A52" s="6"/>
       <c r="B52" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
     </row>
-    <row r="53">
+    <row r="53" customHeight="1" spans="1:5">
       <c r="A53" s="6"/>
-      <c r="B53" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>103</v>
+      <c r="B53" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
     </row>
-    <row r="54">
+    <row r="54" customHeight="1" spans="1:5">
       <c r="A54" s="6"/>
-      <c r="B54" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>105</v>
+      <c r="B54" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>107</v>
       </c>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
     </row>
-    <row r="55">
+    <row r="55" customHeight="1" spans="1:5">
       <c r="A55" s="6"/>
-      <c r="B55" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>107</v>
+      <c r="B55" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>109</v>
       </c>
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
     </row>
-    <row r="56">
+    <row r="56" customHeight="1" spans="1:5">
       <c r="A56" s="6"/>
-      <c r="B56" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>109</v>
+      <c r="B56" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>111</v>
       </c>
       <c r="E56" s="8"/>
     </row>
-    <row r="57">
+    <row r="57" customHeight="1" spans="1:5">
       <c r="A57" s="6"/>
-      <c r="B57" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C57" s="11" t="s">
-        <v>111</v>
+      <c r="B57" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>113</v>
       </c>
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
     </row>
-    <row r="58">
+    <row r="58" customHeight="1" spans="1:5">
       <c r="A58" s="6"/>
-      <c r="B58" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>113</v>
+      <c r="B58" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="D58" s="8"/>
       <c r="E58" s="8"/>
     </row>
-    <row r="59">
+    <row r="59" customHeight="1" spans="1:5">
       <c r="A59" s="6"/>
-      <c r="B59" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>115</v>
+      <c r="B59" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>117</v>
       </c>
       <c r="D59" s="8"/>
       <c r="E59" s="8"/>
     </row>
-    <row r="60">
+    <row r="60" customHeight="1" spans="1:5">
       <c r="A60" s="6"/>
       <c r="B60" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C60" s="8"/>
       <c r="D60" s="8"/>
       <c r="E60" s="8"/>
     </row>
-    <row r="61">
+    <row r="61" customHeight="1" spans="1:5">
       <c r="A61" s="6"/>
-      <c r="B61" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="C61" s="11" t="s">
-        <v>118</v>
+      <c r="B61" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>120</v>
       </c>
       <c r="E61" s="8"/>
     </row>
-    <row r="62">
+    <row r="62" customHeight="1" spans="1:5">
       <c r="A62" s="6"/>
-      <c r="B62" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>120</v>
+      <c r="B62" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>122</v>
       </c>
       <c r="D62" s="8"/>
       <c r="E62" s="8"/>
     </row>
-    <row r="63">
+    <row r="63" customHeight="1" spans="1:5">
       <c r="A63" s="6"/>
-      <c r="B63" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>122</v>
+      <c r="B63" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="D63" s="8"/>
       <c r="E63" s="8"/>
     </row>
-    <row r="64">
+    <row r="64" customHeight="1" spans="1:5">
       <c r="A64" s="6"/>
-      <c r="B64" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>124</v>
+      <c r="B64" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="D64" s="8"/>
       <c r="E64" s="8"/>
     </row>
-    <row r="65">
+    <row r="65" customHeight="1" spans="1:5">
       <c r="A65" s="6"/>
-      <c r="B65" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>126</v>
+      <c r="B65" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>128</v>
       </c>
       <c r="D65" s="8"/>
       <c r="E65" s="8"/>
     </row>
-    <row r="66">
+    <row r="66" customHeight="1" spans="1:5">
       <c r="A66" s="6"/>
-      <c r="B66" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>128</v>
+      <c r="B66" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="D66" s="8"/>
       <c r="E66" s="8"/>
     </row>
-    <row r="67">
+    <row r="67" customHeight="1" spans="1:5">
       <c r="A67" s="6"/>
-      <c r="B67" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>130</v>
+      <c r="B67" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>132</v>
       </c>
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
     </row>
-    <row r="68">
+    <row r="68" customHeight="1" spans="1:5">
       <c r="A68" s="6"/>
-      <c r="B68" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="C68" s="11" t="s">
-        <v>132</v>
+      <c r="B68" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>134</v>
       </c>
       <c r="D68" s="8"/>
       <c r="E68" s="8"/>
     </row>
-    <row r="69">
+    <row r="69" customHeight="1" spans="1:5">
       <c r="A69" s="6"/>
       <c r="B69" s="7" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C69" s="8"/>
       <c r="D69" s="8"/>
       <c r="E69" s="8"/>
     </row>
-    <row r="70">
+    <row r="70" customHeight="1" spans="1:5">
       <c r="A70" s="6"/>
-      <c r="B70" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="C70" s="11" t="s">
-        <v>135</v>
+      <c r="B70" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>137</v>
       </c>
       <c r="D70" s="8"/>
       <c r="E70" s="8"/>
     </row>
-    <row r="71">
+    <row r="71" customHeight="1" spans="1:5">
       <c r="A71" s="6"/>
-      <c r="B71" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="C71" s="11" t="s">
-        <v>137</v>
+      <c r="B71" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>139</v>
       </c>
       <c r="D71" s="8"/>
       <c r="E71" s="8"/>
     </row>
-    <row r="72">
+    <row r="72" customHeight="1" spans="1:5">
       <c r="A72" s="6"/>
-      <c r="B72" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="C72" s="11" t="s">
-        <v>139</v>
+      <c r="B72" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>141</v>
       </c>
       <c r="D72" s="8"/>
       <c r="E72" s="8"/>
     </row>
-    <row r="73">
+    <row r="73" customHeight="1" spans="1:5">
       <c r="A73" s="6"/>
-      <c r="B73" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="C73" s="11" t="s">
-        <v>141</v>
+      <c r="B73" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>143</v>
       </c>
       <c r="D73" s="8"/>
       <c r="E73" s="8"/>
     </row>
-    <row r="74">
+    <row r="74" customHeight="1" spans="1:5">
       <c r="A74" s="6"/>
-      <c r="B74" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="C74" s="11" t="s">
-        <v>143</v>
+      <c r="B74" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>145</v>
       </c>
       <c r="D74" s="8"/>
       <c r="E74" s="8"/>
     </row>
-    <row r="75">
+    <row r="75" customHeight="1" spans="1:5">
       <c r="A75" s="6"/>
-      <c r="B75" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C75" s="11" t="s">
-        <v>145</v>
+      <c r="B75" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>147</v>
       </c>
       <c r="D75" s="8"/>
       <c r="E75" s="8"/>
     </row>
-    <row r="76">
+    <row r="76" customHeight="1" spans="1:5">
       <c r="A76" s="6"/>
       <c r="B76" s="7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C76" s="8"/>
       <c r="D76" s="8"/>
       <c r="E76" s="8"/>
     </row>
-    <row r="77">
+    <row r="77" customHeight="1" spans="1:5">
       <c r="A77" s="6"/>
-      <c r="B77" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="C77" s="11" t="s">
-        <v>148</v>
+      <c r="B77" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>150</v>
       </c>
       <c r="D77" s="8"/>
       <c r="E77" s="8"/>
     </row>
-    <row r="78">
+    <row r="78" customHeight="1" spans="1:5">
       <c r="A78" s="6"/>
-      <c r="B78" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="C78" s="11" t="s">
-        <v>150</v>
+      <c r="B78" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="D78" s="8"/>
       <c r="E78" s="8"/>
     </row>
-    <row r="79">
+    <row r="79" customHeight="1" spans="1:5">
       <c r="A79" s="6"/>
-      <c r="B79" s="9" t="s">
-        <v>151</v>
+      <c r="B79" s="10" t="s">
+        <v>153</v>
       </c>
       <c r="C79" s="8"/>
       <c r="D79" s="8"/>
       <c r="E79" s="8"/>
     </row>
-    <row r="80">
+    <row r="80" customHeight="1" spans="1:5">
       <c r="A80" s="6"/>
-      <c r="B80" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="C80" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="D80" s="13"/>
-      <c r="E80" s="13"/>
-    </row>
-    <row r="81">
+      <c r="B80" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="D80" s="14"/>
+      <c r="E80" s="14"/>
+    </row>
+    <row r="81" customHeight="1" spans="1:5">
       <c r="A81" s="6"/>
-      <c r="B81" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="C81" s="11" t="s">
-        <v>155</v>
+      <c r="B81" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>157</v>
       </c>
       <c r="D81" s="8"/>
       <c r="E81" s="8"/>
     </row>
-    <row r="82">
+    <row r="82" customHeight="1" spans="1:5">
       <c r="A82" s="6"/>
-      <c r="B82" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="C82" s="11" t="s">
-        <v>157</v>
+      <c r="B82" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>159</v>
       </c>
       <c r="D82" s="8"/>
       <c r="E82" s="8"/>
     </row>
-    <row r="83">
+    <row r="83" customHeight="1" spans="1:5">
       <c r="A83" s="6"/>
-      <c r="B83" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="C83" s="11" t="s">
-        <v>159</v>
+      <c r="B83" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>161</v>
       </c>
       <c r="D83" s="8"/>
       <c r="E83" s="8"/>
     </row>
-    <row r="84">
+    <row r="84" customHeight="1" spans="1:5">
       <c r="A84" s="6"/>
-      <c r="B84" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="C84" s="11" t="s">
-        <v>161</v>
+      <c r="B84" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>163</v>
       </c>
       <c r="D84" s="8"/>
       <c r="E84" s="8"/>
     </row>
-    <row r="85">
+    <row r="85" customHeight="1" spans="1:5">
       <c r="A85" s="6"/>
-      <c r="B85" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="C85" s="11" t="s">
-        <v>163</v>
+      <c r="B85" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>165</v>
       </c>
       <c r="D85" s="8"/>
       <c r="E85" s="8"/>
     </row>
-    <row r="86">
+    <row r="86" customHeight="1" spans="1:5">
       <c r="A86" s="6"/>
       <c r="B86" s="7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C86" s="8"/>
       <c r="D86" s="8"/>
       <c r="E86" s="8"/>
     </row>
-    <row r="87">
+    <row r="87" customHeight="1" spans="1:5">
       <c r="A87" s="6"/>
-      <c r="B87" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="C87" s="11" t="s">
-        <v>166</v>
+      <c r="B87" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>168</v>
       </c>
       <c r="D87" s="8"/>
       <c r="E87" s="8"/>
     </row>
-    <row r="88">
+    <row r="88" customHeight="1" spans="1:5">
       <c r="A88" s="6"/>
-      <c r="B88" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="C88" s="11" t="s">
-        <v>168</v>
+      <c r="B88" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>170</v>
       </c>
       <c r="D88" s="8"/>
       <c r="E88" s="8"/>
     </row>
-    <row r="89">
+    <row r="89" customHeight="1" spans="1:5">
       <c r="A89" s="6"/>
-      <c r="B89" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C89" s="11" t="s">
-        <v>170</v>
+      <c r="B89" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>172</v>
       </c>
       <c r="D89" s="8"/>
       <c r="E89" s="8"/>
     </row>
-    <row r="90">
+    <row r="90" customHeight="1" spans="1:5">
       <c r="A90" s="6"/>
-      <c r="B90" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="C90" s="11" t="s">
-        <v>172</v>
+      <c r="B90" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>174</v>
       </c>
       <c r="D90" s="8"/>
       <c r="E90" s="8"/>
     </row>
-    <row r="91">
+    <row r="91" customHeight="1" spans="1:5">
       <c r="A91" s="6"/>
       <c r="B91" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C91" s="21"/>
+        <v>175</v>
+      </c>
+      <c r="C91" s="22"/>
       <c r="D91" s="8"/>
       <c r="E91" s="8"/>
     </row>
-    <row r="92">
+    <row r="92" customHeight="1" spans="1:5">
       <c r="A92" s="6"/>
-      <c r="B92" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="C92" s="11" t="s">
-        <v>175</v>
+      <c r="B92" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>177</v>
       </c>
       <c r="D92" s="8"/>
       <c r="E92" s="8"/>
     </row>
-    <row r="93">
+    <row r="93" customHeight="1" spans="1:5">
       <c r="A93" s="6"/>
-      <c r="B93" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="C93" s="11" t="s">
-        <v>177</v>
+      <c r="B93" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>179</v>
       </c>
       <c r="D93" s="8"/>
       <c r="E93" s="8"/>
     </row>
-    <row r="94">
+    <row r="94" customHeight="1" spans="1:5">
       <c r="A94" s="6"/>
-      <c r="B94" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C94" s="11" t="s">
-        <v>179</v>
+      <c r="B94" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>181</v>
       </c>
       <c r="D94" s="8"/>
       <c r="E94" s="8"/>
     </row>
-    <row r="95">
+    <row r="95" customHeight="1" spans="1:5">
       <c r="A95" s="6"/>
-      <c r="B95" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="C95" s="11" t="s">
-        <v>181</v>
+      <c r="B95" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="C95" s="12" t="s">
+        <v>183</v>
       </c>
       <c r="D95" s="8"/>
       <c r="E95" s="8"/>
     </row>
-    <row r="96">
+    <row r="96" customHeight="1" spans="1:5">
       <c r="A96" s="6"/>
-      <c r="B96" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="C96" s="11" t="s">
-        <v>183</v>
+      <c r="B96" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>185</v>
       </c>
       <c r="D96" s="8"/>
       <c r="E96" s="8"/>
     </row>
-    <row r="97">
+    <row r="97" customHeight="1" spans="1:5">
       <c r="A97" s="6"/>
-      <c r="B97" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="C97" s="11" t="s">
-        <v>185</v>
+      <c r="B97" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="C97" s="12" t="s">
+        <v>187</v>
       </c>
       <c r="D97" s="8"/>
       <c r="E97" s="8"/>
     </row>
-    <row r="98">
+    <row r="98" customHeight="1" spans="1:5">
       <c r="A98" s="6"/>
-      <c r="B98" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="C98" s="11" t="s">
-        <v>187</v>
+      <c r="B98" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C98" s="12" t="s">
+        <v>189</v>
       </c>
       <c r="D98" s="8"/>
       <c r="E98" s="8"/>
     </row>
-    <row r="99">
+    <row r="99" customHeight="1" spans="1:5">
       <c r="A99" s="6"/>
-      <c r="B99" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="C99" s="11" t="s">
-        <v>189</v>
+      <c r="B99" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>191</v>
       </c>
       <c r="D99" s="8"/>
       <c r="E99" s="8"/>
     </row>
-    <row r="100">
+    <row r="100" customHeight="1" spans="1:5">
       <c r="A100" s="6"/>
-      <c r="B100" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="C100" s="11" t="s">
-        <v>191</v>
+      <c r="B100" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="C100" s="12" t="s">
+        <v>193</v>
       </c>
       <c r="D100" s="8"/>
       <c r="E100" s="8"/>
     </row>
-    <row r="101">
+    <row r="101" customHeight="1" spans="1:5">
       <c r="A101" s="6"/>
-      <c r="B101" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="C101" s="11" t="s">
-        <v>193</v>
+      <c r="B101" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C101" s="12" t="s">
+        <v>195</v>
       </c>
       <c r="D101" s="8"/>
       <c r="E101" s="8"/>
     </row>
-    <row r="102">
+    <row r="102" customHeight="1" spans="1:5">
       <c r="A102" s="6"/>
-      <c r="B102" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="C102" s="11" t="s">
-        <v>195</v>
+      <c r="B102" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="C102" s="12" t="s">
+        <v>197</v>
       </c>
       <c r="D102" s="8"/>
       <c r="E102" s="8"/>
     </row>
-    <row r="103">
+    <row r="103" customHeight="1" spans="1:5">
       <c r="A103" s="6"/>
-      <c r="B103" s="15" t="s">
-        <v>196</v>
-      </c>
-      <c r="C103" s="11" t="s">
-        <v>197</v>
+      <c r="B103" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="C103" s="12" t="s">
+        <v>199</v>
       </c>
       <c r="D103" s="8"/>
       <c r="E103" s="8"/>
     </row>
-    <row r="104">
+    <row r="104" customHeight="1" spans="1:5">
       <c r="A104" s="6"/>
-      <c r="B104" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="C104" s="11" t="s">
-        <v>199</v>
+      <c r="B104" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C104" s="12" t="s">
+        <v>201</v>
       </c>
       <c r="D104" s="8"/>
       <c r="E104" s="8"/>
     </row>
-    <row r="105">
+    <row r="105" customHeight="1" spans="1:5">
       <c r="A105" s="6"/>
-      <c r="B105" s="15" t="s">
-        <v>200</v>
-      </c>
-      <c r="C105" s="11" t="s">
-        <v>201</v>
+      <c r="B105" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C105" s="12" t="s">
+        <v>203</v>
       </c>
       <c r="D105" s="8"/>
       <c r="E105" s="8"/>
     </row>
-    <row r="106">
+    <row r="106" customHeight="1" spans="1:5">
       <c r="A106" s="6"/>
-      <c r="B106" s="15" t="s">
-        <v>202</v>
-      </c>
-      <c r="C106" s="11" t="s">
-        <v>203</v>
+      <c r="B106" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="C106" s="12" t="s">
+        <v>205</v>
       </c>
       <c r="D106" s="8"/>
       <c r="E106" s="8"/>
     </row>
-    <row r="107">
+    <row r="107" customHeight="1" spans="1:5">
       <c r="A107" s="6"/>
-      <c r="B107" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="C107" s="14" t="s">
-        <v>205</v>
+      <c r="B107" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="C107" s="16" t="s">
+        <v>207</v>
       </c>
       <c r="D107" s="8"/>
       <c r="E107" s="8"/>
     </row>
-    <row r="108">
+    <row r="108" customHeight="1" spans="1:5">
       <c r="A108" s="6"/>
-      <c r="B108" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="C108" s="14" t="s">
-        <v>207</v>
+      <c r="B108" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C108" s="16" t="s">
+        <v>209</v>
       </c>
       <c r="D108" s="8"/>
       <c r="E108" s="8"/>
     </row>
-    <row r="109">
+    <row r="109" customHeight="1" spans="1:5">
       <c r="A109" s="6"/>
-      <c r="B109" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="C109" s="14" t="s">
-        <v>209</v>
+      <c r="B109" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="C109" s="16" t="s">
+        <v>211</v>
       </c>
       <c r="D109" s="8"/>
       <c r="E109" s="8"/>
     </row>
-    <row r="110">
+    <row r="110" customHeight="1" spans="1:5">
       <c r="A110" s="6"/>
-      <c r="B110" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="C110" s="14" t="s">
-        <v>211</v>
+      <c r="B110" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C110" s="16" t="s">
+        <v>213</v>
       </c>
       <c r="D110" s="8"/>
       <c r="E110" s="8"/>
     </row>
-    <row r="111">
+    <row r="111" customHeight="1" spans="1:5">
       <c r="A111" s="6"/>
-      <c r="B111" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="C111" s="14" t="s">
-        <v>213</v>
+      <c r="B111" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="C111" s="16" t="s">
+        <v>215</v>
       </c>
       <c r="D111" s="8"/>
       <c r="E111" s="8"/>
     </row>
-    <row r="112">
+    <row r="112" customHeight="1" spans="1:5">
       <c r="A112" s="6"/>
-      <c r="B112" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="C112" s="14" t="s">
-        <v>215</v>
+      <c r="B112" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="C112" s="16" t="s">
+        <v>217</v>
       </c>
       <c r="D112" s="8"/>
       <c r="E112" s="8"/>
     </row>
-    <row r="113">
+    <row r="113" customHeight="1" spans="1:5">
       <c r="A113" s="6"/>
-      <c r="B113" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="C113" s="14" t="s">
-        <v>217</v>
+      <c r="B113" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C113" s="16" t="s">
+        <v>219</v>
       </c>
       <c r="D113" s="8"/>
       <c r="E113" s="8"/>
     </row>
-    <row r="114">
+    <row r="114" customHeight="1" spans="1:5">
       <c r="A114" s="6"/>
       <c r="B114" s="7" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C114" s="8"/>
       <c r="D114" s="8"/>
       <c r="E114" s="8"/>
     </row>
-    <row r="115">
+    <row r="115" customHeight="1" spans="1:5">
       <c r="A115" s="6"/>
-      <c r="B115" s="15" t="s">
-        <v>219</v>
-      </c>
-      <c r="C115" s="11" t="s">
-        <v>220</v>
+      <c r="B115" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C115" s="12" t="s">
+        <v>222</v>
       </c>
       <c r="D115" s="8"/>
       <c r="E115" s="8"/>
     </row>
-    <row r="116">
+    <row r="116" customHeight="1" spans="1:5">
       <c r="A116" s="6"/>
-      <c r="B116" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="C116" s="11" t="s">
-        <v>222</v>
+      <c r="B116" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C116" s="12" t="s">
+        <v>224</v>
       </c>
       <c r="D116" s="8"/>
       <c r="E116" s="8"/>
     </row>
-    <row r="117">
+    <row r="117" customHeight="1" spans="1:5">
       <c r="A117" s="6"/>
-      <c r="B117" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="C117" s="11" t="s">
-        <v>224</v>
+      <c r="B117" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>226</v>
       </c>
       <c r="D117" s="8"/>
       <c r="E117" s="8"/>
     </row>
-    <row r="118">
+    <row r="118" customHeight="1" spans="1:5">
       <c r="A118" s="6"/>
-      <c r="B118" s="22" t="s">
-        <v>225</v>
+      <c r="B118" s="23" t="s">
+        <v>227</v>
       </c>
       <c r="C118" s="8"/>
       <c r="D118" s="8"/>
       <c r="E118" s="8"/>
     </row>
-    <row r="119">
+    <row r="119" customHeight="1" spans="1:5">
       <c r="A119" s="6"/>
-      <c r="B119" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="C119" s="11" t="s">
-        <v>227</v>
+      <c r="B119" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C119" s="12" t="s">
+        <v>229</v>
       </c>
       <c r="D119" s="8"/>
       <c r="E119" s="8"/>
     </row>
-    <row r="120">
+    <row r="120" customHeight="1" spans="1:5">
       <c r="A120" s="6"/>
-      <c r="B120" s="15" t="s">
-        <v>228</v>
+      <c r="B120" s="6" t="s">
+        <v>230</v>
       </c>
       <c r="C120" s="8"/>
       <c r="D120" s="8"/>
       <c r="E120" s="8"/>
     </row>
-    <row r="121">
+    <row r="121" customHeight="1" spans="1:5">
       <c r="A121" s="6"/>
-      <c r="B121" s="15" t="s">
-        <v>229</v>
-      </c>
-      <c r="C121" s="11" t="s">
-        <v>230</v>
+      <c r="B121" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C121" s="12" t="s">
+        <v>232</v>
       </c>
       <c r="D121" s="8"/>
       <c r="E121" s="8"/>
     </row>
-    <row r="122">
+    <row r="122" customHeight="1" spans="1:5">
       <c r="A122" s="6"/>
-      <c r="B122" s="15" t="s">
-        <v>231</v>
-      </c>
-      <c r="C122" s="11" t="s">
-        <v>232</v>
+      <c r="B122" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="C122" s="12" t="s">
+        <v>234</v>
       </c>
       <c r="D122" s="8"/>
       <c r="E122" s="8"/>
     </row>
-    <row r="123">
+    <row r="123" customHeight="1" spans="1:5">
       <c r="A123" s="6"/>
-      <c r="B123" s="15" t="s">
-        <v>233</v>
+      <c r="B123" s="6" t="s">
+        <v>235</v>
       </c>
       <c r="C123" s="8"/>
       <c r="D123" s="8"/>
       <c r="E123" s="8"/>
     </row>
-    <row r="124">
+    <row r="124" customHeight="1" spans="1:5">
       <c r="A124" s="6"/>
-      <c r="B124" s="15" t="s">
-        <v>234</v>
+      <c r="B124" s="6" t="s">
+        <v>236</v>
       </c>
       <c r="C124" s="8"/>
       <c r="D124" s="8"/>
       <c r="E124" s="8"/>
     </row>
-    <row r="125">
+    <row r="125" customHeight="1" spans="1:5">
       <c r="A125" s="6"/>
-      <c r="B125" s="15" t="s">
-        <v>235</v>
+      <c r="B125" s="6" t="s">
+        <v>237</v>
       </c>
       <c r="C125" s="8"/>
       <c r="D125" s="8"/>
       <c r="E125" s="8"/>
     </row>
-    <row r="126">
+    <row r="126" customHeight="1" spans="1:5">
       <c r="A126" s="6"/>
-      <c r="B126" s="22" t="s">
-        <v>236</v>
+      <c r="B126" s="23" t="s">
+        <v>238</v>
       </c>
       <c r="C126" s="8"/>
       <c r="D126" s="8"/>
       <c r="E126" s="8"/>
     </row>
-    <row r="127">
+    <row r="127" customHeight="1" spans="1:5">
       <c r="A127" s="6"/>
-      <c r="B127" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="C127" s="11" t="s">
-        <v>238</v>
+      <c r="B127" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="C127" s="12" t="s">
+        <v>240</v>
       </c>
       <c r="D127" s="8"/>
       <c r="E127" s="8"/>
     </row>
-    <row r="128">
+    <row r="128" customHeight="1" spans="1:5">
       <c r="A128" s="6"/>
-      <c r="B128" s="15" t="s">
-        <v>239</v>
-      </c>
-      <c r="C128" s="11" t="s">
-        <v>240</v>
+      <c r="B128" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C128" s="12" t="s">
+        <v>242</v>
       </c>
       <c r="D128" s="8"/>
       <c r="E128" s="8"/>
     </row>
-    <row r="129">
+    <row r="129" customHeight="1" spans="1:5">
       <c r="A129" s="6"/>
-      <c r="B129" s="15" t="s">
-        <v>241</v>
-      </c>
-      <c r="C129" s="11" t="s">
-        <v>242</v>
+      <c r="B129" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="C129" s="12" t="s">
+        <v>244</v>
       </c>
       <c r="D129" s="8"/>
       <c r="E129" s="8"/>
     </row>
-    <row r="130">
+    <row r="130" customHeight="1" spans="1:5">
       <c r="A130" s="6"/>
-      <c r="B130" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="C130" s="11" t="s">
-        <v>244</v>
+      <c r="B130" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="C130" s="12" t="s">
+        <v>246</v>
       </c>
       <c r="D130" s="8"/>
       <c r="E130" s="8"/>
     </row>
-    <row r="131">
+    <row r="131" customHeight="1" spans="1:5">
       <c r="A131" s="6"/>
-      <c r="B131" s="22" t="s">
-        <v>245</v>
+      <c r="B131" s="23" t="s">
+        <v>247</v>
       </c>
       <c r="C131" s="8"/>
       <c r="D131" s="8"/>
       <c r="E131" s="8"/>
     </row>
-    <row r="132">
+    <row r="132" customHeight="1" spans="1:5">
       <c r="A132" s="6"/>
-      <c r="B132" s="15" t="s">
-        <v>246</v>
-      </c>
-      <c r="C132" s="11" t="s">
-        <v>247</v>
+      <c r="B132" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="C132" s="12" t="s">
+        <v>249</v>
       </c>
       <c r="D132" s="8"/>
       <c r="E132" s="8"/>
     </row>
-    <row r="133">
+    <row r="133" customHeight="1" spans="1:5">
       <c r="A133" s="6"/>
-      <c r="B133" s="15" t="s">
-        <v>248</v>
-      </c>
-      <c r="C133" s="11" t="s">
-        <v>249</v>
+      <c r="B133" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C133" s="12" t="s">
+        <v>251</v>
       </c>
       <c r="D133" s="8"/>
       <c r="E133" s="8"/>
     </row>
-    <row r="134">
+    <row r="134" customHeight="1" spans="1:5">
       <c r="A134" s="6"/>
-      <c r="B134" s="15" t="s">
-        <v>250</v>
-      </c>
-      <c r="C134" s="11" t="s">
-        <v>251</v>
+      <c r="B134" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="C134" s="12" t="s">
+        <v>253</v>
       </c>
       <c r="D134" s="8"/>
       <c r="E134" s="8"/>
     </row>
-    <row r="135">
+    <row r="135" customHeight="1" spans="1:5">
       <c r="A135" s="6"/>
-      <c r="B135" s="15" t="s">
-        <v>252</v>
+      <c r="B135" s="6" t="s">
+        <v>254</v>
       </c>
       <c r="C135" s="8"/>
       <c r="D135" s="8"/>
       <c r="E135" s="8"/>
     </row>
-    <row r="136">
+    <row r="136" customHeight="1" spans="1:5">
       <c r="A136" s="6"/>
-      <c r="B136" s="15" t="s">
-        <v>253</v>
+      <c r="B136" s="6" t="s">
+        <v>255</v>
       </c>
       <c r="C136" s="8"/>
       <c r="D136" s="8"/>
       <c r="E136" s="8"/>
     </row>
-    <row r="137">
+    <row r="137" customHeight="1" spans="1:5">
       <c r="A137" s="6"/>
-      <c r="B137" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="C137" s="11" t="s">
-        <v>255</v>
+      <c r="B137" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="C137" s="12" t="s">
+        <v>257</v>
       </c>
       <c r="D137" s="8"/>
       <c r="E137" s="8"/>
     </row>
-    <row r="138">
+    <row r="138" customHeight="1" spans="1:5">
       <c r="A138" s="6"/>
-      <c r="B138" s="22" t="s">
-        <v>256</v>
+      <c r="B138" s="23" t="s">
+        <v>258</v>
       </c>
       <c r="C138" s="8"/>
       <c r="D138" s="8"/>
       <c r="E138" s="8"/>
     </row>
-    <row r="139">
+    <row r="139" customHeight="1" spans="1:5">
       <c r="A139" s="6"/>
-      <c r="B139" s="15" t="s">
-        <v>257</v>
+      <c r="B139" s="6" t="s">
+        <v>259</v>
       </c>
       <c r="C139" s="8"/>
       <c r="D139" s="8"/>
       <c r="E139" s="8"/>
     </row>
-    <row r="140">
+    <row r="140" customHeight="1" spans="1:5">
       <c r="A140" s="6"/>
-      <c r="B140" s="15" t="s">
-        <v>258</v>
+      <c r="B140" s="6" t="s">
+        <v>260</v>
       </c>
       <c r="C140" s="8"/>
       <c r="D140" s="8"/>
       <c r="E140" s="8"/>
     </row>
-    <row r="141">
+    <row r="141" customHeight="1" spans="1:5">
       <c r="A141" s="6"/>
-      <c r="B141" s="15" t="s">
-        <v>259</v>
+      <c r="B141" s="6" t="s">
+        <v>261</v>
       </c>
       <c r="C141" s="8"/>
       <c r="D141" s="8"/>
       <c r="E141" s="8"/>
     </row>
-    <row r="142">
+    <row r="142" customHeight="1" spans="1:5">
       <c r="A142" s="6"/>
-      <c r="B142" s="15" t="s">
-        <v>260</v>
+      <c r="B142" s="6" t="s">
+        <v>262</v>
       </c>
       <c r="C142" s="8"/>
       <c r="D142" s="8"/>
       <c r="E142" s="8"/>
     </row>
-    <row r="143">
+    <row r="143" customHeight="1" spans="1:5">
       <c r="A143" s="6"/>
-      <c r="B143" s="22" t="s">
-        <v>261</v>
+      <c r="B143" s="23" t="s">
+        <v>263</v>
       </c>
       <c r="C143" s="8"/>
       <c r="D143" s="8"/>
       <c r="E143" s="8"/>
     </row>
-    <row r="144">
+    <row r="144" customHeight="1" spans="1:5">
       <c r="A144" s="6"/>
-      <c r="B144" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="C144" s="11" t="s">
-        <v>263</v>
+      <c r="B144" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="C144" s="12" t="s">
+        <v>265</v>
       </c>
       <c r="E144" s="8"/>
     </row>
-    <row r="145">
+    <row r="145" customHeight="1" spans="1:5">
       <c r="A145" s="6"/>
-      <c r="B145" s="15" t="s">
-        <v>264</v>
+      <c r="B145" s="6" t="s">
+        <v>266</v>
       </c>
       <c r="C145" s="8"/>
       <c r="D145" s="8"/>
       <c r="E145" s="8"/>
     </row>
-    <row r="146">
+    <row r="146" customHeight="1" spans="1:5">
       <c r="A146" s="6"/>
-      <c r="B146" s="23" t="s">
-        <v>265</v>
-      </c>
-      <c r="C146" s="11" t="s">
-        <v>266</v>
+      <c r="B146" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="C146" s="12" t="s">
+        <v>268</v>
       </c>
       <c r="D146" s="8"/>
       <c r="E146" s="8"/>
     </row>
-    <row r="147">
+    <row r="147" customHeight="1" spans="1:5">
       <c r="A147" s="6"/>
-      <c r="B147" s="15" t="s">
-        <v>267</v>
+      <c r="B147" s="6" t="s">
+        <v>269</v>
       </c>
       <c r="C147" s="8"/>
       <c r="D147" s="8"/>
       <c r="E147" s="8"/>
     </row>
-    <row r="148">
+    <row r="148" customHeight="1" spans="1:5">
       <c r="A148" s="6"/>
-      <c r="B148" s="15" t="s">
-        <v>268</v>
+      <c r="B148" s="6" t="s">
+        <v>270</v>
       </c>
       <c r="C148" s="8"/>
       <c r="D148" s="8"/>
       <c r="E148" s="8"/>
     </row>
-    <row r="149">
+    <row r="149" customHeight="1" spans="1:5">
       <c r="A149" s="6"/>
-      <c r="B149" s="15" t="s">
-        <v>269</v>
+      <c r="B149" s="6" t="s">
+        <v>271</v>
       </c>
       <c r="C149" s="8"/>
       <c r="D149" s="8"/>
       <c r="E149" s="8"/>
     </row>
-    <row r="150">
+    <row r="150" customHeight="1" spans="1:5">
       <c r="A150" s="6"/>
-      <c r="B150" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="C150" s="11" t="s">
-        <v>271</v>
+      <c r="B150" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="C150" s="12" t="s">
+        <v>273</v>
       </c>
       <c r="D150" s="8"/>
       <c r="E150" s="8"/>
     </row>
-    <row r="151">
+    <row r="151" customHeight="1" spans="1:5">
       <c r="A151" s="6"/>
-      <c r="B151" s="23" t="s">
-        <v>272</v>
+      <c r="B151" s="24" t="s">
+        <v>274</v>
       </c>
       <c r="C151" s="8"/>
       <c r="D151" s="8"/>
       <c r="E151" s="8"/>
     </row>
-    <row r="152">
+    <row r="152" customHeight="1" spans="1:5">
       <c r="A152" s="6"/>
-      <c r="B152" s="15" t="s">
-        <v>273</v>
+      <c r="B152" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="C152" s="8"/>
       <c r="D152" s="8"/>
       <c r="E152" s="8"/>
     </row>
-    <row r="153">
+    <row r="153" customHeight="1" spans="1:5">
       <c r="A153" s="6"/>
-      <c r="B153" s="15" t="s">
-        <v>274</v>
+      <c r="B153" s="6" t="s">
+        <v>276</v>
       </c>
       <c r="C153" s="8"/>
       <c r="D153" s="8"/>
       <c r="E153" s="8"/>
     </row>
-    <row r="154">
+    <row r="154" customHeight="1" spans="1:5">
       <c r="A154" s="6"/>
-      <c r="B154" s="15" t="s">
-        <v>275</v>
+      <c r="B154" s="6" t="s">
+        <v>277</v>
       </c>
       <c r="C154" s="8"/>
       <c r="D154" s="8"/>
       <c r="E154" s="8"/>
     </row>
-    <row r="155">
+    <row r="155" customHeight="1" spans="1:5">
       <c r="A155" s="6"/>
-      <c r="B155" s="15" t="s">
-        <v>276</v>
+      <c r="B155" s="6" t="s">
+        <v>278</v>
       </c>
       <c r="C155" s="8"/>
       <c r="D155" s="8"/>
       <c r="E155" s="8"/>
     </row>
-    <row r="156">
+    <row r="156" customHeight="1" spans="1:5">
       <c r="A156" s="6"/>
-      <c r="B156" s="15" t="s">
-        <v>277</v>
+      <c r="B156" s="6" t="s">
+        <v>279</v>
       </c>
       <c r="C156" s="8"/>
       <c r="D156" s="8"/>
       <c r="E156" s="8"/>
     </row>
-    <row r="157">
+    <row r="157" customHeight="1" spans="1:5">
       <c r="A157" s="6"/>
-      <c r="B157" s="15" t="s">
-        <v>278</v>
+      <c r="B157" s="6" t="s">
+        <v>280</v>
       </c>
       <c r="C157" s="8"/>
       <c r="D157" s="8"/>
       <c r="E157" s="8"/>
     </row>
-    <row r="158">
+    <row r="158" customHeight="1" spans="1:5">
       <c r="A158" s="6"/>
-      <c r="B158" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="C158" s="11" t="s">
-        <v>280</v>
+      <c r="B158" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="C158" s="12" t="s">
+        <v>282</v>
       </c>
       <c r="E158" s="8"/>
     </row>
-    <row r="159">
+    <row r="159" customHeight="1" spans="1:5">
       <c r="A159" s="6"/>
-      <c r="B159" s="22" t="s">
-        <v>281</v>
+      <c r="B159" s="23" t="s">
+        <v>283</v>
       </c>
       <c r="C159" s="8"/>
       <c r="D159" s="8"/>
       <c r="E159" s="8"/>
     </row>
-    <row r="160">
+    <row r="160" customHeight="1" spans="1:5">
       <c r="A160" s="6"/>
-      <c r="B160" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="C160" s="11" t="s">
-        <v>283</v>
+      <c r="B160" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="C160" s="12" t="s">
+        <v>285</v>
       </c>
       <c r="D160" s="8"/>
       <c r="E160" s="8"/>
     </row>
-    <row r="161">
+    <row r="161" customHeight="1" spans="1:5">
       <c r="A161" s="6"/>
-      <c r="B161" s="15" t="s">
-        <v>284</v>
-      </c>
-      <c r="C161" s="11" t="s">
-        <v>285</v>
+      <c r="B161" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="C161" s="12" t="s">
+        <v>287</v>
       </c>
       <c r="D161" s="8"/>
       <c r="E161" s="8"/>
     </row>
-    <row r="162">
+    <row r="162" customHeight="1" spans="1:5">
       <c r="A162" s="6"/>
-      <c r="B162" s="15" t="s">
-        <v>286</v>
-      </c>
-      <c r="C162" s="11" t="s">
-        <v>287</v>
+      <c r="B162" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="C162" s="12" t="s">
+        <v>289</v>
       </c>
       <c r="D162" s="8"/>
       <c r="E162" s="8"/>
     </row>
-    <row r="163">
+    <row r="163" customHeight="1" spans="1:5">
       <c r="A163" s="6"/>
-      <c r="B163" s="15" t="s">
-        <v>288</v>
-      </c>
-      <c r="C163" s="11" t="s">
-        <v>289</v>
+      <c r="B163" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C163" s="12" t="s">
+        <v>291</v>
       </c>
       <c r="D163" s="8"/>
       <c r="E163" s="8"/>
     </row>
-    <row r="164">
+    <row r="164" customHeight="1" spans="1:5">
       <c r="A164" s="6"/>
-      <c r="B164" s="15" t="s">
-        <v>290</v>
+      <c r="B164" s="6" t="s">
+        <v>292</v>
       </c>
       <c r="C164" s="8"/>
       <c r="D164" s="8"/>
       <c r="E164" s="8"/>
     </row>
-    <row r="165">
+    <row r="165" customHeight="1" spans="1:5">
       <c r="A165" s="6"/>
-      <c r="B165" s="22" t="s">
-        <v>291</v>
+      <c r="B165" s="23" t="s">
+        <v>293</v>
       </c>
       <c r="C165" s="8"/>
       <c r="D165" s="8"/>
       <c r="E165" s="8"/>
     </row>
-    <row r="166">
+    <row r="166" customHeight="1" spans="1:5">
       <c r="A166" s="6"/>
-      <c r="B166" s="15" t="s">
-        <v>292</v>
-      </c>
-      <c r="C166" s="11" t="s">
-        <v>293</v>
+      <c r="B166" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="C166" s="12" t="s">
+        <v>295</v>
       </c>
       <c r="D166" s="8"/>
       <c r="E166" s="8"/>
     </row>
-    <row r="167">
+    <row r="167" customHeight="1" spans="1:5">
       <c r="A167" s="6"/>
-      <c r="B167" s="15" t="s">
-        <v>294</v>
-      </c>
-      <c r="C167" s="11" t="s">
-        <v>295</v>
+      <c r="B167" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="C167" s="12" t="s">
+        <v>297</v>
       </c>
       <c r="D167" s="8"/>
       <c r="E167" s="8"/>
     </row>
-    <row r="168">
+    <row r="168" customHeight="1" spans="1:5">
       <c r="A168" s="6"/>
-      <c r="B168" s="15" t="s">
-        <v>296</v>
-      </c>
-      <c r="C168" s="11" t="s">
-        <v>297</v>
+      <c r="B168" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="C168" s="12" t="s">
+        <v>299</v>
       </c>
       <c r="D168" s="8"/>
       <c r="E168" s="8"/>
     </row>
-    <row r="169">
+    <row r="169" customHeight="1" spans="1:5">
       <c r="A169" s="6"/>
-      <c r="B169" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="C169" s="11" t="s">
-        <v>299</v>
+      <c r="B169" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="C169" s="12" t="s">
+        <v>301</v>
       </c>
       <c r="D169" s="8"/>
       <c r="E169" s="8"/>
     </row>
-    <row r="170">
+    <row r="170" customHeight="1" spans="1:5">
       <c r="A170" s="6"/>
-      <c r="B170" s="15" t="s">
-        <v>300</v>
-      </c>
-      <c r="C170" s="11" t="s">
-        <v>301</v>
+      <c r="B170" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C170" s="12" t="s">
+        <v>303</v>
       </c>
       <c r="D170" s="8"/>
       <c r="E170" s="8"/>
     </row>
-    <row r="171">
+    <row r="171" customHeight="1" spans="1:5">
       <c r="A171" s="6"/>
-      <c r="B171" s="15" t="s">
-        <v>302</v>
-      </c>
-      <c r="C171" s="11" t="s">
-        <v>303</v>
+      <c r="B171" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="C171" s="12" t="s">
+        <v>305</v>
       </c>
       <c r="D171" s="8"/>
       <c r="E171" s="8"/>
     </row>
-    <row r="172">
+    <row r="172" customHeight="1" spans="1:5">
       <c r="A172" s="6"/>
-      <c r="B172" s="22" t="s">
-        <v>304</v>
+      <c r="B172" s="23" t="s">
+        <v>306</v>
       </c>
       <c r="C172" s="8"/>
       <c r="D172" s="8"/>
       <c r="E172" s="8"/>
     </row>
-    <row r="173">
+    <row r="173" customHeight="1" spans="1:5">
       <c r="A173" s="6"/>
-      <c r="B173" s="15" t="s">
-        <v>305</v>
-      </c>
-      <c r="C173" s="11" t="s">
-        <v>306</v>
+      <c r="B173" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="C173" s="12" t="s">
+        <v>308</v>
       </c>
       <c r="D173" s="8"/>
       <c r="E173" s="8"/>
     </row>
-    <row r="174">
+    <row r="174" customHeight="1" spans="1:5">
       <c r="A174" s="6"/>
-      <c r="B174" s="15" t="s">
-        <v>307</v>
-      </c>
-      <c r="C174" s="11" t="s">
-        <v>308</v>
+      <c r="B174" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C174" s="12" t="s">
+        <v>310</v>
       </c>
       <c r="D174" s="8"/>
       <c r="E174" s="8"/>
     </row>
-    <row r="175">
+    <row r="175" customHeight="1" spans="1:5">
       <c r="A175" s="6"/>
-      <c r="B175" s="15" t="s">
-        <v>309</v>
-      </c>
-      <c r="C175" s="11" t="s">
-        <v>310</v>
+      <c r="B175" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="C175" s="12" t="s">
+        <v>312</v>
       </c>
       <c r="D175" s="8"/>
       <c r="E175" s="8"/>
     </row>
-    <row r="176">
+    <row r="176" customHeight="1" spans="1:5">
       <c r="A176" s="6"/>
-      <c r="B176" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="C176" s="11" t="s">
-        <v>312</v>
+      <c r="B176" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="C176" s="12" t="s">
+        <v>314</v>
       </c>
       <c r="E176" s="8"/>
     </row>
-    <row r="177">
+    <row r="177" customHeight="1" spans="1:5">
       <c r="A177" s="6"/>
-      <c r="B177" s="15" t="s">
-        <v>313</v>
+      <c r="B177" s="6" t="s">
+        <v>315</v>
       </c>
       <c r="C177" s="8"/>
       <c r="D177" s="8"/>
       <c r="E177" s="8"/>
     </row>
-    <row r="178">
+    <row r="178" customHeight="1" spans="1:5">
       <c r="A178" s="6"/>
-      <c r="B178" s="15" t="s">
-        <v>314</v>
+      <c r="B178" s="6" t="s">
+        <v>316</v>
       </c>
       <c r="C178" s="8"/>
       <c r="D178" s="8"/>
       <c r="E178" s="8"/>
     </row>
-    <row r="179">
+    <row r="179" customHeight="1" spans="1:5">
       <c r="A179" s="6"/>
-      <c r="B179" s="22" t="s">
-        <v>315</v>
+      <c r="B179" s="23" t="s">
+        <v>317</v>
       </c>
       <c r="C179" s="8"/>
       <c r="D179" s="8"/>
       <c r="E179" s="8"/>
     </row>
-    <row r="180">
+    <row r="180" customHeight="1" spans="1:5">
       <c r="A180" s="6"/>
-      <c r="B180" s="15" t="s">
-        <v>316</v>
-      </c>
-      <c r="C180" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="D180" s="11" t="s">
+      <c r="B180" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="E180" s="11" t="s">
+      <c r="C180" s="12" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="181">
+      <c r="D180" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="E180" s="12" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="181" customHeight="1" spans="1:5">
       <c r="A181" s="6"/>
-      <c r="B181" s="15" t="s">
-        <v>320</v>
-      </c>
-      <c r="C181" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="D181" s="11" t="s">
+      <c r="B181" s="6" t="s">
         <v>322</v>
       </c>
+      <c r="C181" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D181" s="12" t="s">
+        <v>324</v>
+      </c>
       <c r="E181" s="8"/>
     </row>
-    <row r="182">
+    <row r="182" customHeight="1" spans="1:5">
       <c r="A182" s="6"/>
-      <c r="B182" s="15" t="s">
-        <v>323</v>
-      </c>
-      <c r="C182" s="11" t="s">
-        <v>324</v>
+      <c r="B182" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="C182" s="12" t="s">
+        <v>326</v>
       </c>
       <c r="D182" s="8"/>
       <c r="E182" s="8"/>
     </row>
-    <row r="183">
+    <row r="183" customHeight="1" spans="1:5">
       <c r="A183" s="6"/>
-      <c r="B183" s="15" t="s">
-        <v>325</v>
-      </c>
-      <c r="C183" s="11" t="s">
-        <v>326</v>
+      <c r="B183" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C183" s="12" t="s">
+        <v>328</v>
       </c>
       <c r="D183" s="8"/>
       <c r="E183" s="8"/>
     </row>
-    <row r="184">
+    <row r="184" customHeight="1" spans="1:5">
       <c r="A184" s="6"/>
-      <c r="B184" s="15" t="s">
-        <v>327</v>
-      </c>
-      <c r="C184" s="11" t="s">
-        <v>328</v>
+      <c r="B184" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="C184" s="12" t="s">
+        <v>330</v>
       </c>
       <c r="D184" s="8"/>
       <c r="E184" s="8"/>
     </row>
-    <row r="185">
+    <row r="185" customHeight="1" spans="1:5">
       <c r="A185" s="6"/>
-      <c r="B185" s="22" t="s">
-        <v>329</v>
+      <c r="B185" s="23" t="s">
+        <v>331</v>
       </c>
       <c r="C185" s="8"/>
       <c r="D185" s="8"/>
       <c r="E185" s="8"/>
     </row>
-    <row r="186">
+    <row r="186" customHeight="1" spans="1:5">
       <c r="A186" s="6"/>
-      <c r="B186" s="15" t="s">
-        <v>330</v>
-      </c>
-      <c r="C186" s="11" t="s">
-        <v>331</v>
+      <c r="B186" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="C186" s="12" t="s">
+        <v>333</v>
       </c>
       <c r="D186" s="8"/>
       <c r="E186" s="8"/>
     </row>
-    <row r="187">
+    <row r="187" customHeight="1" spans="1:5">
       <c r="A187" s="6"/>
-      <c r="B187" s="15" t="s">
-        <v>332</v>
-      </c>
-      <c r="C187" s="11" t="s">
-        <v>333</v>
+      <c r="B187" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="C187" s="12" t="s">
+        <v>335</v>
       </c>
       <c r="D187" s="8"/>
       <c r="E187" s="8"/>
     </row>
-    <row r="188">
+    <row r="188" customHeight="1" spans="1:5">
       <c r="A188" s="6"/>
-      <c r="B188" s="15" t="s">
-        <v>334</v>
-      </c>
-      <c r="C188" s="11" t="s">
-        <v>335</v>
+      <c r="B188" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="C188" s="12" t="s">
+        <v>337</v>
       </c>
       <c r="D188" s="8"/>
       <c r="E188" s="8"/>
     </row>
-    <row r="189">
+    <row r="189" customHeight="1" spans="1:5">
       <c r="A189" s="6"/>
-      <c r="B189" s="15" t="s">
-        <v>336</v>
-      </c>
-      <c r="C189" s="11" t="s">
-        <v>337</v>
+      <c r="B189" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="C189" s="12" t="s">
+        <v>339</v>
       </c>
       <c r="D189" s="8"/>
       <c r="E189" s="8"/>
     </row>
-    <row r="190">
+    <row r="190" customHeight="1" spans="1:5">
       <c r="A190" s="6"/>
-      <c r="B190" s="15" t="s">
-        <v>338</v>
-      </c>
-      <c r="C190" s="11" t="s">
-        <v>339</v>
+      <c r="B190" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="C190" s="12" t="s">
+        <v>341</v>
       </c>
       <c r="D190" s="8"/>
       <c r="E190" s="8"/>
     </row>
-    <row r="191">
+    <row r="191" customHeight="1" spans="1:5">
       <c r="A191" s="6"/>
-      <c r="B191" s="22" t="s">
-        <v>340</v>
+      <c r="B191" s="23" t="s">
+        <v>342</v>
       </c>
       <c r="C191" s="8"/>
       <c r="D191" s="8"/>
       <c r="E191" s="8"/>
     </row>
-    <row r="192">
+    <row r="192" customHeight="1" spans="1:5">
       <c r="A192" s="6"/>
-      <c r="B192" s="15" t="s">
-        <v>341</v>
-      </c>
-      <c r="C192" s="11" t="s">
-        <v>342</v>
+      <c r="B192" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="C192" s="12" t="s">
+        <v>344</v>
       </c>
       <c r="D192" s="8"/>
       <c r="E192" s="8"/>
     </row>
-    <row r="193">
+    <row r="193" customHeight="1" spans="1:5">
       <c r="A193" s="6"/>
-      <c r="B193" s="15" t="s">
-        <v>343</v>
-      </c>
-      <c r="C193" s="11" t="s">
-        <v>344</v>
+      <c r="B193" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="C193" s="12" t="s">
+        <v>346</v>
       </c>
       <c r="D193" s="8"/>
       <c r="E193" s="8"/>
     </row>
-    <row r="194">
+    <row r="194" customHeight="1" spans="1:5">
       <c r="A194" s="6"/>
-      <c r="B194" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="C194" s="11" t="s">
+      <c r="B194" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="C194" s="12" t="s">
         <v>346</v>
       </c>
       <c r="D194" s="8"/>
       <c r="E194" s="8"/>
     </row>
-    <row r="195">
+    <row r="195" customHeight="1" spans="1:5">
       <c r="A195" s="6"/>
-      <c r="B195" s="15" t="s">
-        <v>347</v>
-      </c>
-      <c r="C195" s="11" t="s">
+      <c r="B195" s="6" t="s">
         <v>348</v>
+      </c>
+      <c r="C195" s="12" t="s">
+        <v>349</v>
       </c>
       <c r="D195" s="8"/>
       <c r="E195" s="8"/>
     </row>
-    <row r="196">
+    <row r="196" customHeight="1" spans="1:5">
       <c r="A196" s="6"/>
-      <c r="B196" s="15" t="s">
-        <v>349</v>
-      </c>
-      <c r="C196" s="11" t="s">
+      <c r="B196" s="6" t="s">
         <v>350</v>
+      </c>
+      <c r="C196" s="12" t="s">
+        <v>351</v>
       </c>
       <c r="D196" s="8"/>
       <c r="E196" s="8"/>
     </row>
-    <row r="197">
+    <row r="197" customHeight="1" spans="1:5">
       <c r="A197" s="6"/>
-      <c r="B197" s="15" t="s">
-        <v>351</v>
-      </c>
-      <c r="C197" s="11" t="s">
+      <c r="B197" s="6" t="s">
         <v>352</v>
+      </c>
+      <c r="C197" s="12" t="s">
+        <v>353</v>
       </c>
       <c r="D197" s="8"/>
       <c r="E197" s="8"/>
     </row>
-    <row r="198">
+    <row r="198" customHeight="1" spans="1:5">
       <c r="A198" s="6"/>
-      <c r="B198" s="15" t="s">
-        <v>353</v>
-      </c>
-      <c r="C198" s="11" t="s">
+      <c r="B198" s="6" t="s">
         <v>354</v>
+      </c>
+      <c r="C198" s="12" t="s">
+        <v>355</v>
       </c>
       <c r="D198" s="8"/>
       <c r="E198" s="8"/>
     </row>
-    <row r="199">
+    <row r="199" customHeight="1" spans="1:5">
       <c r="A199" s="6"/>
-      <c r="B199" s="22" t="s">
-        <v>355</v>
+      <c r="B199" s="23" t="s">
+        <v>356</v>
       </c>
       <c r="C199" s="8"/>
       <c r="D199" s="8"/>
       <c r="E199" s="8"/>
     </row>
-    <row r="200">
+    <row r="200" customHeight="1" spans="1:5">
       <c r="A200" s="6"/>
-      <c r="B200" s="15" t="s">
-        <v>356</v>
-      </c>
-      <c r="C200" s="11" t="s">
+      <c r="B200" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="D200" s="11" t="s">
+      <c r="C200" s="12" t="s">
         <v>358</v>
       </c>
+      <c r="D200" s="12" t="s">
+        <v>359</v>
+      </c>
       <c r="E200" s="8"/>
     </row>
-    <row r="201">
+    <row r="201" customHeight="1" spans="1:5">
       <c r="A201" s="6"/>
-      <c r="B201" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="C201" s="11" t="s">
-        <v>359</v>
+      <c r="B201" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C201" s="12" t="s">
+        <v>224</v>
       </c>
       <c r="D201" s="8"/>
       <c r="E201" s="8"/>
     </row>
-    <row r="202">
+    <row r="202" customHeight="1" spans="1:5">
       <c r="A202" s="6"/>
-      <c r="B202" s="15" t="s">
+      <c r="B202" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="C202" s="11" t="s">
+      <c r="C202" s="12" t="s">
         <v>361</v>
       </c>
       <c r="D202" s="8"/>
       <c r="E202" s="8"/>
     </row>
-    <row r="203">
+    <row r="203" customHeight="1" spans="1:5">
       <c r="A203" s="6"/>
-      <c r="B203" s="15" t="s">
+      <c r="B203" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="C203" s="11" t="s">
+      <c r="C203" s="12" t="s">
         <v>363</v>
       </c>
       <c r="D203" s="8"/>
       <c r="E203" s="8"/>
     </row>
-    <row r="204">
+    <row r="204" customHeight="1" spans="1:5">
       <c r="A204" s="6"/>
-      <c r="B204" s="22" t="s">
+      <c r="B204" s="23" t="s">
         <v>364</v>
       </c>
       <c r="C204" s="8"/>
       <c r="D204" s="8"/>
       <c r="E204" s="8"/>
     </row>
-    <row r="205">
+    <row r="205" customHeight="1" spans="1:5">
       <c r="A205" s="6"/>
-      <c r="B205" s="15" t="s">
+      <c r="B205" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="C205" s="11" t="s">
+      <c r="C205" s="12" t="s">
         <v>366</v>
       </c>
       <c r="D205" s="8"/>
       <c r="E205" s="8"/>
     </row>
-    <row r="206">
+    <row r="206" customHeight="1" spans="1:5">
       <c r="A206" s="6"/>
-      <c r="B206" s="15" t="s">
+      <c r="B206" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="C206" s="11" t="s">
+      <c r="C206" s="12" t="s">
         <v>368</v>
       </c>
       <c r="D206" s="8"/>
       <c r="E206" s="8"/>
     </row>
-    <row r="207">
+    <row r="207" customHeight="1" spans="1:5">
       <c r="A207" s="6"/>
-      <c r="B207" s="15" t="s">
+      <c r="B207" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="C207" s="11" t="s">
+      <c r="C207" s="12" t="s">
         <v>370</v>
       </c>
-      <c r="D207" s="11" t="s">
+      <c r="D207" s="12" t="s">
         <v>371</v>
       </c>
-      <c r="E207" s="11" t="s">
+      <c r="E207" s="12" t="s">
         <v>372</v>
       </c>
     </row>
@@ -4630,173 +5570,174 @@
     <mergeCell ref="C176:D176"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="A1"/>
-    <hyperlink r:id="rId2" ref="C4"/>
-    <hyperlink r:id="rId3" ref="C5"/>
-    <hyperlink r:id="rId4" ref="C6"/>
-    <hyperlink r:id="rId5" ref="D6"/>
-    <hyperlink r:id="rId6" ref="E6"/>
-    <hyperlink r:id="rId7" ref="C7"/>
-    <hyperlink r:id="rId8" ref="C8"/>
-    <hyperlink r:id="rId9" ref="C9"/>
-    <hyperlink r:id="rId10" ref="C10"/>
-    <hyperlink r:id="rId11" ref="C11"/>
-    <hyperlink r:id="rId12" ref="C12"/>
-    <hyperlink r:id="rId13" ref="C13"/>
-    <hyperlink r:id="rId14" ref="C14"/>
-    <hyperlink r:id="rId15" ref="C15"/>
-    <hyperlink r:id="rId16" ref="D15"/>
-    <hyperlink r:id="rId17" ref="C17"/>
-    <hyperlink r:id="rId18" ref="C18"/>
-    <hyperlink r:id="rId19" ref="C19"/>
-    <hyperlink r:id="rId20" ref="C20"/>
-    <hyperlink r:id="rId21" ref="C21"/>
-    <hyperlink r:id="rId22" ref="C22"/>
-    <hyperlink r:id="rId23" ref="C23"/>
-    <hyperlink r:id="rId24" ref="C24"/>
-    <hyperlink r:id="rId25" ref="C26"/>
-    <hyperlink r:id="rId26" ref="C27"/>
-    <hyperlink r:id="rId27" ref="C28"/>
-    <hyperlink r:id="rId28" ref="C29"/>
-    <hyperlink r:id="rId29" ref="C30"/>
-    <hyperlink r:id="rId30" ref="C31"/>
-    <hyperlink r:id="rId31" ref="C32"/>
-    <hyperlink r:id="rId32" ref="C33"/>
-    <hyperlink r:id="rId33" ref="C34"/>
-    <hyperlink r:id="rId34" ref="C35"/>
-    <hyperlink r:id="rId35" ref="C36"/>
-    <hyperlink r:id="rId36" ref="C37"/>
-    <hyperlink r:id="rId37" ref="C39"/>
-    <hyperlink r:id="rId38" ref="C40"/>
-    <hyperlink r:id="rId39" ref="C41"/>
-    <hyperlink r:id="rId40" ref="C42"/>
-    <hyperlink r:id="rId41" ref="C43"/>
-    <hyperlink r:id="rId42" ref="C44"/>
-    <hyperlink r:id="rId43" ref="C46"/>
-    <hyperlink r:id="rId44" ref="C47"/>
-    <hyperlink r:id="rId45" ref="C48"/>
-    <hyperlink r:id="rId46" ref="C49"/>
-    <hyperlink r:id="rId47" ref="C50"/>
-    <hyperlink r:id="rId48" ref="C51"/>
-    <hyperlink r:id="rId49" ref="C53"/>
-    <hyperlink r:id="rId50" ref="C54"/>
-    <hyperlink r:id="rId51" ref="C55"/>
-    <hyperlink r:id="rId52" ref="C56"/>
-    <hyperlink r:id="rId53" ref="C57"/>
-    <hyperlink r:id="rId54" ref="C58"/>
-    <hyperlink r:id="rId55" ref="C59"/>
-    <hyperlink r:id="rId56" ref="C61"/>
-    <hyperlink r:id="rId57" ref="C62"/>
-    <hyperlink r:id="rId58" ref="C63"/>
-    <hyperlink r:id="rId59" ref="C64"/>
-    <hyperlink r:id="rId60" ref="C65"/>
-    <hyperlink r:id="rId61" ref="C66"/>
-    <hyperlink r:id="rId62" ref="C67"/>
-    <hyperlink r:id="rId63" ref="C68"/>
-    <hyperlink r:id="rId64" ref="C70"/>
-    <hyperlink r:id="rId65" ref="C71"/>
-    <hyperlink r:id="rId66" ref="C72"/>
-    <hyperlink r:id="rId67" ref="C73"/>
-    <hyperlink r:id="rId68" ref="C74"/>
-    <hyperlink r:id="rId69" ref="C75"/>
-    <hyperlink r:id="rId70" ref="B77"/>
-    <hyperlink r:id="rId71" ref="C77"/>
-    <hyperlink r:id="rId72" ref="C78"/>
-    <hyperlink r:id="rId73" ref="C80"/>
-    <hyperlink r:id="rId74" ref="C81"/>
-    <hyperlink r:id="rId75" ref="C82"/>
-    <hyperlink r:id="rId76" ref="C83"/>
-    <hyperlink r:id="rId77" ref="C84"/>
-    <hyperlink r:id="rId78" ref="C85"/>
-    <hyperlink r:id="rId79" ref="C87"/>
-    <hyperlink r:id="rId80" ref="C88"/>
-    <hyperlink r:id="rId81" ref="C89"/>
-    <hyperlink r:id="rId82" ref="C90"/>
-    <hyperlink r:id="rId83" ref="C92"/>
-    <hyperlink r:id="rId84" ref="C93"/>
-    <hyperlink r:id="rId85" ref="C94"/>
-    <hyperlink r:id="rId86" ref="C95"/>
-    <hyperlink r:id="rId87" ref="C96"/>
-    <hyperlink r:id="rId88" ref="C97"/>
-    <hyperlink r:id="rId89" ref="C98"/>
-    <hyperlink r:id="rId90" ref="C99"/>
-    <hyperlink r:id="rId91" ref="C100"/>
-    <hyperlink r:id="rId92" ref="C101"/>
-    <hyperlink r:id="rId93" ref="C102"/>
-    <hyperlink r:id="rId94" ref="C103"/>
-    <hyperlink r:id="rId95" ref="C104"/>
-    <hyperlink r:id="rId96" ref="C105"/>
-    <hyperlink r:id="rId97" ref="C106"/>
-    <hyperlink r:id="rId98" ref="C107"/>
-    <hyperlink r:id="rId99" ref="C108"/>
-    <hyperlink r:id="rId100" ref="C109"/>
-    <hyperlink r:id="rId101" ref="C110"/>
-    <hyperlink r:id="rId102" ref="C111"/>
-    <hyperlink r:id="rId103" ref="C112"/>
-    <hyperlink r:id="rId104" ref="C113"/>
-    <hyperlink r:id="rId105" ref="C115"/>
-    <hyperlink r:id="rId106" ref="C116"/>
-    <hyperlink r:id="rId107" ref="C117"/>
-    <hyperlink r:id="rId108" ref="C119"/>
-    <hyperlink r:id="rId109" ref="C121"/>
-    <hyperlink r:id="rId110" ref="C122"/>
-    <hyperlink r:id="rId111" ref="C127"/>
-    <hyperlink r:id="rId112" ref="C128"/>
-    <hyperlink r:id="rId113" ref="C129"/>
-    <hyperlink r:id="rId114" ref="C130"/>
-    <hyperlink r:id="rId115" ref="C132"/>
-    <hyperlink r:id="rId116" ref="C133"/>
-    <hyperlink r:id="rId117" ref="C134"/>
-    <hyperlink r:id="rId118" ref="C137"/>
-    <hyperlink r:id="rId119" ref="C144"/>
-    <hyperlink r:id="rId120" ref="C146"/>
-    <hyperlink r:id="rId121" ref="C150"/>
-    <hyperlink r:id="rId122" ref="C158"/>
-    <hyperlink r:id="rId123" ref="C160"/>
-    <hyperlink r:id="rId124" ref="C161"/>
-    <hyperlink r:id="rId125" ref="C162"/>
-    <hyperlink r:id="rId126" ref="C163"/>
-    <hyperlink r:id="rId127" ref="C166"/>
-    <hyperlink r:id="rId128" ref="C167"/>
-    <hyperlink r:id="rId129" ref="C168"/>
-    <hyperlink r:id="rId130" ref="C169"/>
-    <hyperlink r:id="rId131" ref="C170"/>
-    <hyperlink r:id="rId132" ref="C171"/>
-    <hyperlink r:id="rId133" ref="C173"/>
-    <hyperlink r:id="rId134" ref="C174"/>
-    <hyperlink r:id="rId135" ref="C175"/>
-    <hyperlink r:id="rId136" ref="C176"/>
-    <hyperlink r:id="rId137" ref="C180"/>
-    <hyperlink r:id="rId138" ref="D180"/>
-    <hyperlink r:id="rId139" ref="E180"/>
-    <hyperlink r:id="rId140" ref="C181"/>
-    <hyperlink r:id="rId141" ref="D181"/>
-    <hyperlink r:id="rId142" ref="C182"/>
-    <hyperlink r:id="rId143" ref="C183"/>
-    <hyperlink r:id="rId144" ref="C184"/>
-    <hyperlink r:id="rId145" ref="C186"/>
-    <hyperlink r:id="rId146" ref="C187"/>
-    <hyperlink r:id="rId147" ref="C188"/>
-    <hyperlink r:id="rId148" ref="C189"/>
-    <hyperlink r:id="rId149" ref="C190"/>
-    <hyperlink r:id="rId150" ref="C192"/>
-    <hyperlink r:id="rId151" ref="C193"/>
-    <hyperlink r:id="rId152" ref="C194"/>
-    <hyperlink r:id="rId153" ref="C195"/>
-    <hyperlink r:id="rId154" ref="C196"/>
-    <hyperlink r:id="rId155" ref="C197"/>
-    <hyperlink r:id="rId156" ref="C198"/>
-    <hyperlink r:id="rId157" ref="C200"/>
-    <hyperlink r:id="rId158" ref="D200"/>
-    <hyperlink r:id="rId159" ref="C201"/>
-    <hyperlink r:id="rId160" ref="C202"/>
-    <hyperlink r:id="rId161" ref="C203"/>
-    <hyperlink r:id="rId162" ref="C205"/>
-    <hyperlink r:id="rId163" ref="C206"/>
-    <hyperlink r:id="rId164" ref="C207"/>
-    <hyperlink r:id="rId165" ref="D207"/>
-    <hyperlink r:id="rId166" ref="E207"/>
+    <hyperlink ref="A1" r:id="rId1" display="INSTA Channel. One question Daily"/>
+    <hyperlink ref="C4" r:id="rId2" display="https://leetcode.com/problems/two-sum-ii-input-array-is-sorted/description/"/>
+    <hyperlink ref="C5" r:id="rId3" display="https://www.geeksforgeeks.org/problems/segregate-0s-and-1s5106/1"/>
+    <hyperlink ref="C6" r:id="rId4" display="https://leetcode.com/problems/remove-duplicates-from-sorted-list/"/>
+    <hyperlink ref="D6" r:id="rId5" display="https://leetcode.com/problems/remove-duplicates-from-sorted-array/description/"/>
+    <hyperlink ref="E6" r:id="rId6" display="https://leetcode.com/problems/remove-duplicates-from-sorted-array-ii/"/>
+    <hyperlink ref="C7" r:id="rId7" display="https://leetcode.com/problems/squares-of-a-sorted-array/"/>
+    <hyperlink ref="C8" r:id="rId8" display="https://leetcode.com/problems/3sum/"/>
+    <hyperlink ref="C9" r:id="rId9" display="https://leetcode.com/problems/3sum-closest/"/>
+    <hyperlink ref="C10" r:id="rId10" display="https://www.geeksforgeeks.org/problems/count-triplets-with-sum-smaller-than-x5549/1"/>
+    <hyperlink ref="C11" r:id="rId11" display="https://leetcode.com/problems/subarray-product-less-than-k/"/>
+    <hyperlink ref="C12" r:id="rId12" display="https://leetcode.com/problems/sort-colors/description/"/>
+    <hyperlink ref="C13" r:id="rId13" display="https://leetcode.com/problems/4sum/"/>
+    <hyperlink ref="C14" r:id="rId14" display="https://leetcode.com/problems/backspace-string-compare/"/>
+    <hyperlink ref="C15" r:id="rId15" display="https://leetcode.com/problems/shortest-unsorted-continuous-subarray/"/>
+    <hyperlink ref="D15" r:id="rId16" display="https://www.ideserve.co.in/learn/minimum-length-subarray-sorting-which-results-in-sorted-array"/>
+    <hyperlink ref="C17" r:id="rId17" display="https://leetcode.com/problems/linked-list-cycle/"/>
+    <hyperlink ref="C18" r:id="rId18" display="https://leetcode.com/problems/linked-list-cycle-ii/"/>
+    <hyperlink ref="C19" r:id="rId19" display="https://leetcode.com/problems/happy-number/"/>
+    <hyperlink ref="C20" r:id="rId20" display="https://leetcode.com/problems/find-the-duplicate-number/description/"/>
+    <hyperlink ref="C21" r:id="rId21" display="https://leetcode.com/problems/middle-of-the-linked-list/"/>
+    <hyperlink ref="C22" r:id="rId22" display="https://leetcode.com/problems/palindrome-linked-list/"/>
+    <hyperlink ref="C23" r:id="rId23" display="https://leetcode.com/problems/reorder-list/"/>
+    <hyperlink ref="C24" r:id="rId24" display="https://leetcode.com/problems/circular-array-loop/"/>
+    <hyperlink ref="C26" r:id="rId25" display="https://www.geeksforgeeks.org/problems/max-sum-subarray-of-size-k5313/1"/>
+    <hyperlink ref="C27" r:id="rId26" display="https://leetcode.com/problems/minimum-size-subarray-sum/"/>
+    <hyperlink ref="C28" r:id="rId27" display="https://www.geeksforgeeks.org/problems/longest-k-unique-characters-substring0853/1"/>
+    <hyperlink ref="C29" r:id="rId28" display="https://leetcode.com/problems/fruit-into-baskets/"/>
+    <hyperlink ref="C30" r:id="rId29" display="https://leetcode.com/problems/longest-substring-without-repeating-characters/"/>
+    <hyperlink ref="C31" r:id="rId30" display="https://leetcode.com/problems/longest-repeating-character-replacement/"/>
+    <hyperlink ref="C32" r:id="rId31" display="https://leetcode.com/problems/max-consecutive-ones-iii/"/>
+    <hyperlink ref="C33" r:id="rId26" display="https://leetcode.com/problems/minimum-size-subarray-sum/"/>
+    <hyperlink ref="C34" r:id="rId32" display="https://leetcode.com/problems/minimum-window-substring/description/?envType=study-plan-v2&amp;envId=top-interview-150"/>
+    <hyperlink ref="C35" r:id="rId33" display="https://leetcode.com/problems/permutation-in-string/"/>
+    <hyperlink ref="C36" r:id="rId34" display="https://leetcode.com/problems/find-all-anagrams-in-a-string/"/>
+    <hyperlink ref="C37" r:id="rId35" display="https://leetcode.com/problems/substring-with-concatenation-of-all-words/"/>
+    <hyperlink ref="C39" r:id="rId36" display="https://leetcode.com/problems/maximum-subarray/?utm_source=chatgpt.com"/>
+    <hyperlink ref="C40" r:id="rId37" display="https://www.geeksforgeeks.org/problems/smallest-sum-contiguous-subarray/1"/>
+    <hyperlink ref="C41" r:id="rId38" display="https://leetcode.com/problems/maximum-product-subarray/?utm_source=chatgpt.com"/>
+    <hyperlink ref="C42" r:id="rId39" display="https://leetcode.com/problems/maximum-subarray-sum-with-one-deletion/description/"/>
+    <hyperlink ref="C43" r:id="rId40" display="https://leetcode.com/problems/maximum-absolute-sum-of-any-subarray/"/>
+    <hyperlink ref="C44" r:id="rId41" display="https://leetcode.com/problems/maximum-sum-circular-subarray/?utm_source=chatgpt.com"/>
+    <hyperlink ref="C46" r:id="rId42" display="https://leetcode.com/problems/subarray-sum-equals-k/description/"/>
+    <hyperlink ref="C47" r:id="rId43" display="https://leetcode.com/problems/find-pivot-index/description/"/>
+    <hyperlink ref="C48" r:id="rId44" display="https://leetcode.com/problems/subarray-sums-divisible-by-k/description/"/>
+    <hyperlink ref="C49" r:id="rId45" display="https://leetcode.com/problems/contiguous-array/description/"/>
+    <hyperlink ref="C50" r:id="rId46" display="https://leetcode.com/problems/shortest-subarray-with-sum-at-least-k/description/"/>
+    <hyperlink ref="C51" r:id="rId47" display="https://leetcode.com/problems/count-of-range-sum/description/"/>
+    <hyperlink ref="C53" r:id="rId48" display="https://leetcode.com/problems/merge-intervals/description/"/>
+    <hyperlink ref="C54" r:id="rId49" display="https://leetcode.com/problems/insert-interval/"/>
+    <hyperlink ref="C55" r:id="rId50" display="https://leetcode.com/problems/interval-list-intersections/description/"/>
+    <hyperlink ref="C56" r:id="rId51" display="https://www.geeksforgeeks.org/check-if-any-two-intervals-overlap-among-a-given-set-of-intervals/"/>
+    <hyperlink ref="C57" r:id="rId52" display="https://www.geeksforgeeks.org/problems/attend-all-meetings-ii/1"/>
+    <hyperlink ref="C58" r:id="rId53" display="https://www.geeksforgeeks.org/maximum-cpu-load-from-the-given-list-of-jobs/"/>
+    <hyperlink ref="C59" r:id="rId54" display="https://www.codertrain.co/employee-free-time"/>
+    <hyperlink ref="C61" r:id="rId55" display="https://www.geeksforgeeks.org/sort-an-array-which-contain-1-to-n-values-in-on-using-cycle-sort/"/>
+    <hyperlink ref="C62" r:id="rId56" display="https://leetcode.com/problems/missing-number/"/>
+    <hyperlink ref="C63" r:id="rId57" display="https://leetcode.com/problems/find-all-numbers-disappeared-in-an-array/"/>
+    <hyperlink ref="C64" r:id="rId58" display="https://leetcode.com/problems/find-the-duplicate-number/"/>
+    <hyperlink ref="C65" r:id="rId59" display="https://leetcode.com/problems/find-all-duplicates-in-an-array/"/>
+    <hyperlink ref="C66" r:id="rId60" display="https://thecodingsimplified.com/find-currupt-pair/"/>
+    <hyperlink ref="C67" r:id="rId61" display="https://leetcode.com/problems/first-missing-positive/"/>
+    <hyperlink ref="C68" r:id="rId62" display="https://thecodingsimplified.com/find-the-first-k-missing-positive-number/"/>
+    <hyperlink ref="C70" r:id="rId63" display="https://leetcode.com/problems/reverse-linked-list/"/>
+    <hyperlink ref="C71" r:id="rId64" display="https://leetcode.com/problems/reverse-linked-list-ii/"/>
+    <hyperlink ref="C72" r:id="rId65" display="https://leetcode.com/problems/swap-nodes-in-pairs/description/"/>
+    <hyperlink ref="C73" r:id="rId66" display="https://leetcode.com/problems/reverse-nodes-in-k-group/"/>
+    <hyperlink ref="C74" r:id="rId67" display="https://leetcode.com/problems/reverse-nodes-in-even-length-groups/description/"/>
+    <hyperlink ref="C75" r:id="rId68" display="https://leetcode.com/problems/rotate-list/"/>
+    <hyperlink ref="B77" r:id="rId69" display="remove adjacent duplicates"/>
+    <hyperlink ref="C77" r:id="rId69" display="https://leetcode.com/problems/remove-all-adjacent-duplicates-in-string/description/"/>
+    <hyperlink ref="C78" r:id="rId70" display="https://leetcode.com/problems/valid-parentheses/description/"/>
+    <hyperlink ref="C80" r:id="rId71" display="https://leetcode.com/problems/next-greater-element-ii/description/"/>
+    <hyperlink ref="C81" r:id="rId72" display="https://leetcode.com/problems/daily-temperatures/"/>
+    <hyperlink ref="C82" r:id="rId73" display="https://leetcode.com/problems/remove-nodes-from-linked-list/"/>
+    <hyperlink ref="C83" r:id="rId74" display="https://leetcode.com/problems/remove-all-adjacent-duplicates-in-string-ii/"/>
+    <hyperlink ref="C84" r:id="rId75" display="https://leetcode.com/problems/simplify-path/"/>
+    <hyperlink ref="C85" r:id="rId76" display="https://leetcode.com/problems/remove-k-digits/"/>
+    <hyperlink ref="C87" r:id="rId77" display="https://leetcode.com/problems/first-unique-character-in-a-string/"/>
+    <hyperlink ref="C88" r:id="rId78" display="https://leetcode.com/problems/maximum-number-of-balloons/"/>
+    <hyperlink ref="C89" r:id="rId79" display="https://leetcode.com/problems/longest-palindrome/"/>
+    <hyperlink ref="C90" r:id="rId80" display="https://leetcode.com/problems/ransom-note/"/>
+    <hyperlink ref="C92" r:id="rId81" display="https://leetcode.com/problems/binary-search/"/>
+    <hyperlink ref="C93" r:id="rId82" display="https://www.geeksforgeeks.org/problems/ceil-in-a-sorted-array/1"/>
+    <hyperlink ref="C94" r:id="rId83" display="https://leetcode.com/problems/find-first-and-last-position-of-element-in-sorted-array/"/>
+    <hyperlink ref="C95" r:id="rId84" display="https://www.geeksforgeeks.org/problems/number-of-occurrence2259/1"/>
+    <hyperlink ref="C96" r:id="rId85" display="https://www.geeksforgeeks.org/find-position-element-sorted-array-infinite-numbers/"/>
+    <hyperlink ref="C97" r:id="rId86" display="https://leetcode.com/problems/peak-index-in-a-mountain-array/"/>
+    <hyperlink ref="C98" r:id="rId87" display="https://leetcode.com/problems/find-peak-element/"/>
+    <hyperlink ref="C99" r:id="rId88" display="https://leetcode.com/problems/find-minimum-in-rotated-sorted-array/"/>
+    <hyperlink ref="C100" r:id="rId89" display="https://www.geeksforgeeks.org/problems/rotation4723/1"/>
+    <hyperlink ref="C101" r:id="rId90" display="https://leetcode.com/problems/search-in-rotated-sorted-array/description/"/>
+    <hyperlink ref="C102" r:id="rId91" display="https://leetcode.com/problems/koko-eating-bananas/"/>
+    <hyperlink ref="C103" r:id="rId92" display="https://leetcode.com/problems/minimum-number-of-days-to-make-m-bouquets/"/>
+    <hyperlink ref="C104" r:id="rId93" display="https://www.geeksforgeeks.org/problems/aggressive-cows/1"/>
+    <hyperlink ref="C105" r:id="rId94" display="https://leetcode.com/problems/maximum-candies-allocated-to-k-children/description/"/>
+    <hyperlink ref="C106" r:id="rId95" display="https://leetcode.com/problems/capacity-to-ship-packages-within-d-days/description/"/>
+    <hyperlink ref="C107" r:id="rId96" display="https://www.geeksforgeeks.org/problems/allocate-minimum-number-of-pages0937/1"/>
+    <hyperlink ref="C108" r:id="rId97" display="https://leetcode.com/problems/split-array-largest-sum/description/"/>
+    <hyperlink ref="C109" r:id="rId98" display="https://leetcode.com/problems/search-a-2d-matrix/"/>
+    <hyperlink ref="C110" r:id="rId99" display="https://leetcode.com/problems/search-a-2d-matrix-ii/description/"/>
+    <hyperlink ref="C111" r:id="rId100" display="https://leetcode.com/problems/kth-smallest-element-in-a-sorted-matrix/description/"/>
+    <hyperlink ref="C112" r:id="rId101" display="https://leetcode.com/problems/kth-smallest-number-in-multiplication-table/description/"/>
+    <hyperlink ref="C113" r:id="rId102" display="https://leetcode.com/problems/median-of-two-sorted-arrays/"/>
+    <hyperlink ref="C115" r:id="rId103" display="https://leetcode.com/problems/find-if-path-exists-in-graph/"/>
+    <hyperlink ref="C116" r:id="rId104" display="https://leetcode.com/problems/number-of-provinces/"/>
+    <hyperlink ref="C117" r:id="rId105" display="https://leetcode.com/problems/minimum-number-of-vertices-to-reach-all-nodes/"/>
+    <hyperlink ref="C119" r:id="rId106" display="https://leetcode.com/problems/number-of-islands/"/>
+    <hyperlink ref="C121" r:id="rId107" display="https://leetcode.com/problems/flood-fill/"/>
+    <hyperlink ref="C122" r:id="rId108" display="https://leetcode.com/problems/number-of-closed-islands/"/>
+    <hyperlink ref="C127" r:id="rId109" display="https://leetcode.com/problems/find-median-from-data-stream/"/>
+    <hyperlink ref="C128" r:id="rId110" display="https://leetcode.com/problems/sliding-window-median/"/>
+    <hyperlink ref="C129" r:id="rId111" display="https://leetcode.com/problems/ipo/"/>
+    <hyperlink ref="C130" r:id="rId112" display="https://www.interviewbit.com/problems/maximum-sum-combinations/"/>
+    <hyperlink ref="C132" r:id="rId113" display="https://www.educative.io/courses/grokking-the-coding-interview/gx2OqlvEnWG"/>
+    <hyperlink ref="C133" r:id="rId114" display="https://www.educative.io/courses/grokking-the-coding-interview/7npk3V3JQNr"/>
+    <hyperlink ref="C134" r:id="rId115" display="https://www.educative.io/courses/grokking-the-coding-interview/B8R83jyN3KY"/>
+    <hyperlink ref="C137" r:id="rId116" display="https://leetcode.com/problems/generalized-abbreviation/"/>
+    <hyperlink ref="C144" r:id="rId117" display="https://github.com/dipjul/Grokking-the-Coding-Interview-Patterns-for-Coding-Questions/blob/master/13.-pattern-top-k-elements/02.top-k-numbers.md"/>
+    <hyperlink ref="C146" r:id="rId118" display="https://leetcode.com/problems/k-closest-points-to-origin/"/>
+    <hyperlink ref="C150" r:id="rId119" display="https://leetcode.com/problems/kth-largest-element-in-a-stream/"/>
+    <hyperlink ref="C158" r:id="rId120" display="https://github.com/dipjul/Grokking-the-Coding-Interview-Patterns-for-Coding-Questions/blob/master/13.-pattern-top-k-elements/13.HeapImplementation.md"/>
+    <hyperlink ref="C160" r:id="rId121" display="https://leetcode.com/problems/merge-k-sorted-lists/"/>
+    <hyperlink ref="C161" r:id="rId122" display="https://www.geeksforgeeks.org/find-m-th-smallest-value-in-k-sorted-arrays/"/>
+    <hyperlink ref="C162" r:id="rId123" display="https://www.educative.io/courses/grokking-the-coding-interview/x1NJVYKNvqz"/>
+    <hyperlink ref="C163" r:id="rId124" display="https://leetcode.com/problems/smallest-range-covering-elements-from-k-lists/"/>
+    <hyperlink ref="C166" r:id="rId125" display="https://leetcode.com/problems/valid-palindrome-ii/"/>
+    <hyperlink ref="C167" r:id="rId126" display="https://leetcode.com/problems/maximum-length-of-pair-chain/"/>
+    <hyperlink ref="C168" r:id="rId127" display="https://leetcode.com/problems/minimum-add-to-make-parentheses-valid/"/>
+    <hyperlink ref="C169" r:id="rId128" display="https://leetcode.com/problems/remove-duplicate-letters/"/>
+    <hyperlink ref="C170" r:id="rId129" display="https://leetcode.com/problems/largest-palindromic-number/"/>
+    <hyperlink ref="C171" r:id="rId130" display="https://leetcode.com/problems/removing-minimum-and-maximum-from-array/"/>
+    <hyperlink ref="C173" r:id="rId131" display="https://www.geeksforgeeks.org/0-1-knapsack-problem-dp-10/"/>
+    <hyperlink ref="C174" r:id="rId132" display="https://leetcode.com/problems/partition-equal-subset-sum/"/>
+    <hyperlink ref="C175" r:id="rId133" display="https://www.geeksforgeeks.org/subset-sum-problem-dp-25/"/>
+    <hyperlink ref="C176" r:id="rId134" display="https://www.geeksforgeeks.org/partition-a-set-into-two-subsets-such-that-the-difference-of-subset-sums-is-minimum/"/>
+    <hyperlink ref="C180" r:id="rId135" display="https://leetcode.com/problems/combination-sum/"/>
+    <hyperlink ref="D180" r:id="rId136" display="https://leetcode.com/problems/combination-sum-ii/"/>
+    <hyperlink ref="E180" r:id="rId137" display="https://leetcode.com/problems/combination-sum-iii/"/>
+    <hyperlink ref="C181" r:id="rId138" display="https://leetcode.com/problems/word-search/"/>
+    <hyperlink ref="D181" r:id="rId139" display="https://leetcode.com/problems/word-search-ii/"/>
+    <hyperlink ref="C182" r:id="rId140" display="https://leetcode.com/problems/sudoku-solver/"/>
+    <hyperlink ref="C183" r:id="rId141" display="https://leetcode.com/problems/factor-combinations/"/>
+    <hyperlink ref="C184" r:id="rId142" display="https://leetcode.com/problems/split-a-string-into-the-max-number-of-unique-substrings/"/>
+    <hyperlink ref="C186" r:id="rId143" display="https://leetcode.com/problems/implement-trie-prefix-tree/"/>
+    <hyperlink ref="C187" r:id="rId144" display="https://leetcode.com/problems/index-pairs-of-a-string/"/>
+    <hyperlink ref="C188" r:id="rId145" display="https://leetcode.com/problems/design-add-and-search-words-data-structure/"/>
+    <hyperlink ref="C189" r:id="rId146" display="https://leetcode.com/problems/extra-characters-in-a-string/"/>
+    <hyperlink ref="C190" r:id="rId147" display="https://leetcode.com/problems/search-suggestions-system/"/>
+    <hyperlink ref="C192" r:id="rId148" display="https://www.youtube.com/watch?v=cIBFEhD77b4"/>
+    <hyperlink ref="C193" r:id="rId149" display="https://leetcode.com/problems/course-schedule/"/>
+    <hyperlink ref="C194" r:id="rId149" display="https://leetcode.com/problems/course-schedule/"/>
+    <hyperlink ref="C195" r:id="rId150" display="https://leetcode.com/problems/course-schedule-ii/"/>
+    <hyperlink ref="C196" r:id="rId151" display="https://leetcode.com/problems/alien-dictionary/"/>
+    <hyperlink ref="C197" r:id="rId152" display="https://leetcode.com/problems/sequence-reconstruction/"/>
+    <hyperlink ref="C198" r:id="rId153" display="https://leetcode.com/problems/minimum-height-trees/"/>
+    <hyperlink ref="C200" r:id="rId154" display="https://leetcode.com/problems/redundant-connection/"/>
+    <hyperlink ref="D200" r:id="rId155" display="https://leetcode.com/problems/redundant-connection-ii/"/>
+    <hyperlink ref="C201" r:id="rId104" display="https://leetcode.com/problems/number-of-provinces/"/>
+    <hyperlink ref="C202" r:id="rId156" display="https://leetcode.com/problems/is-graph-bipartite/"/>
+    <hyperlink ref="C203" r:id="rId157" display="https://leetcode.com/problems/path-with-minimum-effort/"/>
+    <hyperlink ref="C205" r:id="rId158" display="https://leetcode.com/problems/merge-similar-items/"/>
+    <hyperlink ref="C206" r:id="rId159" display="https://leetcode.com/problems/132-pattern/"/>
+    <hyperlink ref="C207" r:id="rId160" display="https://leetcode.com/problems/my-calendar-i/"/>
+    <hyperlink ref="D207" r:id="rId161" display="https://leetcode.com/problems/my-calendar-ii/"/>
+    <hyperlink ref="E207" r:id="rId162" display="https://leetcode.com/problems/my-calendar-iii/"/>
   </hyperlinks>
-  <drawing r:id="rId167"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -53,13 +53,13 @@
     <t>1. Pattern: Two Pointers</t>
   </si>
   <si>
+    <t>Pair with Target Sum (easy)</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/two-sum-ii-input-array-is-sorted/description/</t>
+  </si>
+  <si>
     <t xml:space="preserve">Done </t>
-  </si>
-  <si>
-    <t>Pair with Target Sum (easy)</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/two-sum-ii-input-array-is-sorted/description/</t>
   </si>
   <si>
     <t>Rearrange 0 and 1</t>
@@ -2362,14 +2362,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF00FF00"/>
+        <bgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
-        <bgColor rgb="FF00FF00"/>
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -2860,19 +2860,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1"/>
@@ -2889,7 +2889,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -3361,7 +3361,7 @@
     <col min="5" max="5" width="30.5047619047619" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:5">
+    <row r="1" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3398,24 +3398,24 @@
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
-      <c r="F3" s="9" t="s">
+    </row>
+    <row r="4" customHeight="1" spans="1:6">
+      <c r="A4" s="6"/>
+      <c r="B4" s="9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:5">
-      <c r="A4" s="6"/>
-      <c r="B4" s="10" t="s">
+      <c r="C4" s="10" t="s">
         <v>9</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
-    </row>
-    <row r="5" customHeight="1" spans="1:5">
+      <c r="F4" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:6">
       <c r="A5" s="6"/>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="12" t="s">
@@ -3424,9 +3424,9 @@
       <c r="D5" s="13"/>
       <c r="E5" s="14"/>
     </row>
-    <row r="6" customHeight="1" spans="1:5">
+    <row r="6" customHeight="1" spans="1:6">
       <c r="A6" s="6"/>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="12" t="s">
@@ -3438,10 +3438,13 @@
       <c r="E6" s="12" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:5">
+      <c r="F6" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:6">
       <c r="A7" s="6"/>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="16" t="s">
@@ -3450,9 +3453,9 @@
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
     </row>
-    <row r="8" customHeight="1" spans="1:5">
+    <row r="8" customHeight="1" spans="1:6">
       <c r="A8" s="6"/>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="9" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="12" t="s">
@@ -3461,9 +3464,9 @@
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
     </row>
-    <row r="9" customHeight="1" spans="1:5">
+    <row r="9" customHeight="1" spans="1:6">
       <c r="A9" s="6"/>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C9" s="12" t="s">
@@ -3472,9 +3475,9 @@
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
     </row>
-    <row r="10" customHeight="1" spans="1:5">
+    <row r="10" customHeight="1" spans="1:6">
       <c r="A10" s="6"/>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="9" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="12" t="s">
@@ -3483,7 +3486,7 @@
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
     </row>
-    <row r="11" customHeight="1" spans="1:5">
+    <row r="11" customHeight="1" spans="1:6">
       <c r="A11" s="6"/>
       <c r="B11" s="6" t="s">
         <v>25</v>
@@ -3494,9 +3497,9 @@
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" customHeight="1" spans="1:5">
+    <row r="12" customHeight="1" spans="1:6">
       <c r="A12" s="6"/>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C12" s="12" t="s">
@@ -3505,7 +3508,7 @@
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
     </row>
-    <row r="13" customHeight="1" spans="1:5">
+    <row r="13" customHeight="1" spans="1:6">
       <c r="A13" s="6"/>
       <c r="B13" s="17" t="s">
         <v>29</v>
@@ -3516,7 +3519,7 @@
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
     </row>
-    <row r="14" customHeight="1" spans="1:5">
+    <row r="14" customHeight="1" spans="1:6">
       <c r="A14" s="6"/>
       <c r="B14" s="6" t="s">
         <v>31</v>
@@ -3527,7 +3530,7 @@
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
     </row>
-    <row r="15" customHeight="1" spans="1:4">
+    <row r="15" customHeight="1" spans="1:6">
       <c r="A15" s="6"/>
       <c r="B15" s="6" t="s">
         <v>33</v>
@@ -3539,7 +3542,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:5">
+    <row r="16" customHeight="1" spans="1:6">
       <c r="A16" s="6"/>
       <c r="B16" s="7" t="s">
         <v>36</v>
@@ -3550,7 +3553,7 @@
     </row>
     <row r="17" customHeight="1" spans="1:5">
       <c r="A17" s="6"/>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="9" t="s">
         <v>37</v>
       </c>
       <c r="C17" s="12" t="s">
@@ -3561,7 +3564,7 @@
     </row>
     <row r="18" customHeight="1" spans="1:5">
       <c r="A18" s="6"/>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="9" t="s">
         <v>39</v>
       </c>
       <c r="C18" s="12" t="s">
@@ -3572,7 +3575,7 @@
     </row>
     <row r="19" customHeight="1" spans="1:5">
       <c r="A19" s="6"/>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="9" t="s">
         <v>41</v>
       </c>
       <c r="C19" s="12" t="s">
@@ -3583,7 +3586,7 @@
     </row>
     <row r="20" customHeight="1" spans="1:5">
       <c r="A20" s="6"/>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="9" t="s">
         <v>43</v>
       </c>
       <c r="C20" s="12" t="s">
@@ -3594,7 +3597,7 @@
     </row>
     <row r="21" customHeight="1" spans="1:5">
       <c r="A21" s="6"/>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="9" t="s">
         <v>45</v>
       </c>
       <c r="C21" s="12" t="s">
@@ -3647,7 +3650,7 @@
     </row>
     <row r="26" customHeight="1" spans="1:5">
       <c r="A26" s="6"/>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="9" t="s">
         <v>54</v>
       </c>
       <c r="C26" s="18" t="s">
@@ -3658,7 +3661,7 @@
     </row>
     <row r="27" customHeight="1" spans="1:5">
       <c r="A27" s="6"/>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="9" t="s">
         <v>56</v>
       </c>
       <c r="C27" s="12" t="s">
@@ -3669,7 +3672,7 @@
     </row>
     <row r="28" customHeight="1" spans="1:5">
       <c r="A28" s="6"/>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="9" t="s">
         <v>58</v>
       </c>
       <c r="C28" s="12" t="s">
@@ -3680,7 +3683,7 @@
     </row>
     <row r="29" customHeight="1" spans="1:5">
       <c r="A29" s="6"/>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C29" s="12" t="s">
@@ -3691,7 +3694,7 @@
     </row>
     <row r="30" customHeight="1" spans="1:5">
       <c r="A30" s="6"/>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="9" t="s">
         <v>62</v>
       </c>
       <c r="C30" s="12" t="s">
@@ -3702,7 +3705,7 @@
     </row>
     <row r="31" customHeight="1" spans="1:5">
       <c r="A31" s="6"/>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="9" t="s">
         <v>64</v>
       </c>
       <c r="C31" s="12" t="s">
@@ -3713,7 +3716,7 @@
     </row>
     <row r="32" customHeight="1" spans="1:5">
       <c r="A32" s="6"/>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C32" s="12" t="s">
@@ -3724,7 +3727,7 @@
     </row>
     <row r="33" customHeight="1" spans="1:5">
       <c r="A33" s="6"/>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="9" t="s">
         <v>68</v>
       </c>
       <c r="C33" s="12" t="s">
@@ -3735,7 +3738,7 @@
     </row>
     <row r="34" customHeight="1" spans="1:5">
       <c r="A34" s="6"/>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="9" t="s">
         <v>69</v>
       </c>
       <c r="C34" s="12" t="s">
@@ -3799,7 +3802,7 @@
     </row>
     <row r="40" customHeight="1" spans="1:5">
       <c r="A40" s="6"/>
-      <c r="B40" s="10" t="s">
+      <c r="B40" s="9" t="s">
         <v>80</v>
       </c>
       <c r="C40" s="18" t="s">
@@ -3938,7 +3941,7 @@
     </row>
     <row r="53" customHeight="1" spans="1:5">
       <c r="A53" s="6"/>
-      <c r="B53" s="10" t="s">
+      <c r="B53" s="9" t="s">
         <v>104</v>
       </c>
       <c r="C53" s="12" t="s">
@@ -3949,7 +3952,7 @@
     </row>
     <row r="54" customHeight="1" spans="1:5">
       <c r="A54" s="6"/>
-      <c r="B54" s="10" t="s">
+      <c r="B54" s="9" t="s">
         <v>106</v>
       </c>
       <c r="C54" s="12" t="s">
@@ -3960,7 +3963,7 @@
     </row>
     <row r="55" customHeight="1" spans="1:5">
       <c r="A55" s="6"/>
-      <c r="B55" s="10" t="s">
+      <c r="B55" s="9" t="s">
         <v>108</v>
       </c>
       <c r="C55" s="12" t="s">
@@ -3971,7 +3974,7 @@
     </row>
     <row r="56" customHeight="1" spans="1:5">
       <c r="A56" s="6"/>
-      <c r="B56" s="10" t="s">
+      <c r="B56" s="9" t="s">
         <v>110</v>
       </c>
       <c r="C56" s="12" t="s">
@@ -3981,7 +3984,7 @@
     </row>
     <row r="57" customHeight="1" spans="1:5">
       <c r="A57" s="6"/>
-      <c r="B57" s="10" t="s">
+      <c r="B57" s="9" t="s">
         <v>112</v>
       </c>
       <c r="C57" s="12" t="s">
@@ -4119,7 +4122,7 @@
     </row>
     <row r="70" customHeight="1" spans="1:5">
       <c r="A70" s="6"/>
-      <c r="B70" s="10" t="s">
+      <c r="B70" s="9" t="s">
         <v>136</v>
       </c>
       <c r="C70" s="12" t="s">
@@ -4130,7 +4133,7 @@
     </row>
     <row r="71" customHeight="1" spans="1:5">
       <c r="A71" s="6"/>
-      <c r="B71" s="10" t="s">
+      <c r="B71" s="9" t="s">
         <v>138</v>
       </c>
       <c r="C71" s="12" t="s">
@@ -4141,7 +4144,7 @@
     </row>
     <row r="72" customHeight="1" spans="1:5">
       <c r="A72" s="6"/>
-      <c r="B72" s="10" t="s">
+      <c r="B72" s="9" t="s">
         <v>140</v>
       </c>
       <c r="C72" s="12" t="s">
@@ -4152,7 +4155,7 @@
     </row>
     <row r="73" customHeight="1" spans="1:5">
       <c r="A73" s="6"/>
-      <c r="B73" s="10" t="s">
+      <c r="B73" s="9" t="s">
         <v>142</v>
       </c>
       <c r="C73" s="12" t="s">
@@ -4174,7 +4177,7 @@
     </row>
     <row r="75" customHeight="1" spans="1:5">
       <c r="A75" s="6"/>
-      <c r="B75" s="10" t="s">
+      <c r="B75" s="9" t="s">
         <v>146</v>
       </c>
       <c r="C75" s="12" t="s">
@@ -4205,7 +4208,7 @@
     </row>
     <row r="78" customHeight="1" spans="1:5">
       <c r="A78" s="6"/>
-      <c r="B78" s="10" t="s">
+      <c r="B78" s="9" t="s">
         <v>151</v>
       </c>
       <c r="C78" s="12" t="s">
@@ -4216,7 +4219,7 @@
     </row>
     <row r="79" customHeight="1" spans="1:5">
       <c r="A79" s="6"/>
-      <c r="B79" s="10" t="s">
+      <c r="B79" s="9" t="s">
         <v>153</v>
       </c>
       <c r="C79" s="8"/>
@@ -4225,7 +4228,7 @@
     </row>
     <row r="80" customHeight="1" spans="1:5">
       <c r="A80" s="6"/>
-      <c r="B80" s="10" t="s">
+      <c r="B80" s="9" t="s">
         <v>154</v>
       </c>
       <c r="C80" s="12" t="s">
@@ -4236,7 +4239,7 @@
     </row>
     <row r="81" customHeight="1" spans="1:5">
       <c r="A81" s="6"/>
-      <c r="B81" s="10" t="s">
+      <c r="B81" s="9" t="s">
         <v>156</v>
       </c>
       <c r="C81" s="12" t="s">
@@ -4258,7 +4261,7 @@
     </row>
     <row r="83" customHeight="1" spans="1:5">
       <c r="A83" s="6"/>
-      <c r="B83" s="10" t="s">
+      <c r="B83" s="9" t="s">
         <v>160</v>
       </c>
       <c r="C83" s="12" t="s">
@@ -4300,7 +4303,7 @@
     </row>
     <row r="87" customHeight="1" spans="1:5">
       <c r="A87" s="6"/>
-      <c r="B87" s="10" t="s">
+      <c r="B87" s="9" t="s">
         <v>167</v>
       </c>
       <c r="C87" s="12" t="s">
@@ -4311,7 +4314,7 @@
     </row>
     <row r="88" customHeight="1" spans="1:5">
       <c r="A88" s="6"/>
-      <c r="B88" s="10" t="s">
+      <c r="B88" s="9" t="s">
         <v>169</v>
       </c>
       <c r="C88" s="12" t="s">
@@ -4322,7 +4325,7 @@
     </row>
     <row r="89" customHeight="1" spans="1:5">
       <c r="A89" s="6"/>
-      <c r="B89" s="10" t="s">
+      <c r="B89" s="9" t="s">
         <v>171</v>
       </c>
       <c r="C89" s="12" t="s">
@@ -4333,7 +4336,7 @@
     </row>
     <row r="90" customHeight="1" spans="1:5">
       <c r="A90" s="6"/>
-      <c r="B90" s="10" t="s">
+      <c r="B90" s="9" t="s">
         <v>173</v>
       </c>
       <c r="C90" s="12" t="s">
@@ -4353,7 +4356,7 @@
     </row>
     <row r="92" customHeight="1" spans="1:5">
       <c r="A92" s="6"/>
-      <c r="B92" s="10" t="s">
+      <c r="B92" s="9" t="s">
         <v>176</v>
       </c>
       <c r="C92" s="12" t="s">
@@ -4364,7 +4367,7 @@
     </row>
     <row r="93" customHeight="1" spans="1:5">
       <c r="A93" s="6"/>
-      <c r="B93" s="10" t="s">
+      <c r="B93" s="9" t="s">
         <v>178</v>
       </c>
       <c r="C93" s="12" t="s">
@@ -4375,7 +4378,7 @@
     </row>
     <row r="94" customHeight="1" spans="1:5">
       <c r="A94" s="6"/>
-      <c r="B94" s="10" t="s">
+      <c r="B94" s="9" t="s">
         <v>180</v>
       </c>
       <c r="C94" s="12" t="s">
@@ -4386,7 +4389,7 @@
     </row>
     <row r="95" customHeight="1" spans="1:5">
       <c r="A95" s="6"/>
-      <c r="B95" s="10" t="s">
+      <c r="B95" s="9" t="s">
         <v>182</v>
       </c>
       <c r="C95" s="12" t="s">
@@ -4408,7 +4411,7 @@
     </row>
     <row r="97" customHeight="1" spans="1:5">
       <c r="A97" s="6"/>
-      <c r="B97" s="10" t="s">
+      <c r="B97" s="9" t="s">
         <v>186</v>
       </c>
       <c r="C97" s="12" t="s">
@@ -4430,7 +4433,7 @@
     </row>
     <row r="99" customHeight="1" spans="1:5">
       <c r="A99" s="6"/>
-      <c r="B99" s="10" t="s">
+      <c r="B99" s="9" t="s">
         <v>190</v>
       </c>
       <c r="C99" s="12" t="s">
@@ -4441,7 +4444,7 @@
     </row>
     <row r="100" customHeight="1" spans="1:5">
       <c r="A100" s="6"/>
-      <c r="B100" s="10" t="s">
+      <c r="B100" s="9" t="s">
         <v>192</v>
       </c>
       <c r="C100" s="12" t="s">
@@ -4452,7 +4455,7 @@
     </row>
     <row r="101" customHeight="1" spans="1:5">
       <c r="A101" s="6"/>
-      <c r="B101" s="10" t="s">
+      <c r="B101" s="9" t="s">
         <v>194</v>
       </c>
       <c r="C101" s="12" t="s">
@@ -4463,7 +4466,7 @@
     </row>
     <row r="102" customHeight="1" spans="1:5">
       <c r="A102" s="6"/>
-      <c r="B102" s="10" t="s">
+      <c r="B102" s="9" t="s">
         <v>196</v>
       </c>
       <c r="C102" s="12" t="s">
@@ -4485,7 +4488,7 @@
     </row>
     <row r="104" customHeight="1" spans="1:5">
       <c r="A104" s="6"/>
-      <c r="B104" s="10" t="s">
+      <c r="B104" s="9" t="s">
         <v>200</v>
       </c>
       <c r="C104" s="12" t="s">
@@ -4518,7 +4521,7 @@
     </row>
     <row r="107" customHeight="1" spans="1:5">
       <c r="A107" s="6"/>
-      <c r="B107" s="10" t="s">
+      <c r="B107" s="9" t="s">
         <v>206</v>
       </c>
       <c r="C107" s="16" t="s">
@@ -4540,7 +4543,7 @@
     </row>
     <row r="109" customHeight="1" spans="1:5">
       <c r="A109" s="6"/>
-      <c r="B109" s="10" t="s">
+      <c r="B109" s="9" t="s">
         <v>210</v>
       </c>
       <c r="C109" s="16" t="s">
@@ -4551,7 +4554,7 @@
     </row>
     <row r="110" customHeight="1" spans="1:5">
       <c r="A110" s="6"/>
-      <c r="B110" s="10" t="s">
+      <c r="B110" s="9" t="s">
         <v>212</v>
       </c>
       <c r="C110" s="16" t="s">
@@ -4562,7 +4565,7 @@
     </row>
     <row r="111" customHeight="1" spans="1:5">
       <c r="A111" s="6"/>
-      <c r="B111" s="10" t="s">
+      <c r="B111" s="9" t="s">
         <v>214</v>
       </c>
       <c r="C111" s="16" t="s">
@@ -4573,7 +4576,7 @@
     </row>
     <row r="112" customHeight="1" spans="1:5">
       <c r="A112" s="6"/>
-      <c r="B112" s="10" t="s">
+      <c r="B112" s="9" t="s">
         <v>216</v>
       </c>
       <c r="C112" s="16" t="s">

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -3452,6 +3452,9 @@
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
+      <c r="F7" s="11" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="8" customHeight="1" spans="1:6">
       <c r="A8" s="6"/>
@@ -5579,7 +5582,7 @@
     <hyperlink ref="C6" r:id="rId4" display="https://leetcode.com/problems/remove-duplicates-from-sorted-list/"/>
     <hyperlink ref="D6" r:id="rId5" display="https://leetcode.com/problems/remove-duplicates-from-sorted-array/description/"/>
     <hyperlink ref="E6" r:id="rId6" display="https://leetcode.com/problems/remove-duplicates-from-sorted-array-ii/"/>
-    <hyperlink ref="C7" r:id="rId7" display="https://leetcode.com/problems/squares-of-a-sorted-array/"/>
+    <hyperlink ref="C7" r:id="rId7" display="https://leetcode.com/problems/squares-of-a-sorted-array/" tooltip="https://leetcode.com/problems/squares-of-a-sorted-array/"/>
     <hyperlink ref="C8" r:id="rId8" display="https://leetcode.com/problems/3sum/"/>
     <hyperlink ref="C9" r:id="rId9" display="https://leetcode.com/problems/3sum-closest/"/>
     <hyperlink ref="C10" r:id="rId10" display="https://www.geeksforgeeks.org/problems/count-triplets-with-sum-smaller-than-x5549/1"/>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7620"/>
+    <workbookView windowWidth="20490" windowHeight="7020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2341,7 +2341,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2350,14 +2350,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEECE1"/>
-        <bgColor rgb="FFEEECE1"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFEEECE1"/>
+        <bgColor rgb="FFEEECE1"/>
       </patternFill>
     </fill>
     <fill>
@@ -2376,6 +2376,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -2716,7 +2722,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2740,16 +2746,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2758,110 +2764,111 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -2869,12 +2876,13 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -3362,2207 +3370,2207 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
     </row>
     <row r="2" customHeight="1" spans="1:6">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:6">
-      <c r="A3" s="6"/>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:6">
+      <c r="A3" s="7"/>
       <c r="B3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
     </row>
     <row r="4" customHeight="1" spans="1:6">
-      <c r="A4" s="6"/>
+      <c r="A4" s="8"/>
       <c r="B4" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="11" t="s">
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="12" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:6">
-      <c r="A5" s="6"/>
+      <c r="A5" s="8"/>
       <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="15"/>
     </row>
     <row r="6" customHeight="1" spans="1:6">
-      <c r="A6" s="6"/>
+      <c r="A6" s="8"/>
       <c r="B6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:6">
-      <c r="A7" s="6"/>
+      <c r="A7" s="8"/>
       <c r="B7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="11" t="s">
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="12" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:6">
-      <c r="A8" s="6"/>
+      <c r="A8" s="8"/>
       <c r="B8" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
     </row>
     <row r="9" customHeight="1" spans="1:6">
-      <c r="A9" s="6"/>
+      <c r="A9" s="8"/>
       <c r="B9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
     </row>
     <row r="10" customHeight="1" spans="1:6">
-      <c r="A10" s="6"/>
+      <c r="A10" s="8"/>
       <c r="B10" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
     </row>
     <row r="11" customHeight="1" spans="1:6">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6" t="s">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
     </row>
     <row r="12" customHeight="1" spans="1:6">
-      <c r="A12" s="6"/>
+      <c r="A12" s="8"/>
       <c r="B12" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
     </row>
     <row r="13" customHeight="1" spans="1:6">
-      <c r="A13" s="6"/>
-      <c r="B13" s="17" t="s">
+      <c r="A13" s="8"/>
+      <c r="B13" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
     </row>
     <row r="14" customHeight="1" spans="1:6">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6" t="s">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
     </row>
     <row r="15" customHeight="1" spans="1:6">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6" t="s">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:6">
-      <c r="A16" s="6"/>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:6">
+      <c r="A16" s="7"/>
       <c r="B16" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
     </row>
     <row r="17" customHeight="1" spans="1:5">
-      <c r="A17" s="6"/>
+      <c r="A17" s="8"/>
       <c r="B17" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
     </row>
     <row r="18" customHeight="1" spans="1:5">
-      <c r="A18" s="6"/>
+      <c r="A18" s="8"/>
       <c r="B18" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
     </row>
     <row r="19" customHeight="1" spans="1:5">
-      <c r="A19" s="6"/>
+      <c r="A19" s="8"/>
       <c r="B19" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
     </row>
     <row r="20" customHeight="1" spans="1:5">
-      <c r="A20" s="6"/>
+      <c r="A20" s="8"/>
       <c r="B20" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
     </row>
     <row r="21" customHeight="1" spans="1:5">
-      <c r="A21" s="6"/>
+      <c r="A21" s="8"/>
       <c r="B21" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
     </row>
     <row r="22" customHeight="1" spans="1:5">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6" t="s">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
     </row>
     <row r="23" customHeight="1" spans="1:5">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6" t="s">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
     </row>
     <row r="24" customHeight="1" spans="1:5">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6" t="s">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:5">
-      <c r="A25" s="6"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A25" s="7"/>
       <c r="B25" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
     </row>
     <row r="26" customHeight="1" spans="1:5">
-      <c r="A26" s="6"/>
+      <c r="A26" s="8"/>
       <c r="B26" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
     </row>
     <row r="27" customHeight="1" spans="1:5">
-      <c r="A27" s="6"/>
+      <c r="A27" s="8"/>
       <c r="B27" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
     </row>
     <row r="28" customHeight="1" spans="1:5">
-      <c r="A28" s="6"/>
+      <c r="A28" s="8"/>
       <c r="B28" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
     </row>
     <row r="29" customHeight="1" spans="1:5">
-      <c r="A29" s="6"/>
+      <c r="A29" s="8"/>
       <c r="B29" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
     </row>
     <row r="30" customHeight="1" spans="1:5">
-      <c r="A30" s="6"/>
+      <c r="A30" s="8"/>
       <c r="B30" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
     </row>
     <row r="31" customHeight="1" spans="1:5">
-      <c r="A31" s="6"/>
+      <c r="A31" s="8"/>
       <c r="B31" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
     </row>
     <row r="32" customHeight="1" spans="1:5">
-      <c r="A32" s="6"/>
+      <c r="A32" s="8"/>
       <c r="B32" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
     </row>
     <row r="33" customHeight="1" spans="1:5">
-      <c r="A33" s="6"/>
+      <c r="A33" s="8"/>
       <c r="B33" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
     </row>
     <row r="34" customHeight="1" spans="1:5">
-      <c r="A34" s="6"/>
+      <c r="A34" s="8"/>
       <c r="B34" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
     </row>
     <row r="35" customHeight="1" spans="1:5">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6" t="s">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
     </row>
     <row r="36" customHeight="1" spans="1:5">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6" t="s">
+      <c r="A36" s="8"/>
+      <c r="B36" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
     </row>
     <row r="37" customHeight="1" spans="1:5">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6" t="s">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C37" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-    </row>
-    <row r="38" customHeight="1" spans="1:5">
-      <c r="A38" s="6"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A38" s="7"/>
       <c r="B38" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
     </row>
     <row r="39" customHeight="1" spans="1:5">
-      <c r="A39" s="6"/>
-      <c r="B39" s="19" t="s">
+      <c r="A39" s="8"/>
+      <c r="B39" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
     </row>
     <row r="40" customHeight="1" spans="1:5">
-      <c r="A40" s="6"/>
+      <c r="A40" s="8"/>
       <c r="B40" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
     </row>
     <row r="41" customHeight="1" spans="1:5">
-      <c r="A41" s="6"/>
-      <c r="B41" s="19" t="s">
+      <c r="A41" s="8"/>
+      <c r="B41" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="C41" s="18" t="s">
+      <c r="C41" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
     </row>
     <row r="42" customHeight="1" spans="1:5">
-      <c r="A42" s="6"/>
-      <c r="B42" s="19" t="s">
+      <c r="A42" s="8"/>
+      <c r="B42" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="C42" s="18" t="s">
+      <c r="C42" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
     </row>
     <row r="43" customHeight="1" spans="1:5">
-      <c r="A43" s="6"/>
-      <c r="B43" s="19" t="s">
+      <c r="A43" s="8"/>
+      <c r="B43" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="C43" s="18" t="s">
+      <c r="C43" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
     </row>
     <row r="44" customHeight="1" spans="1:5">
-      <c r="A44" s="6"/>
-      <c r="B44" s="19" t="s">
+      <c r="A44" s="8"/>
+      <c r="B44" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-    </row>
-    <row r="45" customHeight="1" spans="1:5">
-      <c r="A45" s="6"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+    </row>
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A45" s="7"/>
       <c r="B45" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
     </row>
     <row r="46" customHeight="1" spans="1:5">
-      <c r="A46" s="6"/>
-      <c r="B46" s="19" t="s">
+      <c r="A46" s="8"/>
+      <c r="B46" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="C46" s="18" t="s">
+      <c r="C46" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
     </row>
     <row r="47" customHeight="1" spans="1:5">
-      <c r="A47" s="6"/>
-      <c r="B47" s="19" t="s">
+      <c r="A47" s="8"/>
+      <c r="B47" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="C47" s="18" t="s">
+      <c r="C47" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
     </row>
     <row r="48" customHeight="1" spans="1:5">
-      <c r="A48" s="6"/>
-      <c r="B48" s="19" t="s">
+      <c r="A48" s="8"/>
+      <c r="B48" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="C48" s="18" t="s">
+      <c r="C48" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
     </row>
     <row r="49" customHeight="1" spans="1:5">
-      <c r="A49" s="6"/>
-      <c r="B49" s="19" t="s">
+      <c r="A49" s="8"/>
+      <c r="B49" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="C49" s="18" t="s">
+      <c r="C49" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
     </row>
     <row r="50" customHeight="1" spans="1:5">
-      <c r="A50" s="6"/>
-      <c r="B50" s="20" t="s">
+      <c r="A50" s="8"/>
+      <c r="B50" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="C50" s="18" t="s">
+      <c r="C50" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
     </row>
     <row r="51" customHeight="1" spans="1:5">
-      <c r="A51" s="6"/>
-      <c r="B51" s="20" t="s">
+      <c r="A51" s="8"/>
+      <c r="B51" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="C51" s="18" t="s">
+      <c r="C51" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-    </row>
-    <row r="52" customHeight="1" spans="1:5">
-      <c r="A52" s="6"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+    </row>
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A52" s="7"/>
       <c r="B52" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
     </row>
     <row r="53" customHeight="1" spans="1:5">
-      <c r="A53" s="6"/>
+      <c r="A53" s="8"/>
       <c r="B53" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
     </row>
     <row r="54" customHeight="1" spans="1:5">
-      <c r="A54" s="6"/>
+      <c r="A54" s="8"/>
       <c r="B54" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="C54" s="12" t="s">
+      <c r="C54" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
     </row>
     <row r="55" customHeight="1" spans="1:5">
-      <c r="A55" s="6"/>
+      <c r="A55" s="8"/>
       <c r="B55" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C55" s="12" t="s">
+      <c r="C55" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
     </row>
     <row r="56" customHeight="1" spans="1:5">
-      <c r="A56" s="6"/>
+      <c r="A56" s="8"/>
       <c r="B56" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="C56" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="E56" s="8"/>
+      <c r="E56" s="11"/>
     </row>
     <row r="57" customHeight="1" spans="1:5">
-      <c r="A57" s="6"/>
+      <c r="A57" s="8"/>
       <c r="B57" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="C57" s="12" t="s">
+      <c r="C57" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
     </row>
     <row r="58" customHeight="1" spans="1:5">
-      <c r="A58" s="6"/>
-      <c r="B58" s="6" t="s">
+      <c r="A58" s="8"/>
+      <c r="B58" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="C58" s="12" t="s">
+      <c r="C58" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
+      <c r="D58" s="11"/>
+      <c r="E58" s="11"/>
     </row>
     <row r="59" customHeight="1" spans="1:5">
-      <c r="A59" s="6"/>
-      <c r="B59" s="6" t="s">
+      <c r="A59" s="8"/>
+      <c r="B59" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="C59" s="12" t="s">
+      <c r="C59" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-    </row>
-    <row r="60" customHeight="1" spans="1:5">
-      <c r="A60" s="6"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
+    </row>
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A60" s="7"/>
       <c r="B60" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
     </row>
     <row r="61" customHeight="1" spans="1:5">
-      <c r="A61" s="6"/>
-      <c r="B61" s="6" t="s">
+      <c r="A61" s="8"/>
+      <c r="B61" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C61" s="12" t="s">
+      <c r="C61" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="E61" s="8"/>
+      <c r="E61" s="11"/>
     </row>
     <row r="62" customHeight="1" spans="1:5">
-      <c r="A62" s="6"/>
-      <c r="B62" s="6" t="s">
+      <c r="A62" s="8"/>
+      <c r="B62" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="C62" s="12" t="s">
+      <c r="C62" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
+      <c r="D62" s="11"/>
+      <c r="E62" s="11"/>
     </row>
     <row r="63" customHeight="1" spans="1:5">
-      <c r="A63" s="6"/>
-      <c r="B63" s="6" t="s">
+      <c r="A63" s="8"/>
+      <c r="B63" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C63" s="12" t="s">
+      <c r="C63" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
+      <c r="D63" s="11"/>
+      <c r="E63" s="11"/>
     </row>
     <row r="64" customHeight="1" spans="1:5">
-      <c r="A64" s="6"/>
-      <c r="B64" s="6" t="s">
+      <c r="A64" s="8"/>
+      <c r="B64" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="C64" s="12" t="s">
+      <c r="C64" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
+      <c r="D64" s="11"/>
+      <c r="E64" s="11"/>
     </row>
     <row r="65" customHeight="1" spans="1:5">
-      <c r="A65" s="6"/>
-      <c r="B65" s="6" t="s">
+      <c r="A65" s="8"/>
+      <c r="B65" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C65" s="12" t="s">
+      <c r="C65" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11"/>
     </row>
     <row r="66" customHeight="1" spans="1:5">
-      <c r="A66" s="6"/>
-      <c r="B66" s="6" t="s">
+      <c r="A66" s="8"/>
+      <c r="B66" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="C66" s="12" t="s">
+      <c r="C66" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
     </row>
     <row r="67" customHeight="1" spans="1:5">
-      <c r="A67" s="6"/>
-      <c r="B67" s="6" t="s">
+      <c r="A67" s="8"/>
+      <c r="B67" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C67" s="12" t="s">
+      <c r="C67" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="D67" s="8"/>
-      <c r="E67" s="8"/>
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
     </row>
     <row r="68" customHeight="1" spans="1:5">
-      <c r="A68" s="6"/>
-      <c r="B68" s="6" t="s">
+      <c r="A68" s="8"/>
+      <c r="B68" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C68" s="12" t="s">
+      <c r="C68" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-    </row>
-    <row r="69" customHeight="1" spans="1:5">
-      <c r="A69" s="6"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="11"/>
+    </row>
+    <row r="69" s="1" customFormat="1" customHeight="1" spans="1:5">
+      <c r="A69" s="7"/>
       <c r="B69" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
     </row>
     <row r="70" customHeight="1" spans="1:5">
-      <c r="A70" s="6"/>
+      <c r="A70" s="8"/>
       <c r="B70" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="C70" s="12" t="s">
+      <c r="C70" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
     </row>
     <row r="71" customHeight="1" spans="1:5">
-      <c r="A71" s="6"/>
+      <c r="A71" s="8"/>
       <c r="B71" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="C71" s="12" t="s">
+      <c r="C71" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
     </row>
     <row r="72" customHeight="1" spans="1:5">
-      <c r="A72" s="6"/>
+      <c r="A72" s="8"/>
       <c r="B72" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="C72" s="12" t="s">
+      <c r="C72" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
     </row>
     <row r="73" customHeight="1" spans="1:5">
-      <c r="A73" s="6"/>
+      <c r="A73" s="8"/>
       <c r="B73" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="C73" s="12" t="s">
+      <c r="C73" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
     </row>
     <row r="74" customHeight="1" spans="1:5">
-      <c r="A74" s="6"/>
-      <c r="B74" s="6" t="s">
+      <c r="A74" s="8"/>
+      <c r="B74" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="C74" s="12" t="s">
+      <c r="C74" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
+      <c r="D74" s="11"/>
+      <c r="E74" s="11"/>
     </row>
     <row r="75" customHeight="1" spans="1:5">
-      <c r="A75" s="6"/>
+      <c r="A75" s="8"/>
       <c r="B75" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="C75" s="12" t="s">
+      <c r="C75" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
     </row>
     <row r="76" customHeight="1" spans="1:5">
-      <c r="A76" s="6"/>
-      <c r="B76" s="7" t="s">
+      <c r="A76" s="8"/>
+      <c r="B76" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
+      <c r="C76" s="11"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
     </row>
     <row r="77" customHeight="1" spans="1:5">
-      <c r="A77" s="6"/>
-      <c r="B77" s="21" t="s">
+      <c r="A77" s="8"/>
+      <c r="B77" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="C77" s="12" t="s">
+      <c r="C77" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="11"/>
     </row>
     <row r="78" customHeight="1" spans="1:5">
-      <c r="A78" s="6"/>
+      <c r="A78" s="8"/>
       <c r="B78" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="C78" s="12" t="s">
+      <c r="C78" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="11"/>
     </row>
     <row r="79" customHeight="1" spans="1:5">
-      <c r="A79" s="6"/>
+      <c r="A79" s="8"/>
       <c r="B79" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
+      <c r="C79" s="11"/>
+      <c r="D79" s="11"/>
+      <c r="E79" s="11"/>
     </row>
     <row r="80" customHeight="1" spans="1:5">
-      <c r="A80" s="6"/>
+      <c r="A80" s="8"/>
       <c r="B80" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="C80" s="12" t="s">
+      <c r="C80" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="D80" s="14"/>
-      <c r="E80" s="14"/>
+      <c r="D80" s="15"/>
+      <c r="E80" s="15"/>
     </row>
     <row r="81" customHeight="1" spans="1:5">
-      <c r="A81" s="6"/>
+      <c r="A81" s="8"/>
       <c r="B81" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="C81" s="12" t="s">
+      <c r="C81" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="11"/>
     </row>
     <row r="82" customHeight="1" spans="1:5">
-      <c r="A82" s="6"/>
-      <c r="B82" s="6" t="s">
+      <c r="A82" s="8"/>
+      <c r="B82" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="C82" s="12" t="s">
+      <c r="C82" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="D82" s="8"/>
-      <c r="E82" s="8"/>
+      <c r="D82" s="11"/>
+      <c r="E82" s="11"/>
     </row>
     <row r="83" customHeight="1" spans="1:5">
-      <c r="A83" s="6"/>
+      <c r="A83" s="8"/>
       <c r="B83" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="C83" s="12" t="s">
+      <c r="C83" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="D83" s="8"/>
-      <c r="E83" s="8"/>
+      <c r="D83" s="11"/>
+      <c r="E83" s="11"/>
     </row>
     <row r="84" customHeight="1" spans="1:5">
-      <c r="A84" s="6"/>
-      <c r="B84" s="6" t="s">
+      <c r="A84" s="8"/>
+      <c r="B84" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="C84" s="12" t="s">
+      <c r="C84" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="D84" s="8"/>
-      <c r="E84" s="8"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="11"/>
     </row>
     <row r="85" customHeight="1" spans="1:5">
-      <c r="A85" s="6"/>
-      <c r="B85" s="6" t="s">
+      <c r="A85" s="8"/>
+      <c r="B85" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="C85" s="12" t="s">
+      <c r="C85" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="D85" s="8"/>
-      <c r="E85" s="8"/>
+      <c r="D85" s="11"/>
+      <c r="E85" s="11"/>
     </row>
     <row r="86" customHeight="1" spans="1:5">
-      <c r="A86" s="6"/>
-      <c r="B86" s="7" t="s">
+      <c r="A86" s="8"/>
+      <c r="B86" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="C86" s="8"/>
-      <c r="D86" s="8"/>
-      <c r="E86" s="8"/>
+      <c r="C86" s="11"/>
+      <c r="D86" s="11"/>
+      <c r="E86" s="11"/>
     </row>
     <row r="87" customHeight="1" spans="1:5">
-      <c r="A87" s="6"/>
+      <c r="A87" s="8"/>
       <c r="B87" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="C87" s="12" t="s">
+      <c r="C87" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="D87" s="8"/>
-      <c r="E87" s="8"/>
+      <c r="D87" s="11"/>
+      <c r="E87" s="11"/>
     </row>
     <row r="88" customHeight="1" spans="1:5">
-      <c r="A88" s="6"/>
+      <c r="A88" s="8"/>
       <c r="B88" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C88" s="12" t="s">
+      <c r="C88" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="D88" s="8"/>
-      <c r="E88" s="8"/>
+      <c r="D88" s="11"/>
+      <c r="E88" s="11"/>
     </row>
     <row r="89" customHeight="1" spans="1:5">
-      <c r="A89" s="6"/>
+      <c r="A89" s="8"/>
       <c r="B89" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C89" s="12" t="s">
+      <c r="C89" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="D89" s="8"/>
-      <c r="E89" s="8"/>
+      <c r="D89" s="11"/>
+      <c r="E89" s="11"/>
     </row>
     <row r="90" customHeight="1" spans="1:5">
-      <c r="A90" s="6"/>
+      <c r="A90" s="8"/>
       <c r="B90" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="C90" s="12" t="s">
+      <c r="C90" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="D90" s="8"/>
-      <c r="E90" s="8"/>
+      <c r="D90" s="11"/>
+      <c r="E90" s="11"/>
     </row>
     <row r="91" customHeight="1" spans="1:5">
-      <c r="A91" s="6"/>
-      <c r="B91" s="7" t="s">
+      <c r="A91" s="8"/>
+      <c r="B91" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="C91" s="22"/>
-      <c r="D91" s="8"/>
-      <c r="E91" s="8"/>
+      <c r="C91" s="24"/>
+      <c r="D91" s="11"/>
+      <c r="E91" s="11"/>
     </row>
     <row r="92" customHeight="1" spans="1:5">
-      <c r="A92" s="6"/>
+      <c r="A92" s="8"/>
       <c r="B92" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="C92" s="12" t="s">
+      <c r="C92" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="D92" s="8"/>
-      <c r="E92" s="8"/>
+      <c r="D92" s="11"/>
+      <c r="E92" s="11"/>
     </row>
     <row r="93" customHeight="1" spans="1:5">
-      <c r="A93" s="6"/>
+      <c r="A93" s="8"/>
       <c r="B93" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="C93" s="12" t="s">
+      <c r="C93" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="D93" s="8"/>
-      <c r="E93" s="8"/>
+      <c r="D93" s="11"/>
+      <c r="E93" s="11"/>
     </row>
     <row r="94" customHeight="1" spans="1:5">
-      <c r="A94" s="6"/>
+      <c r="A94" s="8"/>
       <c r="B94" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C94" s="12" t="s">
+      <c r="C94" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="D94" s="8"/>
-      <c r="E94" s="8"/>
+      <c r="D94" s="11"/>
+      <c r="E94" s="11"/>
     </row>
     <row r="95" customHeight="1" spans="1:5">
-      <c r="A95" s="6"/>
+      <c r="A95" s="8"/>
       <c r="B95" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="C95" s="12" t="s">
+      <c r="C95" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="D95" s="8"/>
-      <c r="E95" s="8"/>
+      <c r="D95" s="11"/>
+      <c r="E95" s="11"/>
     </row>
     <row r="96" customHeight="1" spans="1:5">
-      <c r="A96" s="6"/>
-      <c r="B96" s="6" t="s">
+      <c r="A96" s="8"/>
+      <c r="B96" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="C96" s="12" t="s">
+      <c r="C96" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="D96" s="8"/>
-      <c r="E96" s="8"/>
+      <c r="D96" s="11"/>
+      <c r="E96" s="11"/>
     </row>
     <row r="97" customHeight="1" spans="1:5">
-      <c r="A97" s="6"/>
+      <c r="A97" s="8"/>
       <c r="B97" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="C97" s="12" t="s">
+      <c r="C97" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="D97" s="8"/>
-      <c r="E97" s="8"/>
+      <c r="D97" s="11"/>
+      <c r="E97" s="11"/>
     </row>
     <row r="98" customHeight="1" spans="1:5">
-      <c r="A98" s="6"/>
-      <c r="B98" s="6" t="s">
+      <c r="A98" s="8"/>
+      <c r="B98" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="C98" s="12" t="s">
+      <c r="C98" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="D98" s="8"/>
-      <c r="E98" s="8"/>
+      <c r="D98" s="11"/>
+      <c r="E98" s="11"/>
     </row>
     <row r="99" customHeight="1" spans="1:5">
-      <c r="A99" s="6"/>
+      <c r="A99" s="8"/>
       <c r="B99" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="C99" s="12" t="s">
+      <c r="C99" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="D99" s="8"/>
-      <c r="E99" s="8"/>
+      <c r="D99" s="11"/>
+      <c r="E99" s="11"/>
     </row>
     <row r="100" customHeight="1" spans="1:5">
-      <c r="A100" s="6"/>
+      <c r="A100" s="8"/>
       <c r="B100" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="C100" s="12" t="s">
+      <c r="C100" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="D100" s="8"/>
-      <c r="E100" s="8"/>
+      <c r="D100" s="11"/>
+      <c r="E100" s="11"/>
     </row>
     <row r="101" customHeight="1" spans="1:5">
-      <c r="A101" s="6"/>
+      <c r="A101" s="8"/>
       <c r="B101" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="C101" s="12" t="s">
+      <c r="C101" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="D101" s="8"/>
-      <c r="E101" s="8"/>
+      <c r="D101" s="11"/>
+      <c r="E101" s="11"/>
     </row>
     <row r="102" customHeight="1" spans="1:5">
-      <c r="A102" s="6"/>
+      <c r="A102" s="8"/>
       <c r="B102" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="C102" s="12" t="s">
+      <c r="C102" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="D102" s="8"/>
-      <c r="E102" s="8"/>
+      <c r="D102" s="11"/>
+      <c r="E102" s="11"/>
     </row>
     <row r="103" customHeight="1" spans="1:5">
-      <c r="A103" s="6"/>
-      <c r="B103" s="6" t="s">
+      <c r="A103" s="8"/>
+      <c r="B103" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="C103" s="12" t="s">
+      <c r="C103" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="D103" s="8"/>
-      <c r="E103" s="8"/>
+      <c r="D103" s="11"/>
+      <c r="E103" s="11"/>
     </row>
     <row r="104" customHeight="1" spans="1:5">
-      <c r="A104" s="6"/>
+      <c r="A104" s="8"/>
       <c r="B104" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="C104" s="12" t="s">
+      <c r="C104" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="D104" s="8"/>
-      <c r="E104" s="8"/>
+      <c r="D104" s="11"/>
+      <c r="E104" s="11"/>
     </row>
     <row r="105" customHeight="1" spans="1:5">
-      <c r="A105" s="6"/>
-      <c r="B105" s="6" t="s">
+      <c r="A105" s="8"/>
+      <c r="B105" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="C105" s="12" t="s">
+      <c r="C105" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="D105" s="8"/>
-      <c r="E105" s="8"/>
+      <c r="D105" s="11"/>
+      <c r="E105" s="11"/>
     </row>
     <row r="106" customHeight="1" spans="1:5">
-      <c r="A106" s="6"/>
-      <c r="B106" s="6" t="s">
+      <c r="A106" s="8"/>
+      <c r="B106" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="C106" s="12" t="s">
+      <c r="C106" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="D106" s="8"/>
-      <c r="E106" s="8"/>
+      <c r="D106" s="11"/>
+      <c r="E106" s="11"/>
     </row>
     <row r="107" customHeight="1" spans="1:5">
-      <c r="A107" s="6"/>
+      <c r="A107" s="8"/>
       <c r="B107" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="C107" s="16" t="s">
+      <c r="C107" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="D107" s="8"/>
-      <c r="E107" s="8"/>
+      <c r="D107" s="11"/>
+      <c r="E107" s="11"/>
     </row>
     <row r="108" customHeight="1" spans="1:5">
-      <c r="A108" s="6"/>
-      <c r="B108" s="6" t="s">
+      <c r="A108" s="8"/>
+      <c r="B108" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="C108" s="16" t="s">
+      <c r="C108" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="D108" s="8"/>
-      <c r="E108" s="8"/>
+      <c r="D108" s="11"/>
+      <c r="E108" s="11"/>
     </row>
     <row r="109" customHeight="1" spans="1:5">
-      <c r="A109" s="6"/>
+      <c r="A109" s="8"/>
       <c r="B109" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="C109" s="16" t="s">
+      <c r="C109" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="D109" s="8"/>
-      <c r="E109" s="8"/>
+      <c r="D109" s="11"/>
+      <c r="E109" s="11"/>
     </row>
     <row r="110" customHeight="1" spans="1:5">
-      <c r="A110" s="6"/>
+      <c r="A110" s="8"/>
       <c r="B110" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="C110" s="16" t="s">
+      <c r="C110" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="D110" s="8"/>
-      <c r="E110" s="8"/>
+      <c r="D110" s="11"/>
+      <c r="E110" s="11"/>
     </row>
     <row r="111" customHeight="1" spans="1:5">
-      <c r="A111" s="6"/>
+      <c r="A111" s="8"/>
       <c r="B111" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="C111" s="16" t="s">
+      <c r="C111" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="D111" s="8"/>
-      <c r="E111" s="8"/>
+      <c r="D111" s="11"/>
+      <c r="E111" s="11"/>
     </row>
     <row r="112" customHeight="1" spans="1:5">
-      <c r="A112" s="6"/>
+      <c r="A112" s="8"/>
       <c r="B112" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="C112" s="16" t="s">
+      <c r="C112" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="D112" s="8"/>
-      <c r="E112" s="8"/>
+      <c r="D112" s="11"/>
+      <c r="E112" s="11"/>
     </row>
     <row r="113" customHeight="1" spans="1:5">
-      <c r="A113" s="6"/>
-      <c r="B113" s="6" t="s">
+      <c r="A113" s="8"/>
+      <c r="B113" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="C113" s="16" t="s">
+      <c r="C113" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="D113" s="8"/>
-      <c r="E113" s="8"/>
+      <c r="D113" s="11"/>
+      <c r="E113" s="11"/>
     </row>
     <row r="114" customHeight="1" spans="1:5">
-      <c r="A114" s="6"/>
-      <c r="B114" s="7" t="s">
+      <c r="A114" s="8"/>
+      <c r="B114" s="22" t="s">
         <v>220</v>
       </c>
-      <c r="C114" s="8"/>
-      <c r="D114" s="8"/>
-      <c r="E114" s="8"/>
+      <c r="C114" s="11"/>
+      <c r="D114" s="11"/>
+      <c r="E114" s="11"/>
     </row>
     <row r="115" customHeight="1" spans="1:5">
-      <c r="A115" s="6"/>
-      <c r="B115" s="6" t="s">
+      <c r="A115" s="8"/>
+      <c r="B115" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="C115" s="12" t="s">
+      <c r="C115" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="D115" s="8"/>
-      <c r="E115" s="8"/>
+      <c r="D115" s="11"/>
+      <c r="E115" s="11"/>
     </row>
     <row r="116" customHeight="1" spans="1:5">
-      <c r="A116" s="6"/>
-      <c r="B116" s="6" t="s">
+      <c r="A116" s="8"/>
+      <c r="B116" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="C116" s="12" t="s">
+      <c r="C116" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="D116" s="8"/>
-      <c r="E116" s="8"/>
+      <c r="D116" s="11"/>
+      <c r="E116" s="11"/>
     </row>
     <row r="117" customHeight="1" spans="1:5">
-      <c r="A117" s="6"/>
-      <c r="B117" s="6" t="s">
+      <c r="A117" s="8"/>
+      <c r="B117" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="C117" s="12" t="s">
+      <c r="C117" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="D117" s="8"/>
-      <c r="E117" s="8"/>
+      <c r="D117" s="11"/>
+      <c r="E117" s="11"/>
     </row>
     <row r="118" customHeight="1" spans="1:5">
-      <c r="A118" s="6"/>
-      <c r="B118" s="23" t="s">
+      <c r="A118" s="8"/>
+      <c r="B118" s="25" t="s">
         <v>227</v>
       </c>
-      <c r="C118" s="8"/>
-      <c r="D118" s="8"/>
-      <c r="E118" s="8"/>
+      <c r="C118" s="11"/>
+      <c r="D118" s="11"/>
+      <c r="E118" s="11"/>
     </row>
     <row r="119" customHeight="1" spans="1:5">
-      <c r="A119" s="6"/>
-      <c r="B119" s="6" t="s">
+      <c r="A119" s="8"/>
+      <c r="B119" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="C119" s="12" t="s">
+      <c r="C119" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="D119" s="8"/>
-      <c r="E119" s="8"/>
+      <c r="D119" s="11"/>
+      <c r="E119" s="11"/>
     </row>
     <row r="120" customHeight="1" spans="1:5">
-      <c r="A120" s="6"/>
-      <c r="B120" s="6" t="s">
+      <c r="A120" s="8"/>
+      <c r="B120" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="C120" s="8"/>
-      <c r="D120" s="8"/>
-      <c r="E120" s="8"/>
+      <c r="C120" s="11"/>
+      <c r="D120" s="11"/>
+      <c r="E120" s="11"/>
     </row>
     <row r="121" customHeight="1" spans="1:5">
-      <c r="A121" s="6"/>
-      <c r="B121" s="6" t="s">
+      <c r="A121" s="8"/>
+      <c r="B121" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="C121" s="12" t="s">
+      <c r="C121" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="D121" s="8"/>
-      <c r="E121" s="8"/>
+      <c r="D121" s="11"/>
+      <c r="E121" s="11"/>
     </row>
     <row r="122" customHeight="1" spans="1:5">
-      <c r="A122" s="6"/>
-      <c r="B122" s="6" t="s">
+      <c r="A122" s="8"/>
+      <c r="B122" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="C122" s="12" t="s">
+      <c r="C122" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="D122" s="8"/>
-      <c r="E122" s="8"/>
+      <c r="D122" s="11"/>
+      <c r="E122" s="11"/>
     </row>
     <row r="123" customHeight="1" spans="1:5">
-      <c r="A123" s="6"/>
-      <c r="B123" s="6" t="s">
+      <c r="A123" s="8"/>
+      <c r="B123" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="C123" s="8"/>
-      <c r="D123" s="8"/>
-      <c r="E123" s="8"/>
+      <c r="C123" s="11"/>
+      <c r="D123" s="11"/>
+      <c r="E123" s="11"/>
     </row>
     <row r="124" customHeight="1" spans="1:5">
-      <c r="A124" s="6"/>
-      <c r="B124" s="6" t="s">
+      <c r="A124" s="8"/>
+      <c r="B124" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="C124" s="8"/>
-      <c r="D124" s="8"/>
-      <c r="E124" s="8"/>
+      <c r="C124" s="11"/>
+      <c r="D124" s="11"/>
+      <c r="E124" s="11"/>
     </row>
     <row r="125" customHeight="1" spans="1:5">
-      <c r="A125" s="6"/>
-      <c r="B125" s="6" t="s">
+      <c r="A125" s="8"/>
+      <c r="B125" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="C125" s="8"/>
-      <c r="D125" s="8"/>
-      <c r="E125" s="8"/>
+      <c r="C125" s="11"/>
+      <c r="D125" s="11"/>
+      <c r="E125" s="11"/>
     </row>
     <row r="126" customHeight="1" spans="1:5">
-      <c r="A126" s="6"/>
-      <c r="B126" s="23" t="s">
+      <c r="A126" s="8"/>
+      <c r="B126" s="25" t="s">
         <v>238</v>
       </c>
-      <c r="C126" s="8"/>
-      <c r="D126" s="8"/>
-      <c r="E126" s="8"/>
+      <c r="C126" s="11"/>
+      <c r="D126" s="11"/>
+      <c r="E126" s="11"/>
     </row>
     <row r="127" customHeight="1" spans="1:5">
-      <c r="A127" s="6"/>
-      <c r="B127" s="6" t="s">
+      <c r="A127" s="8"/>
+      <c r="B127" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="C127" s="12" t="s">
+      <c r="C127" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="D127" s="8"/>
-      <c r="E127" s="8"/>
+      <c r="D127" s="11"/>
+      <c r="E127" s="11"/>
     </row>
     <row r="128" customHeight="1" spans="1:5">
-      <c r="A128" s="6"/>
-      <c r="B128" s="6" t="s">
+      <c r="A128" s="8"/>
+      <c r="B128" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="C128" s="12" t="s">
+      <c r="C128" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="D128" s="8"/>
-      <c r="E128" s="8"/>
+      <c r="D128" s="11"/>
+      <c r="E128" s="11"/>
     </row>
     <row r="129" customHeight="1" spans="1:5">
-      <c r="A129" s="6"/>
-      <c r="B129" s="6" t="s">
+      <c r="A129" s="8"/>
+      <c r="B129" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="C129" s="12" t="s">
+      <c r="C129" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="D129" s="8"/>
-      <c r="E129" s="8"/>
+      <c r="D129" s="11"/>
+      <c r="E129" s="11"/>
     </row>
     <row r="130" customHeight="1" spans="1:5">
-      <c r="A130" s="6"/>
-      <c r="B130" s="6" t="s">
+      <c r="A130" s="8"/>
+      <c r="B130" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="C130" s="12" t="s">
+      <c r="C130" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="D130" s="8"/>
-      <c r="E130" s="8"/>
+      <c r="D130" s="11"/>
+      <c r="E130" s="11"/>
     </row>
     <row r="131" customHeight="1" spans="1:5">
-      <c r="A131" s="6"/>
-      <c r="B131" s="23" t="s">
+      <c r="A131" s="8"/>
+      <c r="B131" s="25" t="s">
         <v>247</v>
       </c>
-      <c r="C131" s="8"/>
-      <c r="D131" s="8"/>
-      <c r="E131" s="8"/>
+      <c r="C131" s="11"/>
+      <c r="D131" s="11"/>
+      <c r="E131" s="11"/>
     </row>
     <row r="132" customHeight="1" spans="1:5">
-      <c r="A132" s="6"/>
-      <c r="B132" s="6" t="s">
+      <c r="A132" s="8"/>
+      <c r="B132" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C132" s="12" t="s">
+      <c r="C132" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="D132" s="8"/>
-      <c r="E132" s="8"/>
+      <c r="D132" s="11"/>
+      <c r="E132" s="11"/>
     </row>
     <row r="133" customHeight="1" spans="1:5">
-      <c r="A133" s="6"/>
-      <c r="B133" s="6" t="s">
+      <c r="A133" s="8"/>
+      <c r="B133" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="C133" s="12" t="s">
+      <c r="C133" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="D133" s="8"/>
-      <c r="E133" s="8"/>
+      <c r="D133" s="11"/>
+      <c r="E133" s="11"/>
     </row>
     <row r="134" customHeight="1" spans="1:5">
-      <c r="A134" s="6"/>
-      <c r="B134" s="6" t="s">
+      <c r="A134" s="8"/>
+      <c r="B134" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C134" s="12" t="s">
+      <c r="C134" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="D134" s="8"/>
-      <c r="E134" s="8"/>
+      <c r="D134" s="11"/>
+      <c r="E134" s="11"/>
     </row>
     <row r="135" customHeight="1" spans="1:5">
-      <c r="A135" s="6"/>
-      <c r="B135" s="6" t="s">
+      <c r="A135" s="8"/>
+      <c r="B135" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="C135" s="8"/>
-      <c r="D135" s="8"/>
-      <c r="E135" s="8"/>
+      <c r="C135" s="11"/>
+      <c r="D135" s="11"/>
+      <c r="E135" s="11"/>
     </row>
     <row r="136" customHeight="1" spans="1:5">
-      <c r="A136" s="6"/>
-      <c r="B136" s="6" t="s">
+      <c r="A136" s="8"/>
+      <c r="B136" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="C136" s="8"/>
-      <c r="D136" s="8"/>
-      <c r="E136" s="8"/>
+      <c r="C136" s="11"/>
+      <c r="D136" s="11"/>
+      <c r="E136" s="11"/>
     </row>
     <row r="137" customHeight="1" spans="1:5">
-      <c r="A137" s="6"/>
-      <c r="B137" s="6" t="s">
+      <c r="A137" s="8"/>
+      <c r="B137" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="C137" s="12" t="s">
+      <c r="C137" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="D137" s="8"/>
-      <c r="E137" s="8"/>
+      <c r="D137" s="11"/>
+      <c r="E137" s="11"/>
     </row>
     <row r="138" customHeight="1" spans="1:5">
-      <c r="A138" s="6"/>
-      <c r="B138" s="23" t="s">
+      <c r="A138" s="8"/>
+      <c r="B138" s="25" t="s">
         <v>258</v>
       </c>
-      <c r="C138" s="8"/>
-      <c r="D138" s="8"/>
-      <c r="E138" s="8"/>
+      <c r="C138" s="11"/>
+      <c r="D138" s="11"/>
+      <c r="E138" s="11"/>
     </row>
     <row r="139" customHeight="1" spans="1:5">
-      <c r="A139" s="6"/>
-      <c r="B139" s="6" t="s">
+      <c r="A139" s="8"/>
+      <c r="B139" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="C139" s="8"/>
-      <c r="D139" s="8"/>
-      <c r="E139" s="8"/>
+      <c r="C139" s="11"/>
+      <c r="D139" s="11"/>
+      <c r="E139" s="11"/>
     </row>
     <row r="140" customHeight="1" spans="1:5">
-      <c r="A140" s="6"/>
-      <c r="B140" s="6" t="s">
+      <c r="A140" s="8"/>
+      <c r="B140" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="C140" s="8"/>
-      <c r="D140" s="8"/>
-      <c r="E140" s="8"/>
+      <c r="C140" s="11"/>
+      <c r="D140" s="11"/>
+      <c r="E140" s="11"/>
     </row>
     <row r="141" customHeight="1" spans="1:5">
-      <c r="A141" s="6"/>
-      <c r="B141" s="6" t="s">
+      <c r="A141" s="8"/>
+      <c r="B141" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="C141" s="8"/>
-      <c r="D141" s="8"/>
-      <c r="E141" s="8"/>
+      <c r="C141" s="11"/>
+      <c r="D141" s="11"/>
+      <c r="E141" s="11"/>
     </row>
     <row r="142" customHeight="1" spans="1:5">
-      <c r="A142" s="6"/>
-      <c r="B142" s="6" t="s">
+      <c r="A142" s="8"/>
+      <c r="B142" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="C142" s="8"/>
-      <c r="D142" s="8"/>
-      <c r="E142" s="8"/>
+      <c r="C142" s="11"/>
+      <c r="D142" s="11"/>
+      <c r="E142" s="11"/>
     </row>
     <row r="143" customHeight="1" spans="1:5">
-      <c r="A143" s="6"/>
-      <c r="B143" s="23" t="s">
+      <c r="A143" s="8"/>
+      <c r="B143" s="25" t="s">
         <v>263</v>
       </c>
-      <c r="C143" s="8"/>
-      <c r="D143" s="8"/>
-      <c r="E143" s="8"/>
+      <c r="C143" s="11"/>
+      <c r="D143" s="11"/>
+      <c r="E143" s="11"/>
     </row>
     <row r="144" customHeight="1" spans="1:5">
-      <c r="A144" s="6"/>
-      <c r="B144" s="6" t="s">
+      <c r="A144" s="8"/>
+      <c r="B144" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="C144" s="12" t="s">
+      <c r="C144" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="E144" s="8"/>
+      <c r="E144" s="11"/>
     </row>
     <row r="145" customHeight="1" spans="1:5">
-      <c r="A145" s="6"/>
-      <c r="B145" s="6" t="s">
+      <c r="A145" s="8"/>
+      <c r="B145" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="C145" s="8"/>
-      <c r="D145" s="8"/>
-      <c r="E145" s="8"/>
+      <c r="C145" s="11"/>
+      <c r="D145" s="11"/>
+      <c r="E145" s="11"/>
     </row>
     <row r="146" customHeight="1" spans="1:5">
-      <c r="A146" s="6"/>
-      <c r="B146" s="24" t="s">
+      <c r="A146" s="8"/>
+      <c r="B146" s="26" t="s">
         <v>267</v>
       </c>
-      <c r="C146" s="12" t="s">
+      <c r="C146" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="D146" s="8"/>
-      <c r="E146" s="8"/>
+      <c r="D146" s="11"/>
+      <c r="E146" s="11"/>
     </row>
     <row r="147" customHeight="1" spans="1:5">
-      <c r="A147" s="6"/>
-      <c r="B147" s="6" t="s">
+      <c r="A147" s="8"/>
+      <c r="B147" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="C147" s="8"/>
-      <c r="D147" s="8"/>
-      <c r="E147" s="8"/>
+      <c r="C147" s="11"/>
+      <c r="D147" s="11"/>
+      <c r="E147" s="11"/>
     </row>
     <row r="148" customHeight="1" spans="1:5">
-      <c r="A148" s="6"/>
-      <c r="B148" s="6" t="s">
+      <c r="A148" s="8"/>
+      <c r="B148" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="C148" s="8"/>
-      <c r="D148" s="8"/>
-      <c r="E148" s="8"/>
+      <c r="C148" s="11"/>
+      <c r="D148" s="11"/>
+      <c r="E148" s="11"/>
     </row>
     <row r="149" customHeight="1" spans="1:5">
-      <c r="A149" s="6"/>
-      <c r="B149" s="6" t="s">
+      <c r="A149" s="8"/>
+      <c r="B149" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="C149" s="8"/>
-      <c r="D149" s="8"/>
-      <c r="E149" s="8"/>
+      <c r="C149" s="11"/>
+      <c r="D149" s="11"/>
+      <c r="E149" s="11"/>
     </row>
     <row r="150" customHeight="1" spans="1:5">
-      <c r="A150" s="6"/>
-      <c r="B150" s="6" t="s">
+      <c r="A150" s="8"/>
+      <c r="B150" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="C150" s="12" t="s">
+      <c r="C150" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="D150" s="8"/>
-      <c r="E150" s="8"/>
+      <c r="D150" s="11"/>
+      <c r="E150" s="11"/>
     </row>
     <row r="151" customHeight="1" spans="1:5">
-      <c r="A151" s="6"/>
-      <c r="B151" s="24" t="s">
+      <c r="A151" s="8"/>
+      <c r="B151" s="26" t="s">
         <v>274</v>
       </c>
-      <c r="C151" s="8"/>
-      <c r="D151" s="8"/>
-      <c r="E151" s="8"/>
+      <c r="C151" s="11"/>
+      <c r="D151" s="11"/>
+      <c r="E151" s="11"/>
     </row>
     <row r="152" customHeight="1" spans="1:5">
-      <c r="A152" s="6"/>
-      <c r="B152" s="6" t="s">
+      <c r="A152" s="8"/>
+      <c r="B152" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="C152" s="8"/>
-      <c r="D152" s="8"/>
-      <c r="E152" s="8"/>
+      <c r="C152" s="11"/>
+      <c r="D152" s="11"/>
+      <c r="E152" s="11"/>
     </row>
     <row r="153" customHeight="1" spans="1:5">
-      <c r="A153" s="6"/>
-      <c r="B153" s="6" t="s">
+      <c r="A153" s="8"/>
+      <c r="B153" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="C153" s="8"/>
-      <c r="D153" s="8"/>
-      <c r="E153" s="8"/>
+      <c r="C153" s="11"/>
+      <c r="D153" s="11"/>
+      <c r="E153" s="11"/>
     </row>
     <row r="154" customHeight="1" spans="1:5">
-      <c r="A154" s="6"/>
-      <c r="B154" s="6" t="s">
+      <c r="A154" s="8"/>
+      <c r="B154" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="C154" s="8"/>
-      <c r="D154" s="8"/>
-      <c r="E154" s="8"/>
+      <c r="C154" s="11"/>
+      <c r="D154" s="11"/>
+      <c r="E154" s="11"/>
     </row>
     <row r="155" customHeight="1" spans="1:5">
-      <c r="A155" s="6"/>
-      <c r="B155" s="6" t="s">
+      <c r="A155" s="8"/>
+      <c r="B155" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="C155" s="8"/>
-      <c r="D155" s="8"/>
-      <c r="E155" s="8"/>
+      <c r="C155" s="11"/>
+      <c r="D155" s="11"/>
+      <c r="E155" s="11"/>
     </row>
     <row r="156" customHeight="1" spans="1:5">
-      <c r="A156" s="6"/>
-      <c r="B156" s="6" t="s">
+      <c r="A156" s="8"/>
+      <c r="B156" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="C156" s="8"/>
-      <c r="D156" s="8"/>
-      <c r="E156" s="8"/>
+      <c r="C156" s="11"/>
+      <c r="D156" s="11"/>
+      <c r="E156" s="11"/>
     </row>
     <row r="157" customHeight="1" spans="1:5">
-      <c r="A157" s="6"/>
-      <c r="B157" s="6" t="s">
+      <c r="A157" s="8"/>
+      <c r="B157" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C157" s="8"/>
-      <c r="D157" s="8"/>
-      <c r="E157" s="8"/>
+      <c r="C157" s="11"/>
+      <c r="D157" s="11"/>
+      <c r="E157" s="11"/>
     </row>
     <row r="158" customHeight="1" spans="1:5">
-      <c r="A158" s="6"/>
-      <c r="B158" s="6" t="s">
+      <c r="A158" s="8"/>
+      <c r="B158" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="C158" s="12" t="s">
+      <c r="C158" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="E158" s="8"/>
+      <c r="E158" s="11"/>
     </row>
     <row r="159" customHeight="1" spans="1:5">
-      <c r="A159" s="6"/>
-      <c r="B159" s="23" t="s">
+      <c r="A159" s="8"/>
+      <c r="B159" s="25" t="s">
         <v>283</v>
       </c>
-      <c r="C159" s="8"/>
-      <c r="D159" s="8"/>
-      <c r="E159" s="8"/>
+      <c r="C159" s="11"/>
+      <c r="D159" s="11"/>
+      <c r="E159" s="11"/>
     </row>
     <row r="160" customHeight="1" spans="1:5">
-      <c r="A160" s="6"/>
-      <c r="B160" s="6" t="s">
+      <c r="A160" s="8"/>
+      <c r="B160" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="C160" s="12" t="s">
+      <c r="C160" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="D160" s="8"/>
-      <c r="E160" s="8"/>
+      <c r="D160" s="11"/>
+      <c r="E160" s="11"/>
     </row>
     <row r="161" customHeight="1" spans="1:5">
-      <c r="A161" s="6"/>
-      <c r="B161" s="6" t="s">
+      <c r="A161" s="8"/>
+      <c r="B161" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="C161" s="12" t="s">
+      <c r="C161" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="D161" s="8"/>
-      <c r="E161" s="8"/>
+      <c r="D161" s="11"/>
+      <c r="E161" s="11"/>
     </row>
     <row r="162" customHeight="1" spans="1:5">
-      <c r="A162" s="6"/>
-      <c r="B162" s="6" t="s">
+      <c r="A162" s="8"/>
+      <c r="B162" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="C162" s="12" t="s">
+      <c r="C162" s="13" t="s">
         <v>289</v>
       </c>
-      <c r="D162" s="8"/>
-      <c r="E162" s="8"/>
+      <c r="D162" s="11"/>
+      <c r="E162" s="11"/>
     </row>
     <row r="163" customHeight="1" spans="1:5">
-      <c r="A163" s="6"/>
-      <c r="B163" s="6" t="s">
+      <c r="A163" s="8"/>
+      <c r="B163" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="C163" s="12" t="s">
+      <c r="C163" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="D163" s="8"/>
-      <c r="E163" s="8"/>
+      <c r="D163" s="11"/>
+      <c r="E163" s="11"/>
     </row>
     <row r="164" customHeight="1" spans="1:5">
-      <c r="A164" s="6"/>
-      <c r="B164" s="6" t="s">
+      <c r="A164" s="8"/>
+      <c r="B164" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="C164" s="8"/>
-      <c r="D164" s="8"/>
-      <c r="E164" s="8"/>
+      <c r="C164" s="11"/>
+      <c r="D164" s="11"/>
+      <c r="E164" s="11"/>
     </row>
     <row r="165" customHeight="1" spans="1:5">
-      <c r="A165" s="6"/>
-      <c r="B165" s="23" t="s">
+      <c r="A165" s="8"/>
+      <c r="B165" s="25" t="s">
         <v>293</v>
       </c>
-      <c r="C165" s="8"/>
-      <c r="D165" s="8"/>
-      <c r="E165" s="8"/>
+      <c r="C165" s="11"/>
+      <c r="D165" s="11"/>
+      <c r="E165" s="11"/>
     </row>
     <row r="166" customHeight="1" spans="1:5">
-      <c r="A166" s="6"/>
-      <c r="B166" s="6" t="s">
+      <c r="A166" s="8"/>
+      <c r="B166" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="C166" s="12" t="s">
+      <c r="C166" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="D166" s="8"/>
-      <c r="E166" s="8"/>
+      <c r="D166" s="11"/>
+      <c r="E166" s="11"/>
     </row>
     <row r="167" customHeight="1" spans="1:5">
-      <c r="A167" s="6"/>
-      <c r="B167" s="6" t="s">
+      <c r="A167" s="8"/>
+      <c r="B167" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="C167" s="12" t="s">
+      <c r="C167" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="D167" s="8"/>
-      <c r="E167" s="8"/>
+      <c r="D167" s="11"/>
+      <c r="E167" s="11"/>
     </row>
     <row r="168" customHeight="1" spans="1:5">
-      <c r="A168" s="6"/>
-      <c r="B168" s="6" t="s">
+      <c r="A168" s="8"/>
+      <c r="B168" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="C168" s="12" t="s">
+      <c r="C168" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="D168" s="8"/>
-      <c r="E168" s="8"/>
+      <c r="D168" s="11"/>
+      <c r="E168" s="11"/>
     </row>
     <row r="169" customHeight="1" spans="1:5">
-      <c r="A169" s="6"/>
-      <c r="B169" s="6" t="s">
+      <c r="A169" s="8"/>
+      <c r="B169" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="C169" s="12" t="s">
+      <c r="C169" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="D169" s="8"/>
-      <c r="E169" s="8"/>
+      <c r="D169" s="11"/>
+      <c r="E169" s="11"/>
     </row>
     <row r="170" customHeight="1" spans="1:5">
-      <c r="A170" s="6"/>
-      <c r="B170" s="6" t="s">
+      <c r="A170" s="8"/>
+      <c r="B170" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="C170" s="12" t="s">
+      <c r="C170" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="D170" s="8"/>
-      <c r="E170" s="8"/>
+      <c r="D170" s="11"/>
+      <c r="E170" s="11"/>
     </row>
     <row r="171" customHeight="1" spans="1:5">
-      <c r="A171" s="6"/>
-      <c r="B171" s="6" t="s">
+      <c r="A171" s="8"/>
+      <c r="B171" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="C171" s="12" t="s">
+      <c r="C171" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="D171" s="8"/>
-      <c r="E171" s="8"/>
+      <c r="D171" s="11"/>
+      <c r="E171" s="11"/>
     </row>
     <row r="172" customHeight="1" spans="1:5">
-      <c r="A172" s="6"/>
-      <c r="B172" s="23" t="s">
+      <c r="A172" s="8"/>
+      <c r="B172" s="25" t="s">
         <v>306</v>
       </c>
-      <c r="C172" s="8"/>
-      <c r="D172" s="8"/>
-      <c r="E172" s="8"/>
+      <c r="C172" s="11"/>
+      <c r="D172" s="11"/>
+      <c r="E172" s="11"/>
     </row>
     <row r="173" customHeight="1" spans="1:5">
-      <c r="A173" s="6"/>
-      <c r="B173" s="6" t="s">
+      <c r="A173" s="8"/>
+      <c r="B173" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="C173" s="12" t="s">
+      <c r="C173" s="13" t="s">
         <v>308</v>
       </c>
-      <c r="D173" s="8"/>
-      <c r="E173" s="8"/>
+      <c r="D173" s="11"/>
+      <c r="E173" s="11"/>
     </row>
     <row r="174" customHeight="1" spans="1:5">
-      <c r="A174" s="6"/>
-      <c r="B174" s="6" t="s">
+      <c r="A174" s="8"/>
+      <c r="B174" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="C174" s="12" t="s">
+      <c r="C174" s="13" t="s">
         <v>310</v>
       </c>
-      <c r="D174" s="8"/>
-      <c r="E174" s="8"/>
+      <c r="D174" s="11"/>
+      <c r="E174" s="11"/>
     </row>
     <row r="175" customHeight="1" spans="1:5">
-      <c r="A175" s="6"/>
-      <c r="B175" s="6" t="s">
+      <c r="A175" s="8"/>
+      <c r="B175" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="C175" s="12" t="s">
+      <c r="C175" s="13" t="s">
         <v>312</v>
       </c>
-      <c r="D175" s="8"/>
-      <c r="E175" s="8"/>
+      <c r="D175" s="11"/>
+      <c r="E175" s="11"/>
     </row>
     <row r="176" customHeight="1" spans="1:5">
-      <c r="A176" s="6"/>
-      <c r="B176" s="6" t="s">
+      <c r="A176" s="8"/>
+      <c r="B176" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="C176" s="12" t="s">
+      <c r="C176" s="13" t="s">
         <v>314</v>
       </c>
-      <c r="E176" s="8"/>
+      <c r="E176" s="11"/>
     </row>
     <row r="177" customHeight="1" spans="1:5">
-      <c r="A177" s="6"/>
-      <c r="B177" s="6" t="s">
+      <c r="A177" s="8"/>
+      <c r="B177" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="C177" s="8"/>
-      <c r="D177" s="8"/>
-      <c r="E177" s="8"/>
+      <c r="C177" s="11"/>
+      <c r="D177" s="11"/>
+      <c r="E177" s="11"/>
     </row>
     <row r="178" customHeight="1" spans="1:5">
-      <c r="A178" s="6"/>
-      <c r="B178" s="6" t="s">
+      <c r="A178" s="8"/>
+      <c r="B178" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="C178" s="8"/>
-      <c r="D178" s="8"/>
-      <c r="E178" s="8"/>
+      <c r="C178" s="11"/>
+      <c r="D178" s="11"/>
+      <c r="E178" s="11"/>
     </row>
     <row r="179" customHeight="1" spans="1:5">
-      <c r="A179" s="6"/>
-      <c r="B179" s="23" t="s">
+      <c r="A179" s="8"/>
+      <c r="B179" s="25" t="s">
         <v>317</v>
       </c>
-      <c r="C179" s="8"/>
-      <c r="D179" s="8"/>
-      <c r="E179" s="8"/>
+      <c r="C179" s="11"/>
+      <c r="D179" s="11"/>
+      <c r="E179" s="11"/>
     </row>
     <row r="180" customHeight="1" spans="1:5">
-      <c r="A180" s="6"/>
-      <c r="B180" s="6" t="s">
+      <c r="A180" s="8"/>
+      <c r="B180" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="C180" s="12" t="s">
+      <c r="C180" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="D180" s="12" t="s">
+      <c r="D180" s="13" t="s">
         <v>320</v>
       </c>
-      <c r="E180" s="12" t="s">
+      <c r="E180" s="13" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="181" customHeight="1" spans="1:5">
-      <c r="A181" s="6"/>
-      <c r="B181" s="6" t="s">
+      <c r="A181" s="8"/>
+      <c r="B181" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="C181" s="12" t="s">
+      <c r="C181" s="13" t="s">
         <v>323</v>
       </c>
-      <c r="D181" s="12" t="s">
+      <c r="D181" s="13" t="s">
         <v>324</v>
       </c>
-      <c r="E181" s="8"/>
+      <c r="E181" s="11"/>
     </row>
     <row r="182" customHeight="1" spans="1:5">
-      <c r="A182" s="6"/>
-      <c r="B182" s="6" t="s">
+      <c r="A182" s="8"/>
+      <c r="B182" s="8" t="s">
         <v>325</v>
       </c>
-      <c r="C182" s="12" t="s">
+      <c r="C182" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="D182" s="8"/>
-      <c r="E182" s="8"/>
+      <c r="D182" s="11"/>
+      <c r="E182" s="11"/>
     </row>
     <row r="183" customHeight="1" spans="1:5">
-      <c r="A183" s="6"/>
-      <c r="B183" s="6" t="s">
+      <c r="A183" s="8"/>
+      <c r="B183" s="8" t="s">
         <v>327</v>
       </c>
-      <c r="C183" s="12" t="s">
+      <c r="C183" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="D183" s="8"/>
-      <c r="E183" s="8"/>
+      <c r="D183" s="11"/>
+      <c r="E183" s="11"/>
     </row>
     <row r="184" customHeight="1" spans="1:5">
-      <c r="A184" s="6"/>
-      <c r="B184" s="6" t="s">
+      <c r="A184" s="8"/>
+      <c r="B184" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="C184" s="12" t="s">
+      <c r="C184" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="D184" s="8"/>
-      <c r="E184" s="8"/>
+      <c r="D184" s="11"/>
+      <c r="E184" s="11"/>
     </row>
     <row r="185" customHeight="1" spans="1:5">
-      <c r="A185" s="6"/>
-      <c r="B185" s="23" t="s">
+      <c r="A185" s="8"/>
+      <c r="B185" s="25" t="s">
         <v>331</v>
       </c>
-      <c r="C185" s="8"/>
-      <c r="D185" s="8"/>
-      <c r="E185" s="8"/>
+      <c r="C185" s="11"/>
+      <c r="D185" s="11"/>
+      <c r="E185" s="11"/>
     </row>
     <row r="186" customHeight="1" spans="1:5">
-      <c r="A186" s="6"/>
-      <c r="B186" s="6" t="s">
+      <c r="A186" s="8"/>
+      <c r="B186" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="C186" s="12" t="s">
+      <c r="C186" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="D186" s="8"/>
-      <c r="E186" s="8"/>
+      <c r="D186" s="11"/>
+      <c r="E186" s="11"/>
     </row>
     <row r="187" customHeight="1" spans="1:5">
-      <c r="A187" s="6"/>
-      <c r="B187" s="6" t="s">
+      <c r="A187" s="8"/>
+      <c r="B187" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="C187" s="12" t="s">
+      <c r="C187" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="D187" s="8"/>
-      <c r="E187" s="8"/>
+      <c r="D187" s="11"/>
+      <c r="E187" s="11"/>
     </row>
     <row r="188" customHeight="1" spans="1:5">
-      <c r="A188" s="6"/>
-      <c r="B188" s="6" t="s">
+      <c r="A188" s="8"/>
+      <c r="B188" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="C188" s="12" t="s">
+      <c r="C188" s="13" t="s">
         <v>337</v>
       </c>
-      <c r="D188" s="8"/>
-      <c r="E188" s="8"/>
+      <c r="D188" s="11"/>
+      <c r="E188" s="11"/>
     </row>
     <row r="189" customHeight="1" spans="1:5">
-      <c r="A189" s="6"/>
-      <c r="B189" s="6" t="s">
+      <c r="A189" s="8"/>
+      <c r="B189" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="C189" s="12" t="s">
+      <c r="C189" s="13" t="s">
         <v>339</v>
       </c>
-      <c r="D189" s="8"/>
-      <c r="E189" s="8"/>
+      <c r="D189" s="11"/>
+      <c r="E189" s="11"/>
     </row>
     <row r="190" customHeight="1" spans="1:5">
-      <c r="A190" s="6"/>
-      <c r="B190" s="6" t="s">
+      <c r="A190" s="8"/>
+      <c r="B190" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="C190" s="12" t="s">
+      <c r="C190" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="D190" s="8"/>
-      <c r="E190" s="8"/>
+      <c r="D190" s="11"/>
+      <c r="E190" s="11"/>
     </row>
     <row r="191" customHeight="1" spans="1:5">
-      <c r="A191" s="6"/>
-      <c r="B191" s="23" t="s">
+      <c r="A191" s="8"/>
+      <c r="B191" s="25" t="s">
         <v>342</v>
       </c>
-      <c r="C191" s="8"/>
-      <c r="D191" s="8"/>
-      <c r="E191" s="8"/>
+      <c r="C191" s="11"/>
+      <c r="D191" s="11"/>
+      <c r="E191" s="11"/>
     </row>
     <row r="192" customHeight="1" spans="1:5">
-      <c r="A192" s="6"/>
-      <c r="B192" s="6" t="s">
+      <c r="A192" s="8"/>
+      <c r="B192" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="C192" s="12" t="s">
+      <c r="C192" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="D192" s="8"/>
-      <c r="E192" s="8"/>
+      <c r="D192" s="11"/>
+      <c r="E192" s="11"/>
     </row>
     <row r="193" customHeight="1" spans="1:5">
-      <c r="A193" s="6"/>
-      <c r="B193" s="6" t="s">
+      <c r="A193" s="8"/>
+      <c r="B193" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="C193" s="12" t="s">
+      <c r="C193" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="D193" s="8"/>
-      <c r="E193" s="8"/>
+      <c r="D193" s="11"/>
+      <c r="E193" s="11"/>
     </row>
     <row r="194" customHeight="1" spans="1:5">
-      <c r="A194" s="6"/>
-      <c r="B194" s="6" t="s">
+      <c r="A194" s="8"/>
+      <c r="B194" s="8" t="s">
         <v>347</v>
       </c>
-      <c r="C194" s="12" t="s">
+      <c r="C194" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="D194" s="8"/>
-      <c r="E194" s="8"/>
+      <c r="D194" s="11"/>
+      <c r="E194" s="11"/>
     </row>
     <row r="195" customHeight="1" spans="1:5">
-      <c r="A195" s="6"/>
-      <c r="B195" s="6" t="s">
+      <c r="A195" s="8"/>
+      <c r="B195" s="8" t="s">
         <v>348</v>
       </c>
-      <c r="C195" s="12" t="s">
+      <c r="C195" s="13" t="s">
         <v>349</v>
       </c>
-      <c r="D195" s="8"/>
-      <c r="E195" s="8"/>
+      <c r="D195" s="11"/>
+      <c r="E195" s="11"/>
     </row>
     <row r="196" customHeight="1" spans="1:5">
-      <c r="A196" s="6"/>
-      <c r="B196" s="6" t="s">
+      <c r="A196" s="8"/>
+      <c r="B196" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="C196" s="12" t="s">
+      <c r="C196" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="D196" s="8"/>
-      <c r="E196" s="8"/>
+      <c r="D196" s="11"/>
+      <c r="E196" s="11"/>
     </row>
     <row r="197" customHeight="1" spans="1:5">
-      <c r="A197" s="6"/>
-      <c r="B197" s="6" t="s">
+      <c r="A197" s="8"/>
+      <c r="B197" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="C197" s="12" t="s">
+      <c r="C197" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="D197" s="8"/>
-      <c r="E197" s="8"/>
+      <c r="D197" s="11"/>
+      <c r="E197" s="11"/>
     </row>
     <row r="198" customHeight="1" spans="1:5">
-      <c r="A198" s="6"/>
-      <c r="B198" s="6" t="s">
+      <c r="A198" s="8"/>
+      <c r="B198" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="C198" s="12" t="s">
+      <c r="C198" s="13" t="s">
         <v>355</v>
       </c>
-      <c r="D198" s="8"/>
-      <c r="E198" s="8"/>
+      <c r="D198" s="11"/>
+      <c r="E198" s="11"/>
     </row>
     <row r="199" customHeight="1" spans="1:5">
-      <c r="A199" s="6"/>
-      <c r="B199" s="23" t="s">
+      <c r="A199" s="8"/>
+      <c r="B199" s="25" t="s">
         <v>356</v>
       </c>
-      <c r="C199" s="8"/>
-      <c r="D199" s="8"/>
-      <c r="E199" s="8"/>
+      <c r="C199" s="11"/>
+      <c r="D199" s="11"/>
+      <c r="E199" s="11"/>
     </row>
     <row r="200" customHeight="1" spans="1:5">
-      <c r="A200" s="6"/>
-      <c r="B200" s="6" t="s">
+      <c r="A200" s="8"/>
+      <c r="B200" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="C200" s="12" t="s">
+      <c r="C200" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="D200" s="12" t="s">
+      <c r="D200" s="13" t="s">
         <v>359</v>
       </c>
-      <c r="E200" s="8"/>
+      <c r="E200" s="11"/>
     </row>
     <row r="201" customHeight="1" spans="1:5">
-      <c r="A201" s="6"/>
-      <c r="B201" s="6" t="s">
+      <c r="A201" s="8"/>
+      <c r="B201" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="C201" s="12" t="s">
+      <c r="C201" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="D201" s="8"/>
-      <c r="E201" s="8"/>
+      <c r="D201" s="11"/>
+      <c r="E201" s="11"/>
     </row>
     <row r="202" customHeight="1" spans="1:5">
-      <c r="A202" s="6"/>
-      <c r="B202" s="6" t="s">
+      <c r="A202" s="8"/>
+      <c r="B202" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="C202" s="12" t="s">
+      <c r="C202" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="D202" s="8"/>
-      <c r="E202" s="8"/>
+      <c r="D202" s="11"/>
+      <c r="E202" s="11"/>
     </row>
     <row r="203" customHeight="1" spans="1:5">
-      <c r="A203" s="6"/>
-      <c r="B203" s="6" t="s">
+      <c r="A203" s="8"/>
+      <c r="B203" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="C203" s="12" t="s">
+      <c r="C203" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="D203" s="8"/>
-      <c r="E203" s="8"/>
+      <c r="D203" s="11"/>
+      <c r="E203" s="11"/>
     </row>
     <row r="204" customHeight="1" spans="1:5">
-      <c r="A204" s="6"/>
-      <c r="B204" s="23" t="s">
+      <c r="A204" s="8"/>
+      <c r="B204" s="25" t="s">
         <v>364</v>
       </c>
-      <c r="C204" s="8"/>
-      <c r="D204" s="8"/>
-      <c r="E204" s="8"/>
+      <c r="C204" s="11"/>
+      <c r="D204" s="11"/>
+      <c r="E204" s="11"/>
     </row>
     <row r="205" customHeight="1" spans="1:5">
-      <c r="A205" s="6"/>
-      <c r="B205" s="6" t="s">
+      <c r="A205" s="8"/>
+      <c r="B205" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="C205" s="12" t="s">
+      <c r="C205" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="D205" s="8"/>
-      <c r="E205" s="8"/>
+      <c r="D205" s="11"/>
+      <c r="E205" s="11"/>
     </row>
     <row r="206" customHeight="1" spans="1:5">
-      <c r="A206" s="6"/>
-      <c r="B206" s="6" t="s">
+      <c r="A206" s="8"/>
+      <c r="B206" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="C206" s="12" t="s">
+      <c r="C206" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="D206" s="8"/>
-      <c r="E206" s="8"/>
+      <c r="D206" s="11"/>
+      <c r="E206" s="11"/>
     </row>
     <row r="207" customHeight="1" spans="1:5">
-      <c r="A207" s="6"/>
-      <c r="B207" s="6" t="s">
+      <c r="A207" s="8"/>
+      <c r="B207" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="C207" s="12" t="s">
+      <c r="C207" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="D207" s="12" t="s">
+      <c r="D207" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="E207" s="12" t="s">
+      <c r="E207" s="13" t="s">
         <v>372</v>
       </c>
     </row>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7020"/>
+    <workbookView windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -3474,6 +3474,9 @@
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
+      <c r="F8" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="9" customHeight="1" spans="1:6">
       <c r="A9" s="8"/>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -2846,7 +2846,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2875,6 +2875,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -3488,17 +3489,23 @@
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
+      <c r="F9" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="10" customHeight="1" spans="1:6">
       <c r="A10" s="8"/>
       <c r="B10" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="18" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
+      <c r="F10" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="11" customHeight="1" spans="1:6">
       <c r="A11" s="8"/>
@@ -3524,7 +3531,7 @@
     </row>
     <row r="13" customHeight="1" spans="1:6">
       <c r="A13" s="8"/>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="13" t="s">
@@ -3667,7 +3674,7 @@
       <c r="B26" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="20" t="s">
         <v>55</v>
       </c>
       <c r="D26" s="11"/>
@@ -3805,10 +3812,10 @@
     </row>
     <row r="39" customHeight="1" spans="1:5">
       <c r="A39" s="8"/>
-      <c r="B39" s="20" t="s">
+      <c r="B39" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="20" t="s">
         <v>79</v>
       </c>
       <c r="D39" s="11"/>
@@ -3819,7 +3826,7 @@
       <c r="B40" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="19" t="s">
+      <c r="C40" s="20" t="s">
         <v>81</v>
       </c>
       <c r="D40" s="11"/>
@@ -3827,10 +3834,10 @@
     </row>
     <row r="41" customHeight="1" spans="1:5">
       <c r="A41" s="8"/>
-      <c r="B41" s="20" t="s">
+      <c r="B41" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="C41" s="19" t="s">
+      <c r="C41" s="20" t="s">
         <v>83</v>
       </c>
       <c r="D41" s="11"/>
@@ -3838,10 +3845,10 @@
     </row>
     <row r="42" customHeight="1" spans="1:5">
       <c r="A42" s="8"/>
-      <c r="B42" s="20" t="s">
+      <c r="B42" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="C42" s="19" t="s">
+      <c r="C42" s="20" t="s">
         <v>85</v>
       </c>
       <c r="D42" s="11"/>
@@ -3849,10 +3856,10 @@
     </row>
     <row r="43" customHeight="1" spans="1:5">
       <c r="A43" s="8"/>
-      <c r="B43" s="20" t="s">
+      <c r="B43" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="C43" s="19" t="s">
+      <c r="C43" s="20" t="s">
         <v>87</v>
       </c>
       <c r="D43" s="11"/>
@@ -3860,10 +3867,10 @@
     </row>
     <row r="44" customHeight="1" spans="1:5">
       <c r="A44" s="8"/>
-      <c r="B44" s="20" t="s">
+      <c r="B44" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="C44" s="19" t="s">
+      <c r="C44" s="20" t="s">
         <v>89</v>
       </c>
       <c r="D44" s="11"/>
@@ -3880,10 +3887,10 @@
     </row>
     <row r="46" customHeight="1" spans="1:5">
       <c r="A46" s="8"/>
-      <c r="B46" s="20" t="s">
+      <c r="B46" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="C46" s="19" t="s">
+      <c r="C46" s="20" t="s">
         <v>92</v>
       </c>
       <c r="D46" s="11"/>
@@ -3891,10 +3898,10 @@
     </row>
     <row r="47" customHeight="1" spans="1:5">
       <c r="A47" s="8"/>
-      <c r="B47" s="20" t="s">
+      <c r="B47" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C47" s="19" t="s">
+      <c r="C47" s="20" t="s">
         <v>94</v>
       </c>
       <c r="D47" s="11"/>
@@ -3902,10 +3909,10 @@
     </row>
     <row r="48" customHeight="1" spans="1:5">
       <c r="A48" s="8"/>
-      <c r="B48" s="20" t="s">
+      <c r="B48" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="C48" s="19" t="s">
+      <c r="C48" s="20" t="s">
         <v>96</v>
       </c>
       <c r="D48" s="11"/>
@@ -3913,10 +3920,10 @@
     </row>
     <row r="49" customHeight="1" spans="1:5">
       <c r="A49" s="8"/>
-      <c r="B49" s="20" t="s">
+      <c r="B49" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="C49" s="19" t="s">
+      <c r="C49" s="20" t="s">
         <v>98</v>
       </c>
       <c r="D49" s="11"/>
@@ -3924,10 +3931,10 @@
     </row>
     <row r="50" customHeight="1" spans="1:5">
       <c r="A50" s="8"/>
-      <c r="B50" s="21" t="s">
+      <c r="B50" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="C50" s="19" t="s">
+      <c r="C50" s="20" t="s">
         <v>100</v>
       </c>
       <c r="D50" s="11"/>
@@ -3935,10 +3942,10 @@
     </row>
     <row r="51" customHeight="1" spans="1:5">
       <c r="A51" s="8"/>
-      <c r="B51" s="21" t="s">
+      <c r="B51" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="C51" s="19" t="s">
+      <c r="C51" s="20" t="s">
         <v>102</v>
       </c>
       <c r="D51" s="11"/>
@@ -4202,7 +4209,7 @@
     </row>
     <row r="76" customHeight="1" spans="1:5">
       <c r="A76" s="8"/>
-      <c r="B76" s="22" t="s">
+      <c r="B76" s="23" t="s">
         <v>148</v>
       </c>
       <c r="C76" s="11"/>
@@ -4211,7 +4218,7 @@
     </row>
     <row r="77" customHeight="1" spans="1:5">
       <c r="A77" s="8"/>
-      <c r="B77" s="23" t="s">
+      <c r="B77" s="24" t="s">
         <v>149</v>
       </c>
       <c r="C77" s="13" t="s">
@@ -4308,7 +4315,7 @@
     </row>
     <row r="86" customHeight="1" spans="1:5">
       <c r="A86" s="8"/>
-      <c r="B86" s="22" t="s">
+      <c r="B86" s="23" t="s">
         <v>166</v>
       </c>
       <c r="C86" s="11"/>
@@ -4361,10 +4368,10 @@
     </row>
     <row r="91" customHeight="1" spans="1:5">
       <c r="A91" s="8"/>
-      <c r="B91" s="22" t="s">
+      <c r="B91" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="C91" s="24"/>
+      <c r="C91" s="25"/>
       <c r="D91" s="11"/>
       <c r="E91" s="11"/>
     </row>
@@ -4612,7 +4619,7 @@
     </row>
     <row r="114" customHeight="1" spans="1:5">
       <c r="A114" s="8"/>
-      <c r="B114" s="22" t="s">
+      <c r="B114" s="23" t="s">
         <v>220</v>
       </c>
       <c r="C114" s="11"/>
@@ -4654,7 +4661,7 @@
     </row>
     <row r="118" customHeight="1" spans="1:5">
       <c r="A118" s="8"/>
-      <c r="B118" s="25" t="s">
+      <c r="B118" s="26" t="s">
         <v>227</v>
       </c>
       <c r="C118" s="11"/>
@@ -4732,7 +4739,7 @@
     </row>
     <row r="126" customHeight="1" spans="1:5">
       <c r="A126" s="8"/>
-      <c r="B126" s="25" t="s">
+      <c r="B126" s="26" t="s">
         <v>238</v>
       </c>
       <c r="C126" s="11"/>
@@ -4785,7 +4792,7 @@
     </row>
     <row r="131" customHeight="1" spans="1:5">
       <c r="A131" s="8"/>
-      <c r="B131" s="25" t="s">
+      <c r="B131" s="26" t="s">
         <v>247</v>
       </c>
       <c r="C131" s="11"/>
@@ -4856,7 +4863,7 @@
     </row>
     <row r="138" customHeight="1" spans="1:5">
       <c r="A138" s="8"/>
-      <c r="B138" s="25" t="s">
+      <c r="B138" s="26" t="s">
         <v>258</v>
       </c>
       <c r="C138" s="11"/>
@@ -4901,7 +4908,7 @@
     </row>
     <row r="143" customHeight="1" spans="1:5">
       <c r="A143" s="8"/>
-      <c r="B143" s="25" t="s">
+      <c r="B143" s="26" t="s">
         <v>263</v>
       </c>
       <c r="C143" s="11"/>
@@ -4929,7 +4936,7 @@
     </row>
     <row r="146" customHeight="1" spans="1:5">
       <c r="A146" s="8"/>
-      <c r="B146" s="26" t="s">
+      <c r="B146" s="27" t="s">
         <v>267</v>
       </c>
       <c r="C146" s="13" t="s">
@@ -4978,7 +4985,7 @@
     </row>
     <row r="151" customHeight="1" spans="1:5">
       <c r="A151" s="8"/>
-      <c r="B151" s="26" t="s">
+      <c r="B151" s="27" t="s">
         <v>274</v>
       </c>
       <c r="C151" s="11"/>
@@ -5051,7 +5058,7 @@
     </row>
     <row r="159" customHeight="1" spans="1:5">
       <c r="A159" s="8"/>
-      <c r="B159" s="25" t="s">
+      <c r="B159" s="26" t="s">
         <v>283</v>
       </c>
       <c r="C159" s="11"/>
@@ -5113,7 +5120,7 @@
     </row>
     <row r="165" customHeight="1" spans="1:5">
       <c r="A165" s="8"/>
-      <c r="B165" s="25" t="s">
+      <c r="B165" s="26" t="s">
         <v>293</v>
       </c>
       <c r="C165" s="11"/>
@@ -5188,7 +5195,7 @@
     </row>
     <row r="172" customHeight="1" spans="1:5">
       <c r="A172" s="8"/>
-      <c r="B172" s="25" t="s">
+      <c r="B172" s="26" t="s">
         <v>306</v>
       </c>
       <c r="C172" s="11"/>
@@ -5258,7 +5265,7 @@
     </row>
     <row r="179" customHeight="1" spans="1:5">
       <c r="A179" s="8"/>
-      <c r="B179" s="25" t="s">
+      <c r="B179" s="26" t="s">
         <v>317</v>
       </c>
       <c r="C179" s="11"/>
@@ -5328,7 +5335,7 @@
     </row>
     <row r="185" customHeight="1" spans="1:5">
       <c r="A185" s="8"/>
-      <c r="B185" s="25" t="s">
+      <c r="B185" s="26" t="s">
         <v>331</v>
       </c>
       <c r="C185" s="11"/>
@@ -5392,7 +5399,7 @@
     </row>
     <row r="191" customHeight="1" spans="1:5">
       <c r="A191" s="8"/>
-      <c r="B191" s="25" t="s">
+      <c r="B191" s="26" t="s">
         <v>342</v>
       </c>
       <c r="C191" s="11"/>
@@ -5478,7 +5485,7 @@
     </row>
     <row r="199" customHeight="1" spans="1:5">
       <c r="A199" s="8"/>
-      <c r="B199" s="25" t="s">
+      <c r="B199" s="26" t="s">
         <v>356</v>
       </c>
       <c r="C199" s="11"/>
@@ -5533,7 +5540,7 @@
     </row>
     <row r="204" customHeight="1" spans="1:5">
       <c r="A204" s="8"/>
-      <c r="B204" s="25" t="s">
+      <c r="B204" s="26" t="s">
         <v>364</v>
       </c>
       <c r="C204" s="11"/>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -2149,15 +2149,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -2870,19 +2870,19 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
@@ -3432,19 +3432,22 @@
       </c>
       <c r="D5" s="14"/>
       <c r="E5" s="15"/>
+      <c r="F5" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="6" customHeight="1" spans="1:6">
       <c r="A6" s="8"/>
       <c r="B6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="16" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="12" t="s">
@@ -3456,7 +3459,7 @@
       <c r="B7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="18" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="11"/>
@@ -3470,7 +3473,7 @@
       <c r="B8" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="16" t="s">
         <v>20</v>
       </c>
       <c r="D8" s="11"/>
@@ -3484,7 +3487,7 @@
       <c r="B9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="16" t="s">
         <v>22</v>
       </c>
       <c r="D9" s="11"/>
@@ -3498,7 +3501,7 @@
       <c r="B10" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="13" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="11"/>
@@ -3512,7 +3515,7 @@
       <c r="B11" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D11" s="11"/>
@@ -3528,13 +3531,16 @@
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
+      <c r="F12" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="13" customHeight="1" spans="1:6">
       <c r="A13" s="8"/>
       <c r="B13" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="16" t="s">
         <v>30</v>
       </c>
       <c r="D13" s="11"/>
@@ -3545,7 +3551,7 @@
       <c r="B14" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D14" s="11"/>
@@ -3556,10 +3562,10 @@
       <c r="B15" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="16" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3577,7 +3583,7 @@
       <c r="B17" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="16" t="s">
         <v>38</v>
       </c>
       <c r="D17" s="11"/>
@@ -3588,7 +3594,7 @@
       <c r="B18" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="16" t="s">
         <v>40</v>
       </c>
       <c r="D18" s="11"/>
@@ -3599,7 +3605,7 @@
       <c r="B19" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="16" t="s">
         <v>42</v>
       </c>
       <c r="D19" s="11"/>
@@ -3610,7 +3616,7 @@
       <c r="B20" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="16" t="s">
         <v>44</v>
       </c>
       <c r="D20" s="11"/>
@@ -3621,7 +3627,7 @@
       <c r="B21" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D21" s="11"/>
@@ -3632,7 +3638,7 @@
       <c r="B22" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="16" t="s">
         <v>48</v>
       </c>
       <c r="D22" s="11"/>
@@ -3643,7 +3649,7 @@
       <c r="B23" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="16" t="s">
         <v>50</v>
       </c>
       <c r="D23" s="11"/>
@@ -3654,7 +3660,7 @@
       <c r="B24" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="16" t="s">
         <v>52</v>
       </c>
       <c r="D24" s="11"/>
@@ -3685,7 +3691,7 @@
       <c r="B27" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="16" t="s">
         <v>57</v>
       </c>
       <c r="D27" s="11"/>
@@ -3696,7 +3702,7 @@
       <c r="B28" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="16" t="s">
         <v>59</v>
       </c>
       <c r="D28" s="11"/>
@@ -3707,7 +3713,7 @@
       <c r="B29" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="16" t="s">
         <v>61</v>
       </c>
       <c r="D29" s="11"/>
@@ -3718,7 +3724,7 @@
       <c r="B30" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="16" t="s">
         <v>63</v>
       </c>
       <c r="D30" s="11"/>
@@ -3729,7 +3735,7 @@
       <c r="B31" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="16" t="s">
         <v>65</v>
       </c>
       <c r="D31" s="11"/>
@@ -3740,7 +3746,7 @@
       <c r="B32" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="16" t="s">
         <v>67</v>
       </c>
       <c r="D32" s="11"/>
@@ -3751,7 +3757,7 @@
       <c r="B33" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="16" t="s">
         <v>57</v>
       </c>
       <c r="D33" s="11"/>
@@ -3762,7 +3768,7 @@
       <c r="B34" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="16" t="s">
         <v>70</v>
       </c>
       <c r="D34" s="11"/>
@@ -3773,7 +3779,7 @@
       <c r="B35" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="16" t="s">
         <v>72</v>
       </c>
       <c r="D35" s="11"/>
@@ -3784,7 +3790,7 @@
       <c r="B36" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="16" t="s">
         <v>74</v>
       </c>
       <c r="D36" s="11"/>
@@ -3795,7 +3801,7 @@
       <c r="B37" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="18" t="s">
         <v>76</v>
       </c>
       <c r="D37" s="11"/>
@@ -3965,7 +3971,7 @@
       <c r="B53" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="16" t="s">
         <v>105</v>
       </c>
       <c r="D53" s="11"/>
@@ -3976,7 +3982,7 @@
       <c r="B54" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" s="16" t="s">
         <v>107</v>
       </c>
       <c r="D54" s="11"/>
@@ -3987,7 +3993,7 @@
       <c r="B55" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="C55" s="16" t="s">
         <v>109</v>
       </c>
       <c r="D55" s="11"/>
@@ -3998,7 +4004,7 @@
       <c r="B56" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="C56" s="13" t="s">
+      <c r="C56" s="16" t="s">
         <v>111</v>
       </c>
       <c r="E56" s="11"/>
@@ -4008,7 +4014,7 @@
       <c r="B57" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="C57" s="13" t="s">
+      <c r="C57" s="16" t="s">
         <v>113</v>
       </c>
       <c r="D57" s="11"/>
@@ -4019,7 +4025,7 @@
       <c r="B58" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="C58" s="16" t="s">
         <v>115</v>
       </c>
       <c r="D58" s="11"/>
@@ -4030,7 +4036,7 @@
       <c r="B59" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="C59" s="13" t="s">
+      <c r="C59" s="16" t="s">
         <v>117</v>
       </c>
       <c r="D59" s="11"/>
@@ -4050,7 +4056,7 @@
       <c r="B61" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C61" s="13" t="s">
+      <c r="C61" s="16" t="s">
         <v>120</v>
       </c>
       <c r="E61" s="11"/>
@@ -4060,7 +4066,7 @@
       <c r="B62" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="C62" s="13" t="s">
+      <c r="C62" s="16" t="s">
         <v>122</v>
       </c>
       <c r="D62" s="11"/>
@@ -4071,7 +4077,7 @@
       <c r="B63" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C63" s="13" t="s">
+      <c r="C63" s="16" t="s">
         <v>124</v>
       </c>
       <c r="D63" s="11"/>
@@ -4082,7 +4088,7 @@
       <c r="B64" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="C64" s="13" t="s">
+      <c r="C64" s="16" t="s">
         <v>126</v>
       </c>
       <c r="D64" s="11"/>
@@ -4093,7 +4099,7 @@
       <c r="B65" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C65" s="13" t="s">
+      <c r="C65" s="16" t="s">
         <v>128</v>
       </c>
       <c r="D65" s="11"/>
@@ -4104,7 +4110,7 @@
       <c r="B66" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="C66" s="13" t="s">
+      <c r="C66" s="16" t="s">
         <v>130</v>
       </c>
       <c r="D66" s="11"/>
@@ -4115,7 +4121,7 @@
       <c r="B67" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C67" s="13" t="s">
+      <c r="C67" s="16" t="s">
         <v>132</v>
       </c>
       <c r="D67" s="11"/>
@@ -4126,7 +4132,7 @@
       <c r="B68" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C68" s="13" t="s">
+      <c r="C68" s="16" t="s">
         <v>134</v>
       </c>
       <c r="D68" s="11"/>
@@ -4146,7 +4152,7 @@
       <c r="B70" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="C70" s="13" t="s">
+      <c r="C70" s="16" t="s">
         <v>137</v>
       </c>
       <c r="D70" s="11"/>
@@ -4157,7 +4163,7 @@
       <c r="B71" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="C71" s="13" t="s">
+      <c r="C71" s="16" t="s">
         <v>139</v>
       </c>
       <c r="D71" s="11"/>
@@ -4168,7 +4174,7 @@
       <c r="B72" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="C72" s="13" t="s">
+      <c r="C72" s="16" t="s">
         <v>141</v>
       </c>
       <c r="D72" s="11"/>
@@ -4179,7 +4185,7 @@
       <c r="B73" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="C73" s="13" t="s">
+      <c r="C73" s="16" t="s">
         <v>143</v>
       </c>
       <c r="D73" s="11"/>
@@ -4190,7 +4196,7 @@
       <c r="B74" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="C74" s="13" t="s">
+      <c r="C74" s="16" t="s">
         <v>145</v>
       </c>
       <c r="D74" s="11"/>
@@ -4201,7 +4207,7 @@
       <c r="B75" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="C75" s="13" t="s">
+      <c r="C75" s="16" t="s">
         <v>147</v>
       </c>
       <c r="D75" s="11"/>
@@ -4221,7 +4227,7 @@
       <c r="B77" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="C77" s="13" t="s">
+      <c r="C77" s="16" t="s">
         <v>150</v>
       </c>
       <c r="D77" s="11"/>
@@ -4232,7 +4238,7 @@
       <c r="B78" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="C78" s="13" t="s">
+      <c r="C78" s="16" t="s">
         <v>152</v>
       </c>
       <c r="D78" s="11"/>
@@ -4252,7 +4258,7 @@
       <c r="B80" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="C80" s="13" t="s">
+      <c r="C80" s="16" t="s">
         <v>155</v>
       </c>
       <c r="D80" s="15"/>
@@ -4263,7 +4269,7 @@
       <c r="B81" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="C81" s="13" t="s">
+      <c r="C81" s="16" t="s">
         <v>157</v>
       </c>
       <c r="D81" s="11"/>
@@ -4274,7 +4280,7 @@
       <c r="B82" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="C82" s="13" t="s">
+      <c r="C82" s="16" t="s">
         <v>159</v>
       </c>
       <c r="D82" s="11"/>
@@ -4285,7 +4291,7 @@
       <c r="B83" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="C83" s="13" t="s">
+      <c r="C83" s="16" t="s">
         <v>161</v>
       </c>
       <c r="D83" s="11"/>
@@ -4296,7 +4302,7 @@
       <c r="B84" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="C84" s="13" t="s">
+      <c r="C84" s="16" t="s">
         <v>163</v>
       </c>
       <c r="D84" s="11"/>
@@ -4307,7 +4313,7 @@
       <c r="B85" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="C85" s="13" t="s">
+      <c r="C85" s="16" t="s">
         <v>165</v>
       </c>
       <c r="D85" s="11"/>
@@ -4327,7 +4333,7 @@
       <c r="B87" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="C87" s="13" t="s">
+      <c r="C87" s="16" t="s">
         <v>168</v>
       </c>
       <c r="D87" s="11"/>
@@ -4338,7 +4344,7 @@
       <c r="B88" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C88" s="13" t="s">
+      <c r="C88" s="16" t="s">
         <v>170</v>
       </c>
       <c r="D88" s="11"/>
@@ -4349,7 +4355,7 @@
       <c r="B89" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C89" s="13" t="s">
+      <c r="C89" s="16" t="s">
         <v>172</v>
       </c>
       <c r="D89" s="11"/>
@@ -4360,7 +4366,7 @@
       <c r="B90" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="C90" s="13" t="s">
+      <c r="C90" s="16" t="s">
         <v>174</v>
       </c>
       <c r="D90" s="11"/>
@@ -4380,7 +4386,7 @@
       <c r="B92" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="C92" s="13" t="s">
+      <c r="C92" s="16" t="s">
         <v>177</v>
       </c>
       <c r="D92" s="11"/>
@@ -4391,7 +4397,7 @@
       <c r="B93" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="C93" s="13" t="s">
+      <c r="C93" s="16" t="s">
         <v>179</v>
       </c>
       <c r="D93" s="11"/>
@@ -4402,7 +4408,7 @@
       <c r="B94" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C94" s="13" t="s">
+      <c r="C94" s="16" t="s">
         <v>181</v>
       </c>
       <c r="D94" s="11"/>
@@ -4413,7 +4419,7 @@
       <c r="B95" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="C95" s="13" t="s">
+      <c r="C95" s="16" t="s">
         <v>183</v>
       </c>
       <c r="D95" s="11"/>
@@ -4424,7 +4430,7 @@
       <c r="B96" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="C96" s="13" t="s">
+      <c r="C96" s="16" t="s">
         <v>185</v>
       </c>
       <c r="D96" s="11"/>
@@ -4435,7 +4441,7 @@
       <c r="B97" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="C97" s="13" t="s">
+      <c r="C97" s="16" t="s">
         <v>187</v>
       </c>
       <c r="D97" s="11"/>
@@ -4446,7 +4452,7 @@
       <c r="B98" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="C98" s="13" t="s">
+      <c r="C98" s="16" t="s">
         <v>189</v>
       </c>
       <c r="D98" s="11"/>
@@ -4457,7 +4463,7 @@
       <c r="B99" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="C99" s="13" t="s">
+      <c r="C99" s="16" t="s">
         <v>191</v>
       </c>
       <c r="D99" s="11"/>
@@ -4468,7 +4474,7 @@
       <c r="B100" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="C100" s="13" t="s">
+      <c r="C100" s="16" t="s">
         <v>193</v>
       </c>
       <c r="D100" s="11"/>
@@ -4479,7 +4485,7 @@
       <c r="B101" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="C101" s="13" t="s">
+      <c r="C101" s="16" t="s">
         <v>195</v>
       </c>
       <c r="D101" s="11"/>
@@ -4490,7 +4496,7 @@
       <c r="B102" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="C102" s="13" t="s">
+      <c r="C102" s="16" t="s">
         <v>197</v>
       </c>
       <c r="D102" s="11"/>
@@ -4501,7 +4507,7 @@
       <c r="B103" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="C103" s="13" t="s">
+      <c r="C103" s="16" t="s">
         <v>199</v>
       </c>
       <c r="D103" s="11"/>
@@ -4512,7 +4518,7 @@
       <c r="B104" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="C104" s="13" t="s">
+      <c r="C104" s="16" t="s">
         <v>201</v>
       </c>
       <c r="D104" s="11"/>
@@ -4523,7 +4529,7 @@
       <c r="B105" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="C105" s="13" t="s">
+      <c r="C105" s="16" t="s">
         <v>203</v>
       </c>
       <c r="D105" s="11"/>
@@ -4534,7 +4540,7 @@
       <c r="B106" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="C106" s="13" t="s">
+      <c r="C106" s="16" t="s">
         <v>205</v>
       </c>
       <c r="D106" s="11"/>
@@ -4545,7 +4551,7 @@
       <c r="B107" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="C107" s="17" t="s">
+      <c r="C107" s="18" t="s">
         <v>207</v>
       </c>
       <c r="D107" s="11"/>
@@ -4556,7 +4562,7 @@
       <c r="B108" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="C108" s="17" t="s">
+      <c r="C108" s="18" t="s">
         <v>209</v>
       </c>
       <c r="D108" s="11"/>
@@ -4567,7 +4573,7 @@
       <c r="B109" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="C109" s="17" t="s">
+      <c r="C109" s="18" t="s">
         <v>211</v>
       </c>
       <c r="D109" s="11"/>
@@ -4578,7 +4584,7 @@
       <c r="B110" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="C110" s="17" t="s">
+      <c r="C110" s="18" t="s">
         <v>213</v>
       </c>
       <c r="D110" s="11"/>
@@ -4589,7 +4595,7 @@
       <c r="B111" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="C111" s="17" t="s">
+      <c r="C111" s="18" t="s">
         <v>215</v>
       </c>
       <c r="D111" s="11"/>
@@ -4600,7 +4606,7 @@
       <c r="B112" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="C112" s="17" t="s">
+      <c r="C112" s="18" t="s">
         <v>217</v>
       </c>
       <c r="D112" s="11"/>
@@ -4611,7 +4617,7 @@
       <c r="B113" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="C113" s="17" t="s">
+      <c r="C113" s="18" t="s">
         <v>219</v>
       </c>
       <c r="D113" s="11"/>
@@ -4631,7 +4637,7 @@
       <c r="B115" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="C115" s="13" t="s">
+      <c r="C115" s="16" t="s">
         <v>222</v>
       </c>
       <c r="D115" s="11"/>
@@ -4642,7 +4648,7 @@
       <c r="B116" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="C116" s="13" t="s">
+      <c r="C116" s="16" t="s">
         <v>224</v>
       </c>
       <c r="D116" s="11"/>
@@ -4653,7 +4659,7 @@
       <c r="B117" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="C117" s="13" t="s">
+      <c r="C117" s="16" t="s">
         <v>226</v>
       </c>
       <c r="D117" s="11"/>
@@ -4673,7 +4679,7 @@
       <c r="B119" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="C119" s="13" t="s">
+      <c r="C119" s="16" t="s">
         <v>229</v>
       </c>
       <c r="D119" s="11"/>
@@ -4693,7 +4699,7 @@
       <c r="B121" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="C121" s="13" t="s">
+      <c r="C121" s="16" t="s">
         <v>232</v>
       </c>
       <c r="D121" s="11"/>
@@ -4704,7 +4710,7 @@
       <c r="B122" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="C122" s="13" t="s">
+      <c r="C122" s="16" t="s">
         <v>234</v>
       </c>
       <c r="D122" s="11"/>
@@ -4751,7 +4757,7 @@
       <c r="B127" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="C127" s="13" t="s">
+      <c r="C127" s="16" t="s">
         <v>240</v>
       </c>
       <c r="D127" s="11"/>
@@ -4762,7 +4768,7 @@
       <c r="B128" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="C128" s="13" t="s">
+      <c r="C128" s="16" t="s">
         <v>242</v>
       </c>
       <c r="D128" s="11"/>
@@ -4773,7 +4779,7 @@
       <c r="B129" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="C129" s="13" t="s">
+      <c r="C129" s="16" t="s">
         <v>244</v>
       </c>
       <c r="D129" s="11"/>
@@ -4784,7 +4790,7 @@
       <c r="B130" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="C130" s="13" t="s">
+      <c r="C130" s="16" t="s">
         <v>246</v>
       </c>
       <c r="D130" s="11"/>
@@ -4804,7 +4810,7 @@
       <c r="B132" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C132" s="13" t="s">
+      <c r="C132" s="16" t="s">
         <v>249</v>
       </c>
       <c r="D132" s="11"/>
@@ -4815,7 +4821,7 @@
       <c r="B133" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="C133" s="13" t="s">
+      <c r="C133" s="16" t="s">
         <v>251</v>
       </c>
       <c r="D133" s="11"/>
@@ -4826,7 +4832,7 @@
       <c r="B134" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C134" s="13" t="s">
+      <c r="C134" s="16" t="s">
         <v>253</v>
       </c>
       <c r="D134" s="11"/>
@@ -4855,7 +4861,7 @@
       <c r="B137" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="C137" s="13" t="s">
+      <c r="C137" s="16" t="s">
         <v>257</v>
       </c>
       <c r="D137" s="11"/>
@@ -4920,7 +4926,7 @@
       <c r="B144" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="C144" s="13" t="s">
+      <c r="C144" s="16" t="s">
         <v>265</v>
       </c>
       <c r="E144" s="11"/>
@@ -4939,7 +4945,7 @@
       <c r="B146" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="C146" s="13" t="s">
+      <c r="C146" s="16" t="s">
         <v>268</v>
       </c>
       <c r="D146" s="11"/>
@@ -4977,7 +4983,7 @@
       <c r="B150" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="C150" s="13" t="s">
+      <c r="C150" s="16" t="s">
         <v>273</v>
       </c>
       <c r="D150" s="11"/>
@@ -5051,7 +5057,7 @@
       <c r="B158" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="C158" s="13" t="s">
+      <c r="C158" s="16" t="s">
         <v>282</v>
       </c>
       <c r="E158" s="11"/>
@@ -5070,7 +5076,7 @@
       <c r="B160" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="C160" s="13" t="s">
+      <c r="C160" s="16" t="s">
         <v>285</v>
       </c>
       <c r="D160" s="11"/>
@@ -5081,7 +5087,7 @@
       <c r="B161" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="C161" s="13" t="s">
+      <c r="C161" s="16" t="s">
         <v>287</v>
       </c>
       <c r="D161" s="11"/>
@@ -5092,7 +5098,7 @@
       <c r="B162" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="C162" s="13" t="s">
+      <c r="C162" s="16" t="s">
         <v>289</v>
       </c>
       <c r="D162" s="11"/>
@@ -5103,7 +5109,7 @@
       <c r="B163" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="C163" s="13" t="s">
+      <c r="C163" s="16" t="s">
         <v>291</v>
       </c>
       <c r="D163" s="11"/>
@@ -5132,7 +5138,7 @@
       <c r="B166" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="C166" s="13" t="s">
+      <c r="C166" s="16" t="s">
         <v>295</v>
       </c>
       <c r="D166" s="11"/>
@@ -5143,7 +5149,7 @@
       <c r="B167" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="C167" s="13" t="s">
+      <c r="C167" s="16" t="s">
         <v>297</v>
       </c>
       <c r="D167" s="11"/>
@@ -5154,7 +5160,7 @@
       <c r="B168" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="C168" s="13" t="s">
+      <c r="C168" s="16" t="s">
         <v>299</v>
       </c>
       <c r="D168" s="11"/>
@@ -5165,7 +5171,7 @@
       <c r="B169" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="C169" s="13" t="s">
+      <c r="C169" s="16" t="s">
         <v>301</v>
       </c>
       <c r="D169" s="11"/>
@@ -5176,7 +5182,7 @@
       <c r="B170" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="C170" s="13" t="s">
+      <c r="C170" s="16" t="s">
         <v>303</v>
       </c>
       <c r="D170" s="11"/>
@@ -5187,7 +5193,7 @@
       <c r="B171" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="C171" s="13" t="s">
+      <c r="C171" s="16" t="s">
         <v>305</v>
       </c>
       <c r="D171" s="11"/>
@@ -5207,7 +5213,7 @@
       <c r="B173" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="C173" s="13" t="s">
+      <c r="C173" s="16" t="s">
         <v>308</v>
       </c>
       <c r="D173" s="11"/>
@@ -5218,7 +5224,7 @@
       <c r="B174" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="C174" s="13" t="s">
+      <c r="C174" s="16" t="s">
         <v>310</v>
       </c>
       <c r="D174" s="11"/>
@@ -5229,7 +5235,7 @@
       <c r="B175" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="C175" s="13" t="s">
+      <c r="C175" s="16" t="s">
         <v>312</v>
       </c>
       <c r="D175" s="11"/>
@@ -5240,7 +5246,7 @@
       <c r="B176" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="C176" s="13" t="s">
+      <c r="C176" s="16" t="s">
         <v>314</v>
       </c>
       <c r="E176" s="11"/>
@@ -5277,13 +5283,13 @@
       <c r="B180" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="C180" s="13" t="s">
+      <c r="C180" s="16" t="s">
         <v>319</v>
       </c>
-      <c r="D180" s="13" t="s">
+      <c r="D180" s="16" t="s">
         <v>320</v>
       </c>
-      <c r="E180" s="13" t="s">
+      <c r="E180" s="16" t="s">
         <v>321</v>
       </c>
     </row>
@@ -5292,10 +5298,10 @@
       <c r="B181" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="C181" s="13" t="s">
+      <c r="C181" s="16" t="s">
         <v>323</v>
       </c>
-      <c r="D181" s="13" t="s">
+      <c r="D181" s="16" t="s">
         <v>324</v>
       </c>
       <c r="E181" s="11"/>
@@ -5305,7 +5311,7 @@
       <c r="B182" s="8" t="s">
         <v>325</v>
       </c>
-      <c r="C182" s="13" t="s">
+      <c r="C182" s="16" t="s">
         <v>326</v>
       </c>
       <c r="D182" s="11"/>
@@ -5316,7 +5322,7 @@
       <c r="B183" s="8" t="s">
         <v>327</v>
       </c>
-      <c r="C183" s="13" t="s">
+      <c r="C183" s="16" t="s">
         <v>328</v>
       </c>
       <c r="D183" s="11"/>
@@ -5327,7 +5333,7 @@
       <c r="B184" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="C184" s="13" t="s">
+      <c r="C184" s="16" t="s">
         <v>330</v>
       </c>
       <c r="D184" s="11"/>
@@ -5347,7 +5353,7 @@
       <c r="B186" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="C186" s="13" t="s">
+      <c r="C186" s="16" t="s">
         <v>333</v>
       </c>
       <c r="D186" s="11"/>
@@ -5358,7 +5364,7 @@
       <c r="B187" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="C187" s="13" t="s">
+      <c r="C187" s="16" t="s">
         <v>335</v>
       </c>
       <c r="D187" s="11"/>
@@ -5369,7 +5375,7 @@
       <c r="B188" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="C188" s="13" t="s">
+      <c r="C188" s="16" t="s">
         <v>337</v>
       </c>
       <c r="D188" s="11"/>
@@ -5380,7 +5386,7 @@
       <c r="B189" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="C189" s="13" t="s">
+      <c r="C189" s="16" t="s">
         <v>339</v>
       </c>
       <c r="D189" s="11"/>
@@ -5391,7 +5397,7 @@
       <c r="B190" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="C190" s="13" t="s">
+      <c r="C190" s="16" t="s">
         <v>341</v>
       </c>
       <c r="D190" s="11"/>
@@ -5411,7 +5417,7 @@
       <c r="B192" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="C192" s="13" t="s">
+      <c r="C192" s="16" t="s">
         <v>344</v>
       </c>
       <c r="D192" s="11"/>
@@ -5422,7 +5428,7 @@
       <c r="B193" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="C193" s="13" t="s">
+      <c r="C193" s="16" t="s">
         <v>346</v>
       </c>
       <c r="D193" s="11"/>
@@ -5433,7 +5439,7 @@
       <c r="B194" s="8" t="s">
         <v>347</v>
       </c>
-      <c r="C194" s="13" t="s">
+      <c r="C194" s="16" t="s">
         <v>346</v>
       </c>
       <c r="D194" s="11"/>
@@ -5444,7 +5450,7 @@
       <c r="B195" s="8" t="s">
         <v>348</v>
       </c>
-      <c r="C195" s="13" t="s">
+      <c r="C195" s="16" t="s">
         <v>349</v>
       </c>
       <c r="D195" s="11"/>
@@ -5455,7 +5461,7 @@
       <c r="B196" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="C196" s="13" t="s">
+      <c r="C196" s="16" t="s">
         <v>351</v>
       </c>
       <c r="D196" s="11"/>
@@ -5466,7 +5472,7 @@
       <c r="B197" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="C197" s="13" t="s">
+      <c r="C197" s="16" t="s">
         <v>353</v>
       </c>
       <c r="D197" s="11"/>
@@ -5477,7 +5483,7 @@
       <c r="B198" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="C198" s="13" t="s">
+      <c r="C198" s="16" t="s">
         <v>355</v>
       </c>
       <c r="D198" s="11"/>
@@ -5497,10 +5503,10 @@
       <c r="B200" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="C200" s="13" t="s">
+      <c r="C200" s="16" t="s">
         <v>358</v>
       </c>
-      <c r="D200" s="13" t="s">
+      <c r="D200" s="16" t="s">
         <v>359</v>
       </c>
       <c r="E200" s="11"/>
@@ -5510,7 +5516,7 @@
       <c r="B201" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="C201" s="13" t="s">
+      <c r="C201" s="16" t="s">
         <v>224</v>
       </c>
       <c r="D201" s="11"/>
@@ -5521,7 +5527,7 @@
       <c r="B202" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="C202" s="13" t="s">
+      <c r="C202" s="16" t="s">
         <v>361</v>
       </c>
       <c r="D202" s="11"/>
@@ -5532,7 +5538,7 @@
       <c r="B203" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="C203" s="13" t="s">
+      <c r="C203" s="16" t="s">
         <v>363</v>
       </c>
       <c r="D203" s="11"/>
@@ -5552,7 +5558,7 @@
       <c r="B205" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="C205" s="13" t="s">
+      <c r="C205" s="16" t="s">
         <v>366</v>
       </c>
       <c r="D205" s="11"/>
@@ -5563,7 +5569,7 @@
       <c r="B206" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="C206" s="13" t="s">
+      <c r="C206" s="16" t="s">
         <v>368</v>
       </c>
       <c r="D206" s="11"/>
@@ -5574,13 +5580,13 @@
       <c r="B207" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="C207" s="13" t="s">
+      <c r="C207" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="D207" s="13" t="s">
+      <c r="D207" s="16" t="s">
         <v>371</v>
       </c>
-      <c r="E207" s="13" t="s">
+      <c r="E207" s="16" t="s">
         <v>372</v>
       </c>
     </row>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -164,31 +164,13 @@
     <t>Problem Challenge 1: Quadruple Sum to Target (medium)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
-        <charset val="134"/>
-      </rPr>
-      <t>https://leetcode.com/problems/4sum/</t>
-    </r>
+    <t>https://leetcode.com/problems/4sum/</t>
   </si>
   <si>
     <t>Problem Challenge 2: Comparing Strings containing Backspaces (medium)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
-        <charset val="134"/>
-      </rPr>
-      <t>https://leetcode.com/problems/backspace-string-compare/</t>
-    </r>
+    <t>https://leetcode.com/problems/backspace-string-compare/</t>
   </si>
   <si>
     <t>Problem Challenge 3: Minimum Window Sort (medium)</t>
@@ -2112,7 +2094,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2166,6 +2148,13 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri, sans-serif"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2701,31 +2690,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2734,119 +2720,122 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2877,11 +2866,12 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1"/>
@@ -3365,9 +3355,9 @@
   <cols>
     <col min="1" max="1" width="17.6285714285714" customWidth="1"/>
     <col min="2" max="2" width="65.5047619047619" customWidth="1"/>
-    <col min="3" max="3" width="15.8571428571429" customWidth="1"/>
+    <col min="3" max="3" width="20.1428571428571" customWidth="1"/>
     <col min="4" max="4" width="25.7142857142857" customWidth="1"/>
-    <col min="5" max="5" width="30.5047619047619" customWidth="1"/>
+    <col min="5" max="5" width="39.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:6">
@@ -3540,7 +3530,7 @@
       <c r="B13" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="20" t="s">
         <v>30</v>
       </c>
       <c r="D13" s="11"/>
@@ -3551,7 +3541,7 @@
       <c r="B14" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="20" t="s">
         <v>32</v>
       </c>
       <c r="D14" s="11"/>
@@ -3680,7 +3670,7 @@
       <c r="B26" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="C26" s="21" t="s">
         <v>55</v>
       </c>
       <c r="D26" s="11"/>
@@ -3818,10 +3808,10 @@
     </row>
     <row r="39" customHeight="1" spans="1:5">
       <c r="A39" s="8"/>
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C39" s="20" t="s">
+      <c r="C39" s="21" t="s">
         <v>79</v>
       </c>
       <c r="D39" s="11"/>
@@ -3832,7 +3822,7 @@
       <c r="B40" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="20" t="s">
+      <c r="C40" s="21" t="s">
         <v>81</v>
       </c>
       <c r="D40" s="11"/>
@@ -3840,10 +3830,10 @@
     </row>
     <row r="41" customHeight="1" spans="1:5">
       <c r="A41" s="8"/>
-      <c r="B41" s="21" t="s">
+      <c r="B41" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="C41" s="20" t="s">
+      <c r="C41" s="21" t="s">
         <v>83</v>
       </c>
       <c r="D41" s="11"/>
@@ -3851,10 +3841,10 @@
     </row>
     <row r="42" customHeight="1" spans="1:5">
       <c r="A42" s="8"/>
-      <c r="B42" s="21" t="s">
+      <c r="B42" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C42" s="20" t="s">
+      <c r="C42" s="21" t="s">
         <v>85</v>
       </c>
       <c r="D42" s="11"/>
@@ -3862,10 +3852,10 @@
     </row>
     <row r="43" customHeight="1" spans="1:5">
       <c r="A43" s="8"/>
-      <c r="B43" s="21" t="s">
+      <c r="B43" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="C43" s="20" t="s">
+      <c r="C43" s="21" t="s">
         <v>87</v>
       </c>
       <c r="D43" s="11"/>
@@ -3873,10 +3863,10 @@
     </row>
     <row r="44" customHeight="1" spans="1:5">
       <c r="A44" s="8"/>
-      <c r="B44" s="21" t="s">
+      <c r="B44" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="C44" s="20" t="s">
+      <c r="C44" s="21" t="s">
         <v>89</v>
       </c>
       <c r="D44" s="11"/>
@@ -3893,10 +3883,10 @@
     </row>
     <row r="46" customHeight="1" spans="1:5">
       <c r="A46" s="8"/>
-      <c r="B46" s="21" t="s">
+      <c r="B46" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="C46" s="20" t="s">
+      <c r="C46" s="21" t="s">
         <v>92</v>
       </c>
       <c r="D46" s="11"/>
@@ -3904,10 +3894,10 @@
     </row>
     <row r="47" customHeight="1" spans="1:5">
       <c r="A47" s="8"/>
-      <c r="B47" s="21" t="s">
+      <c r="B47" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="C47" s="20" t="s">
+      <c r="C47" s="21" t="s">
         <v>94</v>
       </c>
       <c r="D47" s="11"/>
@@ -3915,10 +3905,10 @@
     </row>
     <row r="48" customHeight="1" spans="1:5">
       <c r="A48" s="8"/>
-      <c r="B48" s="21" t="s">
+      <c r="B48" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="C48" s="20" t="s">
+      <c r="C48" s="21" t="s">
         <v>96</v>
       </c>
       <c r="D48" s="11"/>
@@ -3926,10 +3916,10 @@
     </row>
     <row r="49" customHeight="1" spans="1:5">
       <c r="A49" s="8"/>
-      <c r="B49" s="21" t="s">
+      <c r="B49" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="C49" s="20" t="s">
+      <c r="C49" s="21" t="s">
         <v>98</v>
       </c>
       <c r="D49" s="11"/>
@@ -3937,10 +3927,10 @@
     </row>
     <row r="50" customHeight="1" spans="1:5">
       <c r="A50" s="8"/>
-      <c r="B50" s="22" t="s">
+      <c r="B50" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="C50" s="20" t="s">
+      <c r="C50" s="21" t="s">
         <v>100</v>
       </c>
       <c r="D50" s="11"/>
@@ -3948,10 +3938,10 @@
     </row>
     <row r="51" customHeight="1" spans="1:5">
       <c r="A51" s="8"/>
-      <c r="B51" s="22" t="s">
+      <c r="B51" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="C51" s="20" t="s">
+      <c r="C51" s="21" t="s">
         <v>102</v>
       </c>
       <c r="D51" s="11"/>
@@ -4215,7 +4205,7 @@
     </row>
     <row r="76" customHeight="1" spans="1:5">
       <c r="A76" s="8"/>
-      <c r="B76" s="23" t="s">
+      <c r="B76" s="24" t="s">
         <v>148</v>
       </c>
       <c r="C76" s="11"/>
@@ -4224,7 +4214,7 @@
     </row>
     <row r="77" customHeight="1" spans="1:5">
       <c r="A77" s="8"/>
-      <c r="B77" s="24" t="s">
+      <c r="B77" s="25" t="s">
         <v>149</v>
       </c>
       <c r="C77" s="16" t="s">
@@ -4321,7 +4311,7 @@
     </row>
     <row r="86" customHeight="1" spans="1:5">
       <c r="A86" s="8"/>
-      <c r="B86" s="23" t="s">
+      <c r="B86" s="24" t="s">
         <v>166</v>
       </c>
       <c r="C86" s="11"/>
@@ -4374,10 +4364,10 @@
     </row>
     <row r="91" customHeight="1" spans="1:5">
       <c r="A91" s="8"/>
-      <c r="B91" s="23" t="s">
+      <c r="B91" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="C91" s="25"/>
+      <c r="C91" s="26"/>
       <c r="D91" s="11"/>
       <c r="E91" s="11"/>
     </row>
@@ -4625,7 +4615,7 @@
     </row>
     <row r="114" customHeight="1" spans="1:5">
       <c r="A114" s="8"/>
-      <c r="B114" s="23" t="s">
+      <c r="B114" s="24" t="s">
         <v>220</v>
       </c>
       <c r="C114" s="11"/>
@@ -4667,7 +4657,7 @@
     </row>
     <row r="118" customHeight="1" spans="1:5">
       <c r="A118" s="8"/>
-      <c r="B118" s="26" t="s">
+      <c r="B118" s="27" t="s">
         <v>227</v>
       </c>
       <c r="C118" s="11"/>
@@ -4745,7 +4735,7 @@
     </row>
     <row r="126" customHeight="1" spans="1:5">
       <c r="A126" s="8"/>
-      <c r="B126" s="26" t="s">
+      <c r="B126" s="27" t="s">
         <v>238</v>
       </c>
       <c r="C126" s="11"/>
@@ -4798,7 +4788,7 @@
     </row>
     <row r="131" customHeight="1" spans="1:5">
       <c r="A131" s="8"/>
-      <c r="B131" s="26" t="s">
+      <c r="B131" s="27" t="s">
         <v>247</v>
       </c>
       <c r="C131" s="11"/>
@@ -4869,7 +4859,7 @@
     </row>
     <row r="138" customHeight="1" spans="1:5">
       <c r="A138" s="8"/>
-      <c r="B138" s="26" t="s">
+      <c r="B138" s="27" t="s">
         <v>258</v>
       </c>
       <c r="C138" s="11"/>
@@ -4914,7 +4904,7 @@
     </row>
     <row r="143" customHeight="1" spans="1:5">
       <c r="A143" s="8"/>
-      <c r="B143" s="26" t="s">
+      <c r="B143" s="27" t="s">
         <v>263</v>
       </c>
       <c r="C143" s="11"/>
@@ -4942,7 +4932,7 @@
     </row>
     <row r="146" customHeight="1" spans="1:5">
       <c r="A146" s="8"/>
-      <c r="B146" s="27" t="s">
+      <c r="B146" s="28" t="s">
         <v>267</v>
       </c>
       <c r="C146" s="16" t="s">
@@ -4991,7 +4981,7 @@
     </row>
     <row r="151" customHeight="1" spans="1:5">
       <c r="A151" s="8"/>
-      <c r="B151" s="27" t="s">
+      <c r="B151" s="28" t="s">
         <v>274</v>
       </c>
       <c r="C151" s="11"/>
@@ -5064,7 +5054,7 @@
     </row>
     <row r="159" customHeight="1" spans="1:5">
       <c r="A159" s="8"/>
-      <c r="B159" s="26" t="s">
+      <c r="B159" s="27" t="s">
         <v>283</v>
       </c>
       <c r="C159" s="11"/>
@@ -5126,7 +5116,7 @@
     </row>
     <row r="165" customHeight="1" spans="1:5">
       <c r="A165" s="8"/>
-      <c r="B165" s="26" t="s">
+      <c r="B165" s="27" t="s">
         <v>293</v>
       </c>
       <c r="C165" s="11"/>
@@ -5201,7 +5191,7 @@
     </row>
     <row r="172" customHeight="1" spans="1:5">
       <c r="A172" s="8"/>
-      <c r="B172" s="26" t="s">
+      <c r="B172" s="27" t="s">
         <v>306</v>
       </c>
       <c r="C172" s="11"/>
@@ -5271,7 +5261,7 @@
     </row>
     <row r="179" customHeight="1" spans="1:5">
       <c r="A179" s="8"/>
-      <c r="B179" s="26" t="s">
+      <c r="B179" s="27" t="s">
         <v>317</v>
       </c>
       <c r="C179" s="11"/>
@@ -5341,7 +5331,7 @@
     </row>
     <row r="185" customHeight="1" spans="1:5">
       <c r="A185" s="8"/>
-      <c r="B185" s="26" t="s">
+      <c r="B185" s="27" t="s">
         <v>331</v>
       </c>
       <c r="C185" s="11"/>
@@ -5405,7 +5395,7 @@
     </row>
     <row r="191" customHeight="1" spans="1:5">
       <c r="A191" s="8"/>
-      <c r="B191" s="26" t="s">
+      <c r="B191" s="27" t="s">
         <v>342</v>
       </c>
       <c r="C191" s="11"/>
@@ -5491,7 +5481,7 @@
     </row>
     <row r="199" customHeight="1" spans="1:5">
       <c r="A199" s="8"/>
-      <c r="B199" s="26" t="s">
+      <c r="B199" s="27" t="s">
         <v>356</v>
       </c>
       <c r="C199" s="11"/>
@@ -5546,7 +5536,7 @@
     </row>
     <row r="204" customHeight="1" spans="1:5">
       <c r="A204" s="8"/>
-      <c r="B204" s="26" t="s">
+      <c r="B204" s="27" t="s">
         <v>364</v>
       </c>
       <c r="C204" s="11"/>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -3568,7 +3568,7 @@
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
     </row>
-    <row r="17" customHeight="1" spans="1:5">
+    <row r="17" customHeight="1" spans="1:6">
       <c r="A17" s="8"/>
       <c r="B17" s="9" t="s">
         <v>37</v>
@@ -3579,7 +3579,7 @@
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
     </row>
-    <row r="18" customHeight="1" spans="1:5">
+    <row r="18" customHeight="1" spans="1:6">
       <c r="A18" s="8"/>
       <c r="B18" s="9" t="s">
         <v>39</v>
@@ -3590,7 +3590,7 @@
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
     </row>
-    <row r="19" customHeight="1" spans="1:5">
+    <row r="19" customHeight="1" spans="1:6">
       <c r="A19" s="8"/>
       <c r="B19" s="9" t="s">
         <v>41</v>
@@ -3601,7 +3601,7 @@
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
     </row>
-    <row r="20" customHeight="1" spans="1:5">
+    <row r="20" customHeight="1" spans="1:6">
       <c r="A20" s="8"/>
       <c r="B20" s="9" t="s">
         <v>43</v>
@@ -3612,7 +3612,7 @@
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
     </row>
-    <row r="21" customHeight="1" spans="1:5">
+    <row r="21" customHeight="1" spans="1:6">
       <c r="A21" s="8"/>
       <c r="B21" s="9" t="s">
         <v>45</v>
@@ -3623,7 +3623,7 @@
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
     </row>
-    <row r="22" customHeight="1" spans="1:5">
+    <row r="22" customHeight="1" spans="1:6">
       <c r="A22" s="8"/>
       <c r="B22" s="8" t="s">
         <v>47</v>
@@ -3634,7 +3634,7 @@
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
     </row>
-    <row r="23" customHeight="1" spans="1:5">
+    <row r="23" customHeight="1" spans="1:6">
       <c r="A23" s="8"/>
       <c r="B23" s="8" t="s">
         <v>49</v>
@@ -3645,7 +3645,7 @@
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
     </row>
-    <row r="24" customHeight="1" spans="1:5">
+    <row r="24" customHeight="1" spans="1:6">
       <c r="A24" s="8"/>
       <c r="B24" s="8" t="s">
         <v>51</v>
@@ -3656,7 +3656,7 @@
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
     </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:5">
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A25" s="7"/>
       <c r="B25" s="7" t="s">
         <v>53</v>
@@ -3665,7 +3665,7 @@
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
     </row>
-    <row r="26" customHeight="1" spans="1:5">
+    <row r="26" customHeight="1" spans="1:6">
       <c r="A26" s="8"/>
       <c r="B26" s="9" t="s">
         <v>54</v>
@@ -3675,8 +3675,11 @@
       </c>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
-    </row>
-    <row r="27" customHeight="1" spans="1:5">
+      <c r="F26" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:6">
       <c r="A27" s="8"/>
       <c r="B27" s="9" t="s">
         <v>56</v>
@@ -3687,7 +3690,7 @@
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
     </row>
-    <row r="28" customHeight="1" spans="1:5">
+    <row r="28" customHeight="1" spans="1:6">
       <c r="A28" s="8"/>
       <c r="B28" s="9" t="s">
         <v>58</v>
@@ -3698,7 +3701,7 @@
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
     </row>
-    <row r="29" customHeight="1" spans="1:5">
+    <row r="29" customHeight="1" spans="1:6">
       <c r="A29" s="8"/>
       <c r="B29" s="9" t="s">
         <v>60</v>
@@ -3709,7 +3712,7 @@
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
     </row>
-    <row r="30" customHeight="1" spans="1:5">
+    <row r="30" customHeight="1" spans="1:6">
       <c r="A30" s="8"/>
       <c r="B30" s="9" t="s">
         <v>62</v>
@@ -3720,7 +3723,7 @@
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
     </row>
-    <row r="31" customHeight="1" spans="1:5">
+    <row r="31" customHeight="1" spans="1:6">
       <c r="A31" s="8"/>
       <c r="B31" s="9" t="s">
         <v>64</v>
@@ -3731,7 +3734,7 @@
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
     </row>
-    <row r="32" customHeight="1" spans="1:5">
+    <row r="32" customHeight="1" spans="1:6">
       <c r="A32" s="8"/>
       <c r="B32" s="9" t="s">
         <v>66</v>
@@ -3742,18 +3745,21 @@
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
     </row>
-    <row r="33" customHeight="1" spans="1:5">
+    <row r="33" customHeight="1" spans="1:6">
       <c r="A33" s="8"/>
       <c r="B33" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="13" t="s">
         <v>57</v>
       </c>
       <c r="D33" s="11"/>
       <c r="E33" s="11"/>
-    </row>
-    <row r="34" customHeight="1" spans="1:5">
+      <c r="F33" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:6">
       <c r="A34" s="8"/>
       <c r="B34" s="9" t="s">
         <v>69</v>
@@ -3764,7 +3770,7 @@
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
     </row>
-    <row r="35" customHeight="1" spans="1:5">
+    <row r="35" customHeight="1" spans="1:6">
       <c r="A35" s="8"/>
       <c r="B35" s="8" t="s">
         <v>71</v>
@@ -3775,7 +3781,7 @@
       <c r="D35" s="11"/>
       <c r="E35" s="11"/>
     </row>
-    <row r="36" customHeight="1" spans="1:5">
+    <row r="36" customHeight="1" spans="1:6">
       <c r="A36" s="8"/>
       <c r="B36" s="8" t="s">
         <v>73</v>
@@ -3786,7 +3792,7 @@
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
     </row>
-    <row r="37" customHeight="1" spans="1:5">
+    <row r="37" customHeight="1" spans="1:6">
       <c r="A37" s="8"/>
       <c r="B37" s="8" t="s">
         <v>75</v>
@@ -3797,7 +3803,7 @@
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
     </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="1:5">
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A38" s="7"/>
       <c r="B38" s="7" t="s">
         <v>77</v>
@@ -3806,7 +3812,7 @@
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
     </row>
-    <row r="39" customHeight="1" spans="1:5">
+    <row r="39" customHeight="1" spans="1:6">
       <c r="A39" s="8"/>
       <c r="B39" s="22" t="s">
         <v>78</v>
@@ -3817,7 +3823,7 @@
       <c r="D39" s="11"/>
       <c r="E39" s="11"/>
     </row>
-    <row r="40" customHeight="1" spans="1:5">
+    <row r="40" customHeight="1" spans="1:6">
       <c r="A40" s="8"/>
       <c r="B40" s="9" t="s">
         <v>80</v>
@@ -3828,7 +3834,7 @@
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
     </row>
-    <row r="41" customHeight="1" spans="1:5">
+    <row r="41" customHeight="1" spans="1:6">
       <c r="A41" s="8"/>
       <c r="B41" s="22" t="s">
         <v>82</v>
@@ -3839,7 +3845,7 @@
       <c r="D41" s="11"/>
       <c r="E41" s="11"/>
     </row>
-    <row r="42" customHeight="1" spans="1:5">
+    <row r="42" customHeight="1" spans="1:6">
       <c r="A42" s="8"/>
       <c r="B42" s="22" t="s">
         <v>84</v>
@@ -3850,7 +3856,7 @@
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
     </row>
-    <row r="43" customHeight="1" spans="1:5">
+    <row r="43" customHeight="1" spans="1:6">
       <c r="A43" s="8"/>
       <c r="B43" s="22" t="s">
         <v>86</v>
@@ -3861,7 +3867,7 @@
       <c r="D43" s="11"/>
       <c r="E43" s="11"/>
     </row>
-    <row r="44" customHeight="1" spans="1:5">
+    <row r="44" customHeight="1" spans="1:6">
       <c r="A44" s="8"/>
       <c r="B44" s="22" t="s">
         <v>88</v>
@@ -3872,7 +3878,7 @@
       <c r="D44" s="11"/>
       <c r="E44" s="11"/>
     </row>
-    <row r="45" s="1" customFormat="1" customHeight="1" spans="1:5">
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A45" s="7"/>
       <c r="B45" s="7" t="s">
         <v>90</v>
@@ -3881,7 +3887,7 @@
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
     </row>
-    <row r="46" customHeight="1" spans="1:5">
+    <row r="46" customHeight="1" spans="1:6">
       <c r="A46" s="8"/>
       <c r="B46" s="22" t="s">
         <v>91</v>
@@ -3892,7 +3898,7 @@
       <c r="D46" s="11"/>
       <c r="E46" s="11"/>
     </row>
-    <row r="47" customHeight="1" spans="1:5">
+    <row r="47" customHeight="1" spans="1:6">
       <c r="A47" s="8"/>
       <c r="B47" s="22" t="s">
         <v>93</v>
@@ -3903,7 +3909,7 @@
       <c r="D47" s="11"/>
       <c r="E47" s="11"/>
     </row>
-    <row r="48" customHeight="1" spans="1:5">
+    <row r="48" customHeight="1" spans="1:6">
       <c r="A48" s="8"/>
       <c r="B48" s="22" t="s">
         <v>95</v>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -3695,11 +3695,14 @@
       <c r="B28" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="13" t="s">
         <v>59</v>
       </c>
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
+      <c r="F28" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="29" customHeight="1" spans="1:6">
       <c r="A29" s="8"/>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -338,16 +338,7 @@
     <t>Fruits into Baskets (medium)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
-        <charset val="134"/>
-      </rPr>
-      <t>https://leetcode.com/problems/fruit-into-baskets/</t>
-    </r>
+    <t>https://leetcode.com/problems/fruit-into-baskets/</t>
   </si>
   <si>
     <t>No-repeat Substring (hard)</t>
@@ -3709,11 +3700,14 @@
       <c r="B29" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="20" t="s">
         <v>61</v>
       </c>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
+      <c r="F29" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="30" customHeight="1" spans="1:6">
       <c r="A30" s="8"/>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -344,16 +344,7 @@
     <t>No-repeat Substring (hard)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
-        <charset val="134"/>
-      </rPr>
-      <t>https://leetcode.com/problems/longest-substring-without-repeating-characters/</t>
-    </r>
+    <t>https://leetcode.com/problems/longest-substring-without-repeating-characters/</t>
   </si>
   <si>
     <t>Longest Substring with Same Letters after Replacement (hard)</t>
@@ -3714,11 +3705,14 @@
       <c r="B30" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="20" t="s">
         <v>63</v>
       </c>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
+      <c r="F30" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="31" customHeight="1" spans="1:6">
       <c r="A31" s="8"/>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -365,16 +365,7 @@
     <t>Longest Subarray with Ones after Replacement (hard)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
-        <charset val="134"/>
-      </rPr>
-      <t>https://leetcode.com/problems/max-consecutive-ones-iii/</t>
-    </r>
+    <t>https://leetcode.com/problems/max-consecutive-ones-iii/</t>
   </si>
   <si>
     <t>Minimum size subarray SUM</t>
@@ -3666,11 +3657,14 @@
       <c r="B27" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="13" t="s">
         <v>57</v>
       </c>
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
+      <c r="F27" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="28" customHeight="1" spans="1:6">
       <c r="A28" s="8"/>
@@ -3724,17 +3718,23 @@
       </c>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
+      <c r="F31" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="32" customHeight="1" spans="1:6">
       <c r="A32" s="8"/>
       <c r="B32" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="20" t="s">
         <v>67</v>
       </c>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
+      <c r="F32" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="33" customHeight="1" spans="1:6">
       <c r="A33" s="8"/>
@@ -3755,11 +3755,14 @@
       <c r="B34" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="13" t="s">
         <v>70</v>
       </c>
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
+      <c r="F34" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="35" customHeight="1" spans="1:6">
       <c r="A35" s="8"/>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7620"/>
+    <workbookView windowWidth="20490" windowHeight="7020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -206,31 +206,13 @@
     <t>LinkedList Cycle (easy)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
-        <charset val="134"/>
-      </rPr>
-      <t>https://leetcode.com/problems/linked-list-cycle/</t>
-    </r>
+    <t>https://leetcode.com/problems/linked-list-cycle/</t>
   </si>
   <si>
     <t>Start of LinkedList Cycle (medium)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
-        <charset val="134"/>
-      </rPr>
-      <t>https://leetcode.com/problems/linked-list-cycle-ii/</t>
-    </r>
+    <t>https://leetcode.com/problems/linked-list-cycle-ii/</t>
   </si>
   <si>
     <t>Happy Number (medium)</t>
@@ -257,16 +239,7 @@
     <t>Middle of the LinkedList (easy)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
-        <charset val="134"/>
-      </rPr>
-      <t>https://leetcode.com/problems/middle-of-the-linked-list/</t>
-    </r>
+    <t>https://leetcode.com/problems/middle-of-the-linked-list/</t>
   </si>
   <si>
     <t>Problem Challenge 1: Palindrome LinkedList (medium)</t>
@@ -3546,22 +3519,28 @@
       <c r="B17" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="20" t="s">
         <v>38</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
+      <c r="F17" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="18" customHeight="1" spans="1:6">
       <c r="A18" s="8"/>
       <c r="B18" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="20" t="s">
         <v>40</v>
       </c>
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
+      <c r="F18" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="19" customHeight="1" spans="1:6">
       <c r="A19" s="8"/>
@@ -3590,7 +3569,7 @@
       <c r="B21" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="20" t="s">
         <v>46</v>
       </c>
       <c r="D21" s="11"/>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -3574,6 +3574,9 @@
       </c>
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
+      <c r="F21" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="22" customHeight="1" spans="1:6">
       <c r="A22" s="8"/>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7020"/>
+    <workbookView windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -218,16 +218,7 @@
     <t>Happy Number (medium)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
-        <charset val="134"/>
-      </rPr>
-      <t>https://leetcode.com/problems/happy-number/</t>
-    </r>
+    <t>https://leetcode.com/problems/happy-number/</t>
   </si>
   <si>
     <t xml:space="preserve"> FIND DUPLICATE NUMBER</t>
@@ -3547,7 +3538,7 @@
       <c r="B19" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="20" t="s">
         <v>42</v>
       </c>
       <c r="D19" s="11"/>
@@ -3558,11 +3549,14 @@
       <c r="B20" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="13" t="s">
         <v>44</v>
       </c>
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
+      <c r="F20" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="21" customHeight="1" spans="1:6">
       <c r="A21" s="8"/>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -3543,6 +3543,9 @@
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
+      <c r="F19" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="20" customHeight="1" spans="1:6">
       <c r="A20" s="8"/>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -3795,6 +3795,9 @@
       </c>
       <c r="D39" s="11"/>
       <c r="E39" s="11"/>
+      <c r="F39" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="40" customHeight="1" spans="1:6">
       <c r="A40" s="8"/>
@@ -3806,6 +3809,9 @@
       </c>
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
+      <c r="F40" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="41" customHeight="1" spans="1:6">
       <c r="A41" s="8"/>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -3823,6 +3823,9 @@
       </c>
       <c r="D41" s="11"/>
       <c r="E41" s="11"/>
+      <c r="F41" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="42" customHeight="1" spans="1:6">
       <c r="A42" s="8"/>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -3837,6 +3837,9 @@
       </c>
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
+      <c r="F42" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="43" customHeight="1" spans="1:6">
       <c r="A43" s="8"/>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -3851,6 +3851,9 @@
       </c>
       <c r="D43" s="11"/>
       <c r="E43" s="11"/>
+      <c r="F43" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="44" customHeight="1" spans="1:6">
       <c r="A44" s="8"/>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7620"/>
+    <workbookView windowWidth="20490" windowHeight="7020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -3865,6 +3865,9 @@
       </c>
       <c r="D44" s="11"/>
       <c r="E44" s="11"/>
+      <c r="F44" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A45" s="7"/>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7020"/>
+    <workbookView windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -3899,6 +3899,9 @@
       </c>
       <c r="D47" s="11"/>
       <c r="E47" s="11"/>
+      <c r="F47" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="48" customHeight="1" spans="1:6">
       <c r="A48" s="8"/>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7620"/>
+    <workbookView windowWidth="20490" windowHeight="7020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -3888,6 +3888,9 @@
       </c>
       <c r="D46" s="11"/>
       <c r="E46" s="11"/>
+      <c r="F46" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="47" customHeight="1" spans="1:6">
       <c r="A47" s="8"/>
@@ -3913,6 +3916,9 @@
       </c>
       <c r="D48" s="11"/>
       <c r="E48" s="11"/>
+      <c r="F48" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="49" customHeight="1" spans="1:5">
       <c r="A49" s="8"/>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -3920,7 +3920,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" customHeight="1" spans="1:5">
+    <row r="49" customHeight="1" spans="1:6">
       <c r="A49" s="8"/>
       <c r="B49" s="22" t="s">
         <v>97</v>
@@ -3930,8 +3930,11 @@
       </c>
       <c r="D49" s="11"/>
       <c r="E49" s="11"/>
-    </row>
-    <row r="50" customHeight="1" spans="1:5">
+      <c r="F49" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="1:6">
       <c r="A50" s="8"/>
       <c r="B50" s="23" t="s">
         <v>99</v>
@@ -3942,7 +3945,7 @@
       <c r="D50" s="11"/>
       <c r="E50" s="11"/>
     </row>
-    <row r="51" customHeight="1" spans="1:5">
+    <row r="51" customHeight="1" spans="1:6">
       <c r="A51" s="8"/>
       <c r="B51" s="23" t="s">
         <v>101</v>
@@ -3953,7 +3956,7 @@
       <c r="D51" s="11"/>
       <c r="E51" s="11"/>
     </row>
-    <row r="52" s="1" customFormat="1" customHeight="1" spans="1:5">
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A52" s="7"/>
       <c r="B52" s="7" t="s">
         <v>103</v>
@@ -3962,7 +3965,7 @@
       <c r="D52" s="7"/>
       <c r="E52" s="7"/>
     </row>
-    <row r="53" customHeight="1" spans="1:5">
+    <row r="53" customHeight="1" spans="1:6">
       <c r="A53" s="8"/>
       <c r="B53" s="9" t="s">
         <v>104</v>
@@ -3973,7 +3976,7 @@
       <c r="D53" s="11"/>
       <c r="E53" s="11"/>
     </row>
-    <row r="54" customHeight="1" spans="1:5">
+    <row r="54" customHeight="1" spans="1:6">
       <c r="A54" s="8"/>
       <c r="B54" s="9" t="s">
         <v>106</v>
@@ -3984,7 +3987,7 @@
       <c r="D54" s="11"/>
       <c r="E54" s="11"/>
     </row>
-    <row r="55" customHeight="1" spans="1:5">
+    <row r="55" customHeight="1" spans="1:6">
       <c r="A55" s="8"/>
       <c r="B55" s="9" t="s">
         <v>108</v>
@@ -3995,7 +3998,7 @@
       <c r="D55" s="11"/>
       <c r="E55" s="11"/>
     </row>
-    <row r="56" customHeight="1" spans="1:5">
+    <row r="56" customHeight="1" spans="1:6">
       <c r="A56" s="8"/>
       <c r="B56" s="9" t="s">
         <v>110</v>
@@ -4005,7 +4008,7 @@
       </c>
       <c r="E56" s="11"/>
     </row>
-    <row r="57" customHeight="1" spans="1:5">
+    <row r="57" customHeight="1" spans="1:6">
       <c r="A57" s="8"/>
       <c r="B57" s="9" t="s">
         <v>112</v>
@@ -4016,7 +4019,7 @@
       <c r="D57" s="11"/>
       <c r="E57" s="11"/>
     </row>
-    <row r="58" customHeight="1" spans="1:5">
+    <row r="58" customHeight="1" spans="1:6">
       <c r="A58" s="8"/>
       <c r="B58" s="8" t="s">
         <v>114</v>
@@ -4027,7 +4030,7 @@
       <c r="D58" s="11"/>
       <c r="E58" s="11"/>
     </row>
-    <row r="59" customHeight="1" spans="1:5">
+    <row r="59" customHeight="1" spans="1:6">
       <c r="A59" s="8"/>
       <c r="B59" s="8" t="s">
         <v>116</v>
@@ -4038,7 +4041,7 @@
       <c r="D59" s="11"/>
       <c r="E59" s="11"/>
     </row>
-    <row r="60" s="1" customFormat="1" customHeight="1" spans="1:5">
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A60" s="7"/>
       <c r="B60" s="7" t="s">
         <v>118</v>
@@ -4047,7 +4050,7 @@
       <c r="D60" s="7"/>
       <c r="E60" s="7"/>
     </row>
-    <row r="61" customHeight="1" spans="1:5">
+    <row r="61" customHeight="1" spans="1:6">
       <c r="A61" s="8"/>
       <c r="B61" s="8" t="s">
         <v>119</v>
@@ -4057,7 +4060,7 @@
       </c>
       <c r="E61" s="11"/>
     </row>
-    <row r="62" customHeight="1" spans="1:5">
+    <row r="62" customHeight="1" spans="1:6">
       <c r="A62" s="8"/>
       <c r="B62" s="8" t="s">
         <v>121</v>
@@ -4068,7 +4071,7 @@
       <c r="D62" s="11"/>
       <c r="E62" s="11"/>
     </row>
-    <row r="63" customHeight="1" spans="1:5">
+    <row r="63" customHeight="1" spans="1:6">
       <c r="A63" s="8"/>
       <c r="B63" s="8" t="s">
         <v>123</v>
@@ -4079,7 +4082,7 @@
       <c r="D63" s="11"/>
       <c r="E63" s="11"/>
     </row>
-    <row r="64" customHeight="1" spans="1:5">
+    <row r="64" customHeight="1" spans="1:6">
       <c r="A64" s="8"/>
       <c r="B64" s="8" t="s">
         <v>125</v>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -3970,11 +3970,14 @@
       <c r="B53" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="C53" s="16" t="s">
+      <c r="C53" s="13" t="s">
         <v>105</v>
       </c>
       <c r="D53" s="11"/>
       <c r="E53" s="11"/>
+      <c r="F53" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="54" customHeight="1" spans="1:6">
       <c r="A54" s="8"/>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -3984,11 +3984,14 @@
       <c r="B54" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="C54" s="16" t="s">
+      <c r="C54" s="13" t="s">
         <v>107</v>
       </c>
       <c r="D54" s="11"/>
       <c r="E54" s="11"/>
+      <c r="F54" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="55" customHeight="1" spans="1:6">
       <c r="A55" s="8"/>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7020"/>
+    <workbookView windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -3998,11 +3998,14 @@
       <c r="B55" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C55" s="16" t="s">
+      <c r="C55" s="13" t="s">
         <v>109</v>
       </c>
       <c r="D55" s="11"/>
       <c r="E55" s="11"/>
+      <c r="F55" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="56" customHeight="1" spans="1:6">
       <c r="A56" s="8"/>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -4016,17 +4016,23 @@
         <v>111</v>
       </c>
       <c r="E56" s="11"/>
+      <c r="F56" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="57" customHeight="1" spans="1:6">
       <c r="A57" s="8"/>
       <c r="B57" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="C57" s="16" t="s">
+      <c r="C57" s="13" t="s">
         <v>113</v>
       </c>
       <c r="D57" s="11"/>
       <c r="E57" s="11"/>
+      <c r="F57" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="58" customHeight="1" spans="1:6">
       <c r="A58" s="8"/>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7620"/>
+    <workbookView windowWidth="20490" windowHeight="6420"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -4108,7 +4108,7 @@
       <c r="D64" s="11"/>
       <c r="E64" s="11"/>
     </row>
-    <row r="65" customHeight="1" spans="1:5">
+    <row r="65" customHeight="1" spans="1:6">
       <c r="A65" s="8"/>
       <c r="B65" s="8" t="s">
         <v>127</v>
@@ -4119,7 +4119,7 @@
       <c r="D65" s="11"/>
       <c r="E65" s="11"/>
     </row>
-    <row r="66" customHeight="1" spans="1:5">
+    <row r="66" customHeight="1" spans="1:6">
       <c r="A66" s="8"/>
       <c r="B66" s="8" t="s">
         <v>129</v>
@@ -4130,7 +4130,7 @@
       <c r="D66" s="11"/>
       <c r="E66" s="11"/>
     </row>
-    <row r="67" customHeight="1" spans="1:5">
+    <row r="67" customHeight="1" spans="1:6">
       <c r="A67" s="8"/>
       <c r="B67" s="8" t="s">
         <v>131</v>
@@ -4141,7 +4141,7 @@
       <c r="D67" s="11"/>
       <c r="E67" s="11"/>
     </row>
-    <row r="68" customHeight="1" spans="1:5">
+    <row r="68" customHeight="1" spans="1:6">
       <c r="A68" s="8"/>
       <c r="B68" s="8" t="s">
         <v>133</v>
@@ -4152,7 +4152,7 @@
       <c r="D68" s="11"/>
       <c r="E68" s="11"/>
     </row>
-    <row r="69" s="1" customFormat="1" customHeight="1" spans="1:5">
+    <row r="69" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A69" s="7"/>
       <c r="B69" s="7" t="s">
         <v>135</v>
@@ -4161,7 +4161,7 @@
       <c r="D69" s="7"/>
       <c r="E69" s="7"/>
     </row>
-    <row r="70" customHeight="1" spans="1:5">
+    <row r="70" customHeight="1" spans="1:6">
       <c r="A70" s="8"/>
       <c r="B70" s="9" t="s">
         <v>136</v>
@@ -4172,7 +4172,7 @@
       <c r="D70" s="11"/>
       <c r="E70" s="11"/>
     </row>
-    <row r="71" customHeight="1" spans="1:5">
+    <row r="71" customHeight="1" spans="1:6">
       <c r="A71" s="8"/>
       <c r="B71" s="9" t="s">
         <v>138</v>
@@ -4183,7 +4183,7 @@
       <c r="D71" s="11"/>
       <c r="E71" s="11"/>
     </row>
-    <row r="72" customHeight="1" spans="1:5">
+    <row r="72" customHeight="1" spans="1:6">
       <c r="A72" s="8"/>
       <c r="B72" s="9" t="s">
         <v>140</v>
@@ -4194,7 +4194,7 @@
       <c r="D72" s="11"/>
       <c r="E72" s="11"/>
     </row>
-    <row r="73" customHeight="1" spans="1:5">
+    <row r="73" customHeight="1" spans="1:6">
       <c r="A73" s="8"/>
       <c r="B73" s="9" t="s">
         <v>142</v>
@@ -4205,7 +4205,7 @@
       <c r="D73" s="11"/>
       <c r="E73" s="11"/>
     </row>
-    <row r="74" customHeight="1" spans="1:5">
+    <row r="74" customHeight="1" spans="1:6">
       <c r="A74" s="8"/>
       <c r="B74" s="8" t="s">
         <v>144</v>
@@ -4216,7 +4216,7 @@
       <c r="D74" s="11"/>
       <c r="E74" s="11"/>
     </row>
-    <row r="75" customHeight="1" spans="1:5">
+    <row r="75" customHeight="1" spans="1:6">
       <c r="A75" s="8"/>
       <c r="B75" s="9" t="s">
         <v>146</v>
@@ -4227,7 +4227,7 @@
       <c r="D75" s="11"/>
       <c r="E75" s="11"/>
     </row>
-    <row r="76" customHeight="1" spans="1:5">
+    <row r="76" customHeight="1" spans="1:6">
       <c r="A76" s="8"/>
       <c r="B76" s="24" t="s">
         <v>148</v>
@@ -4236,18 +4236,21 @@
       <c r="D76" s="11"/>
       <c r="E76" s="11"/>
     </row>
-    <row r="77" customHeight="1" spans="1:5">
+    <row r="77" customHeight="1" spans="1:6">
       <c r="A77" s="8"/>
       <c r="B77" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="C77" s="16" t="s">
+      <c r="C77" s="13" t="s">
         <v>150</v>
       </c>
       <c r="D77" s="11"/>
       <c r="E77" s="11"/>
-    </row>
-    <row r="78" customHeight="1" spans="1:5">
+      <c r="F77" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="1:6">
       <c r="A78" s="8"/>
       <c r="B78" s="9" t="s">
         <v>151</v>
@@ -4258,7 +4261,7 @@
       <c r="D78" s="11"/>
       <c r="E78" s="11"/>
     </row>
-    <row r="79" customHeight="1" spans="1:5">
+    <row r="79" customHeight="1" spans="1:6">
       <c r="A79" s="8"/>
       <c r="B79" s="9" t="s">
         <v>153</v>
@@ -4267,7 +4270,7 @@
       <c r="D79" s="11"/>
       <c r="E79" s="11"/>
     </row>
-    <row r="80" customHeight="1" spans="1:5">
+    <row r="80" customHeight="1" spans="1:6">
       <c r="A80" s="8"/>
       <c r="B80" s="9" t="s">
         <v>154</v>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -737,16 +737,7 @@
     <t>Balanced Parentheses</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
-        <charset val="134"/>
-      </rPr>
-      <t>https://leetcode.com/problems/valid-parentheses/description/</t>
-    </r>
+    <t>https://leetcode.com/problems/valid-parentheses/description/</t>
   </si>
   <si>
     <t>Reverse a String</t>
@@ -761,16 +752,7 @@
     <t>Daily Temperatures (easy)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
-        <charset val="134"/>
-      </rPr>
-      <t>https://leetcode.com/problems/daily-temperatures/</t>
-    </r>
+    <t>https://leetcode.com/problems/daily-temperatures/</t>
   </si>
   <si>
     <t>Remove Nodes From Linked List (easy)</t>
@@ -4255,11 +4237,14 @@
       <c r="B78" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="C78" s="16" t="s">
+      <c r="C78" s="20" t="s">
         <v>152</v>
       </c>
       <c r="D78" s="11"/>
       <c r="E78" s="11"/>
+      <c r="F78" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="79" customHeight="1" spans="1:6">
       <c r="A79" s="8"/>
@@ -4275,24 +4260,27 @@
       <c r="B80" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="C80" s="16" t="s">
+      <c r="C80" s="13" t="s">
         <v>155</v>
       </c>
       <c r="D80" s="15"/>
       <c r="E80" s="15"/>
     </row>
-    <row r="81" customHeight="1" spans="1:5">
+    <row r="81" customHeight="1" spans="1:6">
       <c r="A81" s="8"/>
       <c r="B81" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="C81" s="16" t="s">
+      <c r="C81" s="20" t="s">
         <v>157</v>
       </c>
       <c r="D81" s="11"/>
       <c r="E81" s="11"/>
-    </row>
-    <row r="82" customHeight="1" spans="1:5">
+      <c r="F81" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="1:6">
       <c r="A82" s="8"/>
       <c r="B82" s="8" t="s">
         <v>158</v>
@@ -4303,7 +4291,7 @@
       <c r="D82" s="11"/>
       <c r="E82" s="11"/>
     </row>
-    <row r="83" customHeight="1" spans="1:5">
+    <row r="83" customHeight="1" spans="1:6">
       <c r="A83" s="8"/>
       <c r="B83" s="9" t="s">
         <v>160</v>
@@ -4314,7 +4302,7 @@
       <c r="D83" s="11"/>
       <c r="E83" s="11"/>
     </row>
-    <row r="84" customHeight="1" spans="1:5">
+    <row r="84" customHeight="1" spans="1:6">
       <c r="A84" s="8"/>
       <c r="B84" s="8" t="s">
         <v>162</v>
@@ -4325,7 +4313,7 @@
       <c r="D84" s="11"/>
       <c r="E84" s="11"/>
     </row>
-    <row r="85" customHeight="1" spans="1:5">
+    <row r="85" customHeight="1" spans="1:6">
       <c r="A85" s="8"/>
       <c r="B85" s="8" t="s">
         <v>164</v>
@@ -4336,7 +4324,7 @@
       <c r="D85" s="11"/>
       <c r="E85" s="11"/>
     </row>
-    <row r="86" customHeight="1" spans="1:5">
+    <row r="86" customHeight="1" spans="1:6">
       <c r="A86" s="8"/>
       <c r="B86" s="24" t="s">
         <v>166</v>
@@ -4345,7 +4333,7 @@
       <c r="D86" s="11"/>
       <c r="E86" s="11"/>
     </row>
-    <row r="87" customHeight="1" spans="1:5">
+    <row r="87" customHeight="1" spans="1:6">
       <c r="A87" s="8"/>
       <c r="B87" s="9" t="s">
         <v>167</v>
@@ -4356,7 +4344,7 @@
       <c r="D87" s="11"/>
       <c r="E87" s="11"/>
     </row>
-    <row r="88" customHeight="1" spans="1:5">
+    <row r="88" customHeight="1" spans="1:6">
       <c r="A88" s="8"/>
       <c r="B88" s="9" t="s">
         <v>169</v>
@@ -4367,7 +4355,7 @@
       <c r="D88" s="11"/>
       <c r="E88" s="11"/>
     </row>
-    <row r="89" customHeight="1" spans="1:5">
+    <row r="89" customHeight="1" spans="1:6">
       <c r="A89" s="8"/>
       <c r="B89" s="9" t="s">
         <v>171</v>
@@ -4378,7 +4366,7 @@
       <c r="D89" s="11"/>
       <c r="E89" s="11"/>
     </row>
-    <row r="90" customHeight="1" spans="1:5">
+    <row r="90" customHeight="1" spans="1:6">
       <c r="A90" s="8"/>
       <c r="B90" s="9" t="s">
         <v>173</v>
@@ -4389,7 +4377,7 @@
       <c r="D90" s="11"/>
       <c r="E90" s="11"/>
     </row>
-    <row r="91" customHeight="1" spans="1:5">
+    <row r="91" customHeight="1" spans="1:6">
       <c r="A91" s="8"/>
       <c r="B91" s="24" t="s">
         <v>175</v>
@@ -4398,7 +4386,7 @@
       <c r="D91" s="11"/>
       <c r="E91" s="11"/>
     </row>
-    <row r="92" customHeight="1" spans="1:5">
+    <row r="92" customHeight="1" spans="1:6">
       <c r="A92" s="8"/>
       <c r="B92" s="9" t="s">
         <v>176</v>
@@ -4409,7 +4397,7 @@
       <c r="D92" s="11"/>
       <c r="E92" s="11"/>
     </row>
-    <row r="93" customHeight="1" spans="1:5">
+    <row r="93" customHeight="1" spans="1:6">
       <c r="A93" s="8"/>
       <c r="B93" s="9" t="s">
         <v>178</v>
@@ -4420,7 +4408,7 @@
       <c r="D93" s="11"/>
       <c r="E93" s="11"/>
     </row>
-    <row r="94" customHeight="1" spans="1:5">
+    <row r="94" customHeight="1" spans="1:6">
       <c r="A94" s="8"/>
       <c r="B94" s="9" t="s">
         <v>180</v>
@@ -4431,7 +4419,7 @@
       <c r="D94" s="11"/>
       <c r="E94" s="11"/>
     </row>
-    <row r="95" customHeight="1" spans="1:5">
+    <row r="95" customHeight="1" spans="1:6">
       <c r="A95" s="8"/>
       <c r="B95" s="9" t="s">
         <v>182</v>
@@ -4442,7 +4430,7 @@
       <c r="D95" s="11"/>
       <c r="E95" s="11"/>
     </row>
-    <row r="96" customHeight="1" spans="1:5">
+    <row r="96" customHeight="1" spans="1:6">
       <c r="A96" s="8"/>
       <c r="B96" s="8" t="s">
         <v>184</v>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6420"/>
+    <workbookView windowWidth="20490" windowHeight="7020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -4265,6 +4265,9 @@
       </c>
       <c r="D80" s="15"/>
       <c r="E80" s="15"/>
+      <c r="F80" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="81" customHeight="1" spans="1:6">
       <c r="A81" s="8"/>

--- a/DSA patterns Cheat Sheet.xlsx
+++ b/DSA patterns Cheat Sheet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="373">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -773,16 +773,7 @@
     <t>Remove All Adjacent Duplicates in String II (medium)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
-        <charset val="134"/>
-      </rPr>
-      <t>https://leetcode.com/problems/remove-all-adjacent-duplicates-in-string-ii/</t>
-    </r>
+    <t>https://leetcode.com/problems/remove-all-adjacent-duplicates-in-string-ii/</t>
   </si>
   <si>
     <t xml:space="preserve">Simplify Path (Problem Challenge) </t>
@@ -4299,11 +4290,14 @@
       <c r="B83" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="C83" s="16" t="s">
+      <c r="C83" s="20" t="s">
         <v>161</v>
       </c>
       <c r="D83" s="11"/>
       <c r="E83" s="11"/>
+      <c r="F83" s="12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="84" customHeight="1" spans="1:6">
       <c r="A84" s="8"/>
